--- a/docs/cacheBandit_metrics.xlsx
+++ b/docs/cacheBandit_metrics.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91988\Documents\Amruth\Files\Projects\CacheBandit\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91988\Documents\Amruth\Files\Git\cacheBandit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F2190E-D5D4-4404-986C-C9C44DA11709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{909F447A-5CC2-4576-836F-4ACFE0684599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C4CDEA3B-1686-49FD-8414-9D1FD93CDC23}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C4CDEA3B-1686-49FD-8414-9D1FD93CDC23}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet5" sheetId="5" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="65">
   <si>
     <t>Thread Count</t>
   </si>
@@ -186,10 +187,40 @@
     <t>DRAM Access Reduction</t>
   </si>
   <si>
-    <t>DYNAMIC: Virtual Sets</t>
+    <t>STATIC: SINGLE-WARP Virtual Sets</t>
   </si>
   <si>
-    <t>STATIC: Virtual Sets</t>
+    <t>DYNAMIC: SINGLE-WARP Virtual Sets</t>
+  </si>
+  <si>
+    <t>STATIC: MULTI-WARP Virtual Sets</t>
+  </si>
+  <si>
+    <t>Warps</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Cache Segment Size (per warp)</t>
+  </si>
+  <si>
+    <t>L1+L2</t>
+  </si>
+  <si>
+    <t>L1+L2 Hit-rate</t>
+  </si>
+  <si>
+    <t>L1+L2 Miss-Rate</t>
+  </si>
+  <si>
+    <t>Baseline Cache Efficiency</t>
+  </si>
+  <si>
+    <t>CacheBandit Cache Efficiency</t>
+  </si>
+  <si>
+    <t>DYNAMIC: MULTI-WARP Virtual Sets</t>
   </si>
 </sst>
 </file>
@@ -2893,6 +2924,2450 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$26</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>DRAM Access Reduction</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$23:$Q$23</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>bcsstk10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>bcsstk13</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bcsstk17</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>c8_mat11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cq9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>fv1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>kl02</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>lhr34c</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>pdb1HYS</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>psmigr_1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>wiki-Vote</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>p2p-Gnutella04</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>ca-HepTh</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>as-735</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>amazon0312</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$26:$Q$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-29.300291545189506</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>97.211229573071364</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>55.297801181242434</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.6418149751483084</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.2666666666666666</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16.729155507945009</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>77.765237020316022</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>94.344547563805108</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>53.928571428571423</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>44.899603787522665</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>85.744109752460488</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-0.50284463084607511</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DDAA-43E4-BC3B-B1759801FC3C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="2069589295"/>
+        <c:axId val="2069590255"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="2069589295"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Matrix</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2069590255"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2069590255"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Reduction (%)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2069589295"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Cache Hit-Rate</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$24</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Baseline Hit-Rate</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$23:$Q$23</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>bcsstk10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>bcsstk13</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bcsstk17</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>c8_mat11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cq9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>fv1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>kl02</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>lhr34c</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>pdb1HYS</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>psmigr_1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>wiki-Vote</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>p2p-Gnutella04</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>ca-HepTh</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>as-735</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>amazon0312</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$24:$Q$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>99.691889442682367</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>99.904801480865856</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>99.897115947028212</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>99.249923085599704</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>85.634551495016609</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>99.51951903935786</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>85.452382618431173</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>99.715949054786662</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>99.902192129164362</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>99.882385893741102</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>90.163466750349471</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>84.015603815323132</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>71.354647583871952</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>87.535315985130111</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46.078210819316226</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-19C4-42DF-B810-1172D010ED74}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$25</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CacheBandit Hit-Rate</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$23:$Q$23</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>bcsstk10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>bcsstk13</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bcsstk17</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>c8_mat11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cq9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>fv1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>kl02</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>lhr34c</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>pdb1HYS</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>psmigr_1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>wiki-Vote</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>p2p-Gnutella04</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>ca-HepTh</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>as-735</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>amazon0312</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$25:$Q$25</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>99.691889442682367</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>99.90603115887447</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>99.870745493943105</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>99.985138139627551</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>94.522435170814219</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>99.521092641879292</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>87.260932224155766</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>99.788656941353764</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>99.933753651077183</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>99.974959356620701</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>99.514256771343639</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>93.135559398696287</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>84.433989110432364</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>98.383934005003709</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>49.251804673890618</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-19C4-42DF-B810-1172D010ED74}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1931578063"/>
+        <c:axId val="1931577103"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1931578063"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Matrix</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1931577103"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1931577103"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Hit-Rate (%)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1931578063"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Cache Efficiency</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$27</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Baseline Cache Efficiency</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$23:$Q$23</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>bcsstk10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>bcsstk13</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bcsstk17</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>c8_mat11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cq9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>fv1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>kl02</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>lhr34c</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>pdb1HYS</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>psmigr_1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>wiki-Vote</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>p2p-Gnutella04</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>ca-HepTh</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>as-735</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>amazon0312</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$27:$Q$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.6807113925229294E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.5780260442610121E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.3561006894340225E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.836952380952381</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.40653454740224959</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.22234762979683972</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.8917246713070378E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.10119047619047619</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.150157813444362E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.14255890247539516</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-72BB-4746-AA64-BFA97CA8B8D0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$28</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CacheBandit Cache Efficiency</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$23:$Q$23</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>bcsstk10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>bcsstk13</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bcsstk17</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>c8_mat11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cq9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>fv1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>kl02</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>lhr34c</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>pdb1HYS</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>psmigr_1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>wiki-Vote</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>p2p-Gnutella04</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>ca-HepTh</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>as-735</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>amazon0312</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$28:$Q$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.77339346110484786</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.60267111853088484</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.2142629735752945</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.478890229191798E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.87425387982491043</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.4882075471698113</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.86495726495726499</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.21963824289405684</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7.5319926873857398E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-72BB-4746-AA64-BFA97CA8B8D0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:axId val="191828015"/>
+        <c:axId val="191818895"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="191828015"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Matrix</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="191818895"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="191818895"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Efficiency</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> (normalized)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="191828015"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:minorUnit val="5.000000000000001E-2"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$108</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>DRAM Access Reduction</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$105:$Q$105</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>bcsstk10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>bcsstk13</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bcsstk17</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>c8_mat11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cq9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>fv1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>kl02</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>lhr34c</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>pdb1HYS</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>psmigr_1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>wiki-Vote</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>p2p-Gnutella04</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>ca-HepTh</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>as-735</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>amazon0312</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$108:$Q$108</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>97.211229573071364</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>55.297801181242434</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.6418149751483084</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.2666666666666666</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16.729155507945009</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>77.765237020316022</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>94.344547563805108</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>53.928571428571423</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>44.899603787522665</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>85.744109752460488</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-78BE-4C30-B15D-43DBAE6F3E49}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1331473039"/>
+        <c:axId val="1331474479"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1331473039"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1600"/>
+                  <a:t>Matrix</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1331474479"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1331474479"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="100"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1600"/>
+                  <a:t>Reduction (%)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1331473039"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:minorUnit val="5"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -3053,6 +5528,166 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -4564,6 +7199,2018 @@
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -5194,6 +9841,155 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD0E03B0-AF43-6D49-820A-B8F5E1B0E056}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>201386</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>139881</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>125186</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>65314</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1736FF9B-3318-8ED0-6DC5-C591BB6FC89F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CBF9E7A-D1ED-9DB0-0083-60C6E05A57F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>293914</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>65314</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>293914</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>152401</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60927775-A7F2-C7F4-9C67-1EF1AE323CD9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>533399</xdr:colOff>
+      <xdr:row>113</xdr:row>
+      <xdr:rowOff>10884</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>65314</xdr:colOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E3F834D-3268-A9B6-651E-4964FE425745}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5548,7 +10344,7 @@
   <sheetData>
     <row r="2" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -7819,7 +12615,7 @@
     </row>
     <row r="63" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B63" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
@@ -10172,4 +14968,4961 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CEFDD9D-FDB3-41CB-A695-1350C2A9CE69}">
+  <dimension ref="B2:AN110"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="3"/>
+      <c r="AE2" s="3"/>
+      <c r="AF2" s="3"/>
+      <c r="AG2" s="3"/>
+      <c r="AH2" s="3"/>
+      <c r="AI2" s="3"/>
+      <c r="AJ2" s="3"/>
+      <c r="AK2" s="3"/>
+      <c r="AL2" s="3"/>
+      <c r="AM2" s="3"/>
+      <c r="AN2" s="3"/>
+    </row>
+    <row r="3" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z3" s="2"/>
+      <c r="AA3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB3" s="2"/>
+      <c r="AC3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD3" s="2"/>
+      <c r="AE3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF3" s="2"/>
+      <c r="AG3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH3" s="2"/>
+      <c r="AI3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ3" s="2"/>
+      <c r="AK3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL3" s="2"/>
+      <c r="AM3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN3" s="2"/>
+    </row>
+    <row r="4" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD4" s="2"/>
+      <c r="AE4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF4" s="2"/>
+      <c r="AG4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AH4" s="2"/>
+      <c r="AI4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AJ4" s="2"/>
+      <c r="AK4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AL4" s="2"/>
+      <c r="AM4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN4" s="2"/>
+    </row>
+    <row r="5" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" t="s">
+        <v>13</v>
+      </c>
+      <c r="M5" t="s">
+        <v>1</v>
+      </c>
+      <c r="N5" t="s">
+        <v>13</v>
+      </c>
+      <c r="O5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P5" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>1</v>
+      </c>
+      <c r="R5" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" t="s">
+        <v>13</v>
+      </c>
+      <c r="U5" t="s">
+        <v>1</v>
+      </c>
+      <c r="V5" t="s">
+        <v>13</v>
+      </c>
+      <c r="W5" t="s">
+        <v>1</v>
+      </c>
+      <c r="X5" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>13</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>22</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>22</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>22</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>68</v>
+      </c>
+      <c r="D6">
+        <v>68</v>
+      </c>
+      <c r="E6">
+        <v>126</v>
+      </c>
+      <c r="F6">
+        <v>126</v>
+      </c>
+      <c r="G6">
+        <v>686</v>
+      </c>
+      <c r="H6">
+        <v>887</v>
+      </c>
+      <c r="I6">
+        <v>21479</v>
+      </c>
+      <c r="J6">
+        <v>599</v>
+      </c>
+      <c r="K6">
+        <v>14053</v>
+      </c>
+      <c r="L6">
+        <v>6282</v>
+      </c>
+      <c r="M6">
+        <v>601</v>
+      </c>
+      <c r="N6">
+        <v>601</v>
+      </c>
+      <c r="O6">
+        <v>31185</v>
+      </c>
+      <c r="P6">
+        <v>30673</v>
+      </c>
+      <c r="Q6">
+        <v>2625</v>
+      </c>
+      <c r="R6">
+        <v>2513</v>
+      </c>
+      <c r="S6">
+        <v>5601</v>
+      </c>
+      <c r="T6">
+        <v>4664</v>
+      </c>
+      <c r="U6">
+        <v>886</v>
+      </c>
+      <c r="V6">
+        <v>197</v>
+      </c>
+      <c r="W6">
+        <v>10344</v>
+      </c>
+      <c r="X6">
+        <v>585</v>
+      </c>
+      <c r="Y6">
+        <v>6720</v>
+      </c>
+      <c r="Z6">
+        <v>3096</v>
+      </c>
+      <c r="AA6">
+        <v>14891</v>
+      </c>
+      <c r="AB6">
+        <v>8205</v>
+      </c>
+      <c r="AC6">
+        <v>3353</v>
+      </c>
+      <c r="AD6">
+        <v>478</v>
+      </c>
+      <c r="AE6">
+        <v>1728168</v>
+      </c>
+      <c r="AF6">
+        <v>1736858</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7">
+        <v>22002</v>
+      </c>
+      <c r="D7">
+        <v>22002</v>
+      </c>
+      <c r="E7">
+        <v>132229</v>
+      </c>
+      <c r="F7">
+        <v>133961</v>
+      </c>
+      <c r="G7">
+        <v>666084</v>
+      </c>
+      <c r="H7">
+        <v>685356</v>
+      </c>
+      <c r="I7">
+        <v>2842094</v>
+      </c>
+      <c r="J7">
+        <v>4029852</v>
+      </c>
+      <c r="K7">
+        <v>83772</v>
+      </c>
+      <c r="L7">
+        <v>108404</v>
+      </c>
+      <c r="M7">
+        <v>124482</v>
+      </c>
+      <c r="N7">
+        <v>124893</v>
+      </c>
+      <c r="O7">
+        <v>183180</v>
+      </c>
+      <c r="P7">
+        <v>210106</v>
+      </c>
+      <c r="Q7">
+        <v>921505</v>
+      </c>
+      <c r="R7">
+        <v>1186549</v>
+      </c>
+      <c r="S7">
+        <v>5720932</v>
+      </c>
+      <c r="T7">
+        <v>7035724</v>
+      </c>
+      <c r="U7">
+        <v>752425</v>
+      </c>
+      <c r="V7">
+        <v>786524</v>
+      </c>
+      <c r="W7">
+        <v>94815</v>
+      </c>
+      <c r="X7">
+        <v>119849</v>
+      </c>
+      <c r="Y7">
+        <v>35321</v>
+      </c>
+      <c r="Z7">
+        <v>42006</v>
+      </c>
+      <c r="AA7">
+        <v>37093</v>
+      </c>
+      <c r="AB7">
+        <v>44506</v>
+      </c>
+      <c r="AC7">
+        <v>23547</v>
+      </c>
+      <c r="AD7">
+        <v>29100</v>
+      </c>
+      <c r="AE7">
+        <v>1476785</v>
+      </c>
+      <c r="AF7">
+        <v>1685644</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>57</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>57</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>57</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <f t="shared" ref="C8:AN8" si="0">C6+C7</f>
+        <v>22070</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>22070</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>132355</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>134087</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>666770</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>686243</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>2863573</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>4030451</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="0"/>
+        <v>97825</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="0"/>
+        <v>114686</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="0"/>
+        <v>125083</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="0"/>
+        <v>125494</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="0"/>
+        <v>214365</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="0"/>
+        <v>240779</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>924130</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="0"/>
+        <v>1189062</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="0"/>
+        <v>5726533</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="0"/>
+        <v>7040388</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="0"/>
+        <v>753311</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="0"/>
+        <v>786721</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="0"/>
+        <v>105159</v>
+      </c>
+      <c r="X8">
+        <f t="shared" si="0"/>
+        <v>120434</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="0"/>
+        <v>42041</v>
+      </c>
+      <c r="Z8">
+        <f t="shared" si="0"/>
+        <v>45102</v>
+      </c>
+      <c r="AA8">
+        <f t="shared" si="0"/>
+        <v>51984</v>
+      </c>
+      <c r="AB8">
+        <f t="shared" si="0"/>
+        <v>52711</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="0"/>
+        <v>26900</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="0"/>
+        <v>29578</v>
+      </c>
+      <c r="AE8">
+        <f t="shared" si="0"/>
+        <v>3204953</v>
+      </c>
+      <c r="AF8">
+        <f t="shared" si="0"/>
+        <v>3422502</v>
+      </c>
+      <c r="AG8" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AH8" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AI8" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AJ8" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AK8" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AL8" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AM8" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AN8" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="9" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9">
+        <f t="shared" ref="C9:AN9" si="1">IFERROR(C7/C8, 0)</f>
+        <v>0.99691889442682369</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="1"/>
+        <v>0.99691889442682369</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="1"/>
+        <v>0.99904801480865857</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="1"/>
+        <v>0.99906031158874464</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="1"/>
+        <v>0.99897115947028214</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>0.99870745493943103</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="1"/>
+        <v>0.99249923085599701</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="1"/>
+        <v>0.9998513813962755</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="1"/>
+        <v>0.85634551495016609</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="1"/>
+        <v>0.94522435170814223</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="1"/>
+        <v>0.99519519039357862</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="1"/>
+        <v>0.99521092641879294</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="1"/>
+        <v>0.85452382618431177</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="1"/>
+        <v>0.87260932224155763</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="1"/>
+        <v>0.99715949054786668</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>0.99788656941353771</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="1"/>
+        <v>0.99902192129164369</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="1"/>
+        <v>0.99933753651077184</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="1"/>
+        <v>0.99882385893741099</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="1"/>
+        <v>0.99974959356620707</v>
+      </c>
+      <c r="W9">
+        <f t="shared" si="1"/>
+        <v>0.90163466750349475</v>
+      </c>
+      <c r="X9">
+        <f t="shared" si="1"/>
+        <v>0.99514256771343645</v>
+      </c>
+      <c r="Y9">
+        <f t="shared" si="1"/>
+        <v>0.84015603815323137</v>
+      </c>
+      <c r="Z9">
+        <f t="shared" si="1"/>
+        <v>0.93135559398696288</v>
+      </c>
+      <c r="AA9">
+        <f t="shared" si="1"/>
+        <v>0.71354647583871955</v>
+      </c>
+      <c r="AB9">
+        <f t="shared" si="1"/>
+        <v>0.84433989110432361</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="1"/>
+        <v>0.87535315985130113</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="1"/>
+        <v>0.98383934005003715</v>
+      </c>
+      <c r="AE9">
+        <f t="shared" si="1"/>
+        <v>0.46078210819316229</v>
+      </c>
+      <c r="AF9">
+        <f t="shared" si="1"/>
+        <v>0.4925180467389062</v>
+      </c>
+      <c r="AG9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10">
+        <f t="shared" ref="C10:AN10" si="2">IFERROR(C6/C8, 0)</f>
+        <v>3.0811055731762575E-3</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="2"/>
+        <v>3.0811055731762575E-3</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="2"/>
+        <v>9.5198519134146798E-4</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="2"/>
+        <v>9.3968841125537897E-4</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="2"/>
+        <v>1.0288405297178937E-3</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="2"/>
+        <v>1.2925450605689238E-3</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="2"/>
+        <v>7.5007691440029641E-3</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="2"/>
+        <v>1.4861860372449633E-4</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="2"/>
+        <v>0.14365448504983389</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="2"/>
+        <v>5.477564829185777E-2</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="2"/>
+        <v>4.8048096064213361E-3</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="2"/>
+        <v>4.7890735812070699E-3</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="2"/>
+        <v>0.1454761738156882</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="2"/>
+        <v>0.1273906777584424</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>2.8405094521333578E-3</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="2"/>
+        <v>2.1134305864622701E-3</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="2"/>
+        <v>9.780787083563476E-4</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="2"/>
+        <v>6.6246348922815047E-4</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="2"/>
+        <v>1.1761410625890237E-3</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="2"/>
+        <v>2.5040643379292026E-4</v>
+      </c>
+      <c r="W10">
+        <f t="shared" si="2"/>
+        <v>9.8365332496505295E-2</v>
+      </c>
+      <c r="X10">
+        <f t="shared" si="2"/>
+        <v>4.857432286563595E-3</v>
+      </c>
+      <c r="Y10">
+        <f t="shared" si="2"/>
+        <v>0.15984396184676863</v>
+      </c>
+      <c r="Z10">
+        <f t="shared" si="2"/>
+        <v>6.8644406013037118E-2</v>
+      </c>
+      <c r="AA10">
+        <f t="shared" si="2"/>
+        <v>0.28645352416128039</v>
+      </c>
+      <c r="AB10">
+        <f t="shared" si="2"/>
+        <v>0.15566010889567641</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="2"/>
+        <v>0.12464684014869888</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="2"/>
+        <v>1.6160659949962811E-2</v>
+      </c>
+      <c r="AE10">
+        <f t="shared" si="2"/>
+        <v>0.53921789180683777</v>
+      </c>
+      <c r="AF10">
+        <f t="shared" si="2"/>
+        <v>0.5074819532610938</v>
+      </c>
+      <c r="AG10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11">
+        <v>128</v>
+      </c>
+      <c r="D11">
+        <v>128</v>
+      </c>
+      <c r="E11">
+        <v>128</v>
+      </c>
+      <c r="F11">
+        <v>128</v>
+      </c>
+      <c r="G11">
+        <v>128</v>
+      </c>
+      <c r="H11">
+        <v>128</v>
+      </c>
+      <c r="I11">
+        <v>128</v>
+      </c>
+      <c r="J11">
+        <v>128</v>
+      </c>
+      <c r="K11">
+        <v>128</v>
+      </c>
+      <c r="L11">
+        <v>128</v>
+      </c>
+      <c r="M11">
+        <v>128</v>
+      </c>
+      <c r="N11">
+        <v>128</v>
+      </c>
+      <c r="O11">
+        <v>128</v>
+      </c>
+      <c r="P11">
+        <v>128</v>
+      </c>
+      <c r="Q11">
+        <v>128</v>
+      </c>
+      <c r="R11">
+        <v>128</v>
+      </c>
+      <c r="S11">
+        <v>128</v>
+      </c>
+      <c r="T11">
+        <v>128</v>
+      </c>
+      <c r="U11">
+        <v>128</v>
+      </c>
+      <c r="V11">
+        <v>128</v>
+      </c>
+      <c r="W11">
+        <v>128</v>
+      </c>
+      <c r="X11">
+        <v>128</v>
+      </c>
+      <c r="Y11">
+        <v>128</v>
+      </c>
+      <c r="Z11">
+        <v>128</v>
+      </c>
+      <c r="AA11">
+        <v>128</v>
+      </c>
+      <c r="AB11">
+        <v>128</v>
+      </c>
+      <c r="AC11">
+        <v>128</v>
+      </c>
+      <c r="AD11">
+        <v>128</v>
+      </c>
+      <c r="AE11">
+        <v>128</v>
+      </c>
+      <c r="AF11">
+        <v>128</v>
+      </c>
+      <c r="AG11">
+        <v>128</v>
+      </c>
+      <c r="AH11">
+        <v>128</v>
+      </c>
+      <c r="AI11">
+        <v>128</v>
+      </c>
+      <c r="AJ11">
+        <v>128</v>
+      </c>
+      <c r="AK11">
+        <v>128</v>
+      </c>
+      <c r="AL11">
+        <v>128</v>
+      </c>
+      <c r="AM11">
+        <v>128</v>
+      </c>
+      <c r="AN11">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12">
+        <v>68</v>
+      </c>
+      <c r="D12">
+        <v>68</v>
+      </c>
+      <c r="E12">
+        <v>126</v>
+      </c>
+      <c r="F12">
+        <v>126</v>
+      </c>
+      <c r="G12">
+        <v>686</v>
+      </c>
+      <c r="H12">
+        <v>686</v>
+      </c>
+      <c r="I12">
+        <v>361</v>
+      </c>
+      <c r="J12">
+        <v>361</v>
+      </c>
+      <c r="K12">
+        <v>1346</v>
+      </c>
+      <c r="L12">
+        <v>1346</v>
+      </c>
+      <c r="M12">
+        <v>601</v>
+      </c>
+      <c r="N12">
+        <v>601</v>
+      </c>
+      <c r="O12">
+        <v>2294</v>
+      </c>
+      <c r="P12">
+        <v>2294</v>
+      </c>
+      <c r="Q12">
+        <v>2197</v>
+      </c>
+      <c r="R12">
+        <v>2197</v>
+      </c>
+      <c r="S12">
+        <v>2277</v>
+      </c>
+      <c r="T12">
+        <v>2277</v>
+      </c>
+      <c r="U12">
+        <v>197</v>
+      </c>
+      <c r="V12">
+        <v>197</v>
+      </c>
+      <c r="W12">
+        <v>506</v>
+      </c>
+      <c r="X12">
+        <v>506</v>
+      </c>
+      <c r="Y12">
+        <v>680</v>
+      </c>
+      <c r="Z12">
+        <v>680</v>
+      </c>
+      <c r="AA12">
+        <v>618</v>
+      </c>
+      <c r="AB12">
+        <v>618</v>
+      </c>
+      <c r="AC12">
+        <v>478</v>
+      </c>
+      <c r="AD12">
+        <v>478</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG12">
+        <v>125</v>
+      </c>
+      <c r="AH12">
+        <v>125</v>
+      </c>
+      <c r="AI12">
+        <v>188</v>
+      </c>
+      <c r="AJ12">
+        <v>188</v>
+      </c>
+      <c r="AK12">
+        <v>250</v>
+      </c>
+      <c r="AL12">
+        <v>250</v>
+      </c>
+      <c r="AM12">
+        <v>313</v>
+      </c>
+      <c r="AN12">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="13" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13">
+        <f t="shared" ref="C13:AN13" si="3">IFERROR(C12/C6, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="3"/>
+        <v>0.77339346110484786</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="3"/>
+        <v>1.6807113925229294E-2</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="3"/>
+        <v>0.60267111853088484</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="3"/>
+        <v>9.5780260442610121E-2</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="3"/>
+        <v>0.2142629735752945</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <f t="shared" si="3"/>
+        <v>7.3561006894340225E-2</v>
+      </c>
+      <c r="P13">
+        <f t="shared" si="3"/>
+        <v>7.478890229191798E-2</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="3"/>
+        <v>0.836952380952381</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="3"/>
+        <v>0.87425387982491043</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="3"/>
+        <v>0.40653454740224959</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="3"/>
+        <v>0.4882075471698113</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="3"/>
+        <v>0.22234762979683972</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="W13">
+        <f t="shared" si="3"/>
+        <v>4.8917246713070378E-2</v>
+      </c>
+      <c r="X13">
+        <f t="shared" si="3"/>
+        <v>0.86495726495726499</v>
+      </c>
+      <c r="Y13">
+        <f t="shared" si="3"/>
+        <v>0.10119047619047619</v>
+      </c>
+      <c r="Z13">
+        <f t="shared" si="3"/>
+        <v>0.21963824289405684</v>
+      </c>
+      <c r="AA13">
+        <f t="shared" si="3"/>
+        <v>4.150157813444362E-2</v>
+      </c>
+      <c r="AB13">
+        <f t="shared" si="3"/>
+        <v>7.5319926873857398E-2</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" si="3"/>
+        <v>0.14255890247539516</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AE13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>1086</v>
+      </c>
+      <c r="D14">
+        <v>1086</v>
+      </c>
+      <c r="E14">
+        <v>2003</v>
+      </c>
+      <c r="F14">
+        <v>2003</v>
+      </c>
+      <c r="G14">
+        <v>10974</v>
+      </c>
+      <c r="H14">
+        <v>10974</v>
+      </c>
+      <c r="I14">
+        <v>4562</v>
+      </c>
+      <c r="J14">
+        <v>4562</v>
+      </c>
+      <c r="K14">
+        <v>9278</v>
+      </c>
+      <c r="L14">
+        <v>9278</v>
+      </c>
+      <c r="M14">
+        <v>9604</v>
+      </c>
+      <c r="N14">
+        <v>9604</v>
+      </c>
+      <c r="O14">
+        <v>71</v>
+      </c>
+      <c r="P14">
+        <v>71</v>
+      </c>
+      <c r="Q14">
+        <v>35152</v>
+      </c>
+      <c r="R14">
+        <v>35152</v>
+      </c>
+      <c r="S14">
+        <v>36417</v>
+      </c>
+      <c r="T14">
+        <v>36417</v>
+      </c>
+      <c r="U14">
+        <v>3140</v>
+      </c>
+      <c r="V14">
+        <v>3140</v>
+      </c>
+      <c r="W14">
+        <v>8297</v>
+      </c>
+      <c r="X14">
+        <v>8297</v>
+      </c>
+      <c r="Y14">
+        <v>10879</v>
+      </c>
+      <c r="Z14">
+        <v>10879</v>
+      </c>
+      <c r="AA14">
+        <v>9877</v>
+      </c>
+      <c r="AB14">
+        <v>9877</v>
+      </c>
+      <c r="AC14">
+        <v>7716</v>
+      </c>
+      <c r="AD14">
+        <v>7716</v>
+      </c>
+      <c r="AE14">
+        <v>400727</v>
+      </c>
+      <c r="AF14">
+        <v>400727</v>
+      </c>
+      <c r="AG14">
+        <v>2000</v>
+      </c>
+      <c r="AH14">
+        <v>2000</v>
+      </c>
+      <c r="AI14">
+        <v>3000</v>
+      </c>
+      <c r="AJ14">
+        <v>3000</v>
+      </c>
+      <c r="AK14">
+        <v>4000</v>
+      </c>
+      <c r="AL14">
+        <v>4000</v>
+      </c>
+      <c r="AM14">
+        <v>5000</v>
+      </c>
+      <c r="AN14">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="15" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>1086</v>
+      </c>
+      <c r="D15">
+        <v>1086</v>
+      </c>
+      <c r="E15">
+        <v>2003</v>
+      </c>
+      <c r="F15">
+        <v>2003</v>
+      </c>
+      <c r="G15">
+        <v>10974</v>
+      </c>
+      <c r="H15">
+        <v>10974</v>
+      </c>
+      <c r="I15">
+        <v>5761</v>
+      </c>
+      <c r="J15">
+        <v>5761</v>
+      </c>
+      <c r="K15">
+        <v>21534</v>
+      </c>
+      <c r="L15">
+        <v>21534</v>
+      </c>
+      <c r="M15">
+        <v>9604</v>
+      </c>
+      <c r="N15">
+        <v>9604</v>
+      </c>
+      <c r="O15">
+        <v>36699</v>
+      </c>
+      <c r="P15">
+        <v>36699</v>
+      </c>
+      <c r="Q15">
+        <v>35152</v>
+      </c>
+      <c r="R15">
+        <v>35152</v>
+      </c>
+      <c r="S15">
+        <v>36417</v>
+      </c>
+      <c r="T15">
+        <v>36417</v>
+      </c>
+      <c r="U15">
+        <v>3140</v>
+      </c>
+      <c r="V15">
+        <v>3140</v>
+      </c>
+      <c r="W15">
+        <v>8297</v>
+      </c>
+      <c r="X15">
+        <v>8297</v>
+      </c>
+      <c r="Y15">
+        <v>10879</v>
+      </c>
+      <c r="Z15">
+        <v>10879</v>
+      </c>
+      <c r="AA15">
+        <v>9877</v>
+      </c>
+      <c r="AB15">
+        <v>9877</v>
+      </c>
+      <c r="AC15">
+        <v>7716</v>
+      </c>
+      <c r="AD15">
+        <v>7716</v>
+      </c>
+      <c r="AE15">
+        <v>400727</v>
+      </c>
+      <c r="AF15">
+        <v>400727</v>
+      </c>
+      <c r="AG15">
+        <v>2000</v>
+      </c>
+      <c r="AH15">
+        <v>2000</v>
+      </c>
+      <c r="AI15">
+        <v>3000</v>
+      </c>
+      <c r="AJ15">
+        <v>3000</v>
+      </c>
+      <c r="AK15">
+        <v>4000</v>
+      </c>
+      <c r="AL15">
+        <v>4000</v>
+      </c>
+      <c r="AM15">
+        <v>5000</v>
+      </c>
+      <c r="AN15">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="16" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>1.8712968332943301E-2</v>
+      </c>
+      <c r="D16">
+        <v>1.8712968332943301E-2</v>
+      </c>
+      <c r="E16">
+        <v>2.09079790199872E-2</v>
+      </c>
+      <c r="F16">
+        <v>2.09079790199872E-2</v>
+      </c>
+      <c r="G16">
+        <v>3.55936820230424E-3</v>
+      </c>
+      <c r="H16">
+        <v>3.55936820230424E-3</v>
+      </c>
+      <c r="I16">
+        <v>9.3714321632839104E-2</v>
+      </c>
+      <c r="J16">
+        <v>9.3714321632839104E-2</v>
+      </c>
+      <c r="K16">
+        <v>4.8376702439189201E-4</v>
+      </c>
+      <c r="L16">
+        <v>4.8376702439189201E-4</v>
+      </c>
+      <c r="M16">
+        <v>9.2440311469554599E-4</v>
+      </c>
+      <c r="N16">
+        <v>9.2440311469554599E-4</v>
+      </c>
+      <c r="O16">
+        <v>8.1568020619973106E-2</v>
+      </c>
+      <c r="P16">
+        <v>8.1568020619973106E-2</v>
+      </c>
+      <c r="Q16">
+        <v>6.1830283475066002E-4</v>
+      </c>
+      <c r="R16">
+        <v>6.1830283475066002E-4</v>
+      </c>
+      <c r="S16">
+        <v>3.27610610455435E-3</v>
+      </c>
+      <c r="T16">
+        <v>3.27610610455435E-3</v>
+      </c>
+      <c r="U16">
+        <v>5.5089455961702297E-2</v>
+      </c>
+      <c r="V16">
+        <v>5.5089455961702297E-2</v>
+      </c>
+      <c r="W16">
+        <v>1.50622726900785E-3</v>
+      </c>
+      <c r="X16">
+        <v>1.50622726900785E-3</v>
+      </c>
+      <c r="Y16">
+        <v>3.3792232823938402E-4</v>
+      </c>
+      <c r="Z16">
+        <v>3.3792232823938402E-4</v>
+      </c>
+      <c r="AA16">
+        <v>5.3273467559045498E-4</v>
+      </c>
+      <c r="AB16">
+        <v>5.3273467559045498E-4</v>
+      </c>
+      <c r="AC16">
+        <v>4.4454965693740002E-4</v>
+      </c>
+      <c r="AD16">
+        <v>4.4454965693740002E-4</v>
+      </c>
+      <c r="AE16" s="1">
+        <v>1.99302377500994E-5</v>
+      </c>
+      <c r="AF16" s="1">
+        <v>1.99302377500994E-5</v>
+      </c>
+      <c r="AG16">
+        <v>1</v>
+      </c>
+      <c r="AH16">
+        <v>1</v>
+      </c>
+      <c r="AI16">
+        <v>1</v>
+      </c>
+      <c r="AJ16">
+        <v>1</v>
+      </c>
+      <c r="AK16">
+        <v>1</v>
+      </c>
+      <c r="AL16">
+        <v>1</v>
+      </c>
+      <c r="AM16">
+        <v>1</v>
+      </c>
+      <c r="AN16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17">
+        <v>4</v>
+      </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+      <c r="F17">
+        <v>4</v>
+      </c>
+      <c r="G17">
+        <v>4</v>
+      </c>
+      <c r="H17">
+        <v>4</v>
+      </c>
+      <c r="I17">
+        <v>4</v>
+      </c>
+      <c r="J17">
+        <v>4</v>
+      </c>
+      <c r="K17">
+        <v>4</v>
+      </c>
+      <c r="L17">
+        <v>4</v>
+      </c>
+      <c r="M17">
+        <v>4</v>
+      </c>
+      <c r="N17">
+        <v>4</v>
+      </c>
+      <c r="O17">
+        <v>4</v>
+      </c>
+      <c r="P17">
+        <v>4</v>
+      </c>
+      <c r="Q17">
+        <v>4</v>
+      </c>
+      <c r="R17">
+        <v>4</v>
+      </c>
+      <c r="S17">
+        <v>4</v>
+      </c>
+      <c r="T17">
+        <v>4</v>
+      </c>
+      <c r="U17">
+        <v>4</v>
+      </c>
+      <c r="V17">
+        <v>4</v>
+      </c>
+      <c r="W17">
+        <v>4</v>
+      </c>
+      <c r="X17">
+        <v>4</v>
+      </c>
+      <c r="Y17">
+        <v>4</v>
+      </c>
+      <c r="Z17">
+        <v>4</v>
+      </c>
+      <c r="AA17">
+        <v>4</v>
+      </c>
+      <c r="AB17">
+        <v>4</v>
+      </c>
+      <c r="AC17">
+        <v>4</v>
+      </c>
+      <c r="AD17">
+        <v>4</v>
+      </c>
+      <c r="AE17">
+        <v>4</v>
+      </c>
+      <c r="AF17">
+        <v>4</v>
+      </c>
+      <c r="AG17">
+        <v>4</v>
+      </c>
+      <c r="AH17">
+        <v>4</v>
+      </c>
+      <c r="AI17">
+        <v>4</v>
+      </c>
+      <c r="AJ17">
+        <v>4</v>
+      </c>
+      <c r="AK17">
+        <v>4</v>
+      </c>
+      <c r="AL17">
+        <v>4</v>
+      </c>
+      <c r="AM17">
+        <v>4</v>
+      </c>
+      <c r="AN17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" t="s">
+        <v>30</v>
+      </c>
+      <c r="G22" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" t="s">
+        <v>31</v>
+      </c>
+      <c r="J22" t="s">
+        <v>33</v>
+      </c>
+      <c r="K22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" t="s">
+        <v>35</v>
+      </c>
+      <c r="M22" t="s">
+        <v>36</v>
+      </c>
+      <c r="N22" t="s">
+        <v>36</v>
+      </c>
+      <c r="O22" t="s">
+        <v>42</v>
+      </c>
+      <c r="P22" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>36</v>
+      </c>
+      <c r="R22" t="s">
+        <v>45</v>
+      </c>
+      <c r="S22" t="s">
+        <v>45</v>
+      </c>
+      <c r="T22" t="s">
+        <v>45</v>
+      </c>
+      <c r="U22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" t="s">
+        <v>24</v>
+      </c>
+      <c r="M23" t="s">
+        <v>37</v>
+      </c>
+      <c r="N23" t="s">
+        <v>41</v>
+      </c>
+      <c r="O23" t="s">
+        <v>40</v>
+      </c>
+      <c r="P23" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>38</v>
+      </c>
+      <c r="R23" t="s">
+        <v>46</v>
+      </c>
+      <c r="S23" t="s">
+        <v>47</v>
+      </c>
+      <c r="T23" t="s">
+        <v>48</v>
+      </c>
+      <c r="U23" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24">
+        <f>C9*100</f>
+        <v>99.691889442682367</v>
+      </c>
+      <c r="D24">
+        <f>E9*100</f>
+        <v>99.904801480865856</v>
+      </c>
+      <c r="E24">
+        <f>G9*100</f>
+        <v>99.897115947028212</v>
+      </c>
+      <c r="F24">
+        <f>I9*100</f>
+        <v>99.249923085599704</v>
+      </c>
+      <c r="G24">
+        <f>K9*100</f>
+        <v>85.634551495016609</v>
+      </c>
+      <c r="H24">
+        <f>M9*100</f>
+        <v>99.51951903935786</v>
+      </c>
+      <c r="I24">
+        <f>O9*100</f>
+        <v>85.452382618431173</v>
+      </c>
+      <c r="J24">
+        <f>Q9*100</f>
+        <v>99.715949054786662</v>
+      </c>
+      <c r="K24">
+        <f>S9*100</f>
+        <v>99.902192129164362</v>
+      </c>
+      <c r="L24">
+        <f>U9*100</f>
+        <v>99.882385893741102</v>
+      </c>
+      <c r="M24">
+        <f>W9*100</f>
+        <v>90.163466750349471</v>
+      </c>
+      <c r="N24">
+        <f>Y9*100</f>
+        <v>84.015603815323132</v>
+      </c>
+      <c r="O24">
+        <f>AA9*100</f>
+        <v>71.354647583871952</v>
+      </c>
+      <c r="P24">
+        <f>AC9*100</f>
+        <v>87.535315985130111</v>
+      </c>
+      <c r="Q24">
+        <f>AE9*100</f>
+        <v>46.078210819316226</v>
+      </c>
+      <c r="R24">
+        <f>AG9*100</f>
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <f>AI9*100</f>
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <f>AK9*100</f>
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <f>AM9*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25">
+        <f>D9*100</f>
+        <v>99.691889442682367</v>
+      </c>
+      <c r="D25">
+        <f>F9*100</f>
+        <v>99.90603115887447</v>
+      </c>
+      <c r="E25">
+        <f>H9*100</f>
+        <v>99.870745493943105</v>
+      </c>
+      <c r="F25">
+        <f>J9*100</f>
+        <v>99.985138139627551</v>
+      </c>
+      <c r="G25">
+        <f>L9*100</f>
+        <v>94.522435170814219</v>
+      </c>
+      <c r="H25">
+        <f>N9*100</f>
+        <v>99.521092641879292</v>
+      </c>
+      <c r="I25">
+        <f>P9*100</f>
+        <v>87.260932224155766</v>
+      </c>
+      <c r="J25">
+        <f>R9*100</f>
+        <v>99.788656941353764</v>
+      </c>
+      <c r="K25">
+        <f>T9*100</f>
+        <v>99.933753651077183</v>
+      </c>
+      <c r="L25">
+        <f>V9*100</f>
+        <v>99.974959356620701</v>
+      </c>
+      <c r="M25">
+        <f>X9*100</f>
+        <v>99.514256771343639</v>
+      </c>
+      <c r="N25">
+        <f>Z9*100</f>
+        <v>93.135559398696287</v>
+      </c>
+      <c r="O25">
+        <f>AB9*100</f>
+        <v>84.433989110432364</v>
+      </c>
+      <c r="P25">
+        <f>AD9*100</f>
+        <v>98.383934005003709</v>
+      </c>
+      <c r="Q25">
+        <f>AF9*100</f>
+        <v>49.251804673890618</v>
+      </c>
+      <c r="R25">
+        <f>AH9*100</f>
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <f>AJ9*100</f>
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <f>AL9*100</f>
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <f>AN9*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26">
+        <f>IFERROR(((C6-D6)/C6)*100, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <f>IFERROR(((E6-F6)/E6)*100, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <f>IFERROR(((G6-H6)/G6)*100, 0)</f>
+        <v>-29.300291545189506</v>
+      </c>
+      <c r="F26">
+        <f>IFERROR(((I6-J6)/I6)*100, 0)</f>
+        <v>97.211229573071364</v>
+      </c>
+      <c r="G26">
+        <f>IFERROR(((K6-L6)/K6)*100, 0)</f>
+        <v>55.297801181242434</v>
+      </c>
+      <c r="H26">
+        <f>IFERROR(((M6-N6)/M6)*100, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <f>IFERROR(((O6-P6)/O6)*100, 0)</f>
+        <v>1.6418149751483084</v>
+      </c>
+      <c r="J26">
+        <f>IFERROR(((Q6-R6)/Q6)*100, 0)</f>
+        <v>4.2666666666666666</v>
+      </c>
+      <c r="K26">
+        <f>IFERROR(((S6-T6)/S6)*100, 0)</f>
+        <v>16.729155507945009</v>
+      </c>
+      <c r="L26">
+        <f>IFERROR(((U6-V6)/U6)*100, 0)</f>
+        <v>77.765237020316022</v>
+      </c>
+      <c r="M26">
+        <f>IFERROR(((W6-X6)/W6)*100, 0)</f>
+        <v>94.344547563805108</v>
+      </c>
+      <c r="N26">
+        <f>IFERROR(((Y6-Z6)/Y6)*100, 0)</f>
+        <v>53.928571428571423</v>
+      </c>
+      <c r="O26">
+        <f>IFERROR(((AA6-AB6)/AA6)*100, 0)</f>
+        <v>44.899603787522665</v>
+      </c>
+      <c r="P26">
+        <f>IFERROR(((AC6-AD6)/AC6)*100, 0)</f>
+        <v>85.744109752460488</v>
+      </c>
+      <c r="Q26">
+        <f>IFERROR(((AE6-AF6)/AE6)*100, 0)</f>
+        <v>-0.50284463084607511</v>
+      </c>
+      <c r="R26">
+        <f>IFERROR(((AG6-AH6)/AG6)*100, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <f>IFERROR(((AI6-AJ6)/AI6)*100, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <f>IFERROR(((AK6-AL6)/AK6)*100, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <f>IFERROR(((AM6-AN6)/AM6)*100, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27">
+        <f>C13</f>
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <f>E13</f>
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <f>G13</f>
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <f>I13</f>
+        <v>1.6807113925229294E-2</v>
+      </c>
+      <c r="G27">
+        <f>K13</f>
+        <v>9.5780260442610121E-2</v>
+      </c>
+      <c r="H27">
+        <f>M13</f>
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <f>O13</f>
+        <v>7.3561006894340225E-2</v>
+      </c>
+      <c r="J27">
+        <f>Q13</f>
+        <v>0.836952380952381</v>
+      </c>
+      <c r="K27">
+        <f>S13</f>
+        <v>0.40653454740224959</v>
+      </c>
+      <c r="L27">
+        <f>U13</f>
+        <v>0.22234762979683972</v>
+      </c>
+      <c r="M27">
+        <f>W13</f>
+        <v>4.8917246713070378E-2</v>
+      </c>
+      <c r="N27">
+        <f>Y13</f>
+        <v>0.10119047619047619</v>
+      </c>
+      <c r="O27">
+        <f>AA13</f>
+        <v>4.150157813444362E-2</v>
+      </c>
+      <c r="P27">
+        <f>AC13</f>
+        <v>0.14255890247539516</v>
+      </c>
+      <c r="Q27">
+        <f>AE13</f>
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <f>AG13</f>
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <f>AI13</f>
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <f>AK13</f>
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <f>AM13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28">
+        <f>D13</f>
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <f>F13</f>
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <f>H13</f>
+        <v>0.77339346110484786</v>
+      </c>
+      <c r="F28">
+        <f>J13</f>
+        <v>0.60267111853088484</v>
+      </c>
+      <c r="G28">
+        <f>L13</f>
+        <v>0.2142629735752945</v>
+      </c>
+      <c r="H28">
+        <f>N13</f>
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <f>P13</f>
+        <v>7.478890229191798E-2</v>
+      </c>
+      <c r="J28">
+        <f>R13</f>
+        <v>0.87425387982491043</v>
+      </c>
+      <c r="K28">
+        <f>T13</f>
+        <v>0.4882075471698113</v>
+      </c>
+      <c r="L28">
+        <f>V13</f>
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <f>X13</f>
+        <v>0.86495726495726499</v>
+      </c>
+      <c r="N28">
+        <f>Z13</f>
+        <v>0.21963824289405684</v>
+      </c>
+      <c r="O28">
+        <f>AB13</f>
+        <v>7.5319926873857398E-2</v>
+      </c>
+      <c r="P28">
+        <f>AD13</f>
+        <v>1</v>
+      </c>
+      <c r="Q28">
+        <f>AF13</f>
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <f>AH13</f>
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <f>AJ13</f>
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <f>AL13</f>
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <f>AN13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B84" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="4"/>
+      <c r="L84" s="4"/>
+      <c r="M84" s="4"/>
+      <c r="N84" s="4"/>
+      <c r="O84" s="4"/>
+      <c r="P84" s="4"/>
+      <c r="Q84" s="4"/>
+      <c r="R84" s="4"/>
+      <c r="S84" s="4"/>
+      <c r="T84" s="4"/>
+      <c r="U84" s="4"/>
+      <c r="V84" s="4"/>
+      <c r="W84" s="4"/>
+      <c r="X84" s="4"/>
+      <c r="Y84" s="4"/>
+      <c r="Z84" s="4"/>
+      <c r="AA84" s="4"/>
+      <c r="AB84" s="4"/>
+      <c r="AC84" s="4"/>
+      <c r="AD84" s="4"/>
+      <c r="AE84" s="4"/>
+      <c r="AF84" s="4"/>
+      <c r="AG84" s="4"/>
+      <c r="AH84" s="4"/>
+      <c r="AI84" s="4"/>
+      <c r="AJ84" s="4"/>
+      <c r="AK84" s="4"/>
+      <c r="AL84" s="4"/>
+      <c r="AM84" s="4"/>
+      <c r="AN84" s="4"/>
+    </row>
+    <row r="85" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B85" t="s">
+        <v>27</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H85" s="2"/>
+      <c r="I85" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J85" s="2"/>
+      <c r="K85" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L85" s="2"/>
+      <c r="M85" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P85" s="2"/>
+      <c r="Q85" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="R85" s="2"/>
+      <c r="S85" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="T85" s="2"/>
+      <c r="U85" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="V85" s="2"/>
+      <c r="W85" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X85" s="2"/>
+      <c r="Y85" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z85" s="2"/>
+      <c r="AA85" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB85" s="2"/>
+      <c r="AC85" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD85" s="2"/>
+      <c r="AE85" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF85" s="2"/>
+      <c r="AG85" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH85" s="2"/>
+      <c r="AI85" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ85" s="2"/>
+      <c r="AK85" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL85" s="2"/>
+      <c r="AM85" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN85" s="2"/>
+    </row>
+    <row r="86" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B86" t="s">
+        <v>26</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H86" s="2"/>
+      <c r="I86" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J86" s="2"/>
+      <c r="K86" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L86" s="2"/>
+      <c r="M86" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P86" s="2"/>
+      <c r="Q86" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R86" s="2"/>
+      <c r="S86" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T86" s="2"/>
+      <c r="U86" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V86" s="2"/>
+      <c r="W86" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="X86" s="2"/>
+      <c r="Y86" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z86" s="2"/>
+      <c r="AA86" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB86" s="2"/>
+      <c r="AC86" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD86" s="2"/>
+      <c r="AE86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF86" s="2"/>
+      <c r="AG86" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AH86" s="2"/>
+      <c r="AI86" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AJ86" s="2"/>
+      <c r="AK86" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AL86" s="2"/>
+      <c r="AM86" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN86" s="2"/>
+    </row>
+    <row r="87" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B87" t="s">
+        <v>25</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1</v>
+      </c>
+      <c r="D87" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" t="s">
+        <v>1</v>
+      </c>
+      <c r="F87" t="s">
+        <v>13</v>
+      </c>
+      <c r="G87" t="s">
+        <v>1</v>
+      </c>
+      <c r="H87" t="s">
+        <v>13</v>
+      </c>
+      <c r="I87" t="s">
+        <v>1</v>
+      </c>
+      <c r="J87" t="s">
+        <v>13</v>
+      </c>
+      <c r="K87" t="s">
+        <v>1</v>
+      </c>
+      <c r="L87" t="s">
+        <v>13</v>
+      </c>
+      <c r="M87" t="s">
+        <v>1</v>
+      </c>
+      <c r="N87" t="s">
+        <v>13</v>
+      </c>
+      <c r="O87" t="s">
+        <v>1</v>
+      </c>
+      <c r="P87" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>1</v>
+      </c>
+      <c r="R87" t="s">
+        <v>13</v>
+      </c>
+      <c r="S87" t="s">
+        <v>1</v>
+      </c>
+      <c r="T87" t="s">
+        <v>13</v>
+      </c>
+      <c r="U87" t="s">
+        <v>1</v>
+      </c>
+      <c r="V87" t="s">
+        <v>13</v>
+      </c>
+      <c r="W87" t="s">
+        <v>1</v>
+      </c>
+      <c r="X87" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>13</v>
+      </c>
+      <c r="AA87" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB87" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC87" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD87" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE87" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF87" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG87" t="s">
+        <v>22</v>
+      </c>
+      <c r="AH87" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI87" t="s">
+        <v>22</v>
+      </c>
+      <c r="AJ87" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK87" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL87" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM87" t="s">
+        <v>22</v>
+      </c>
+      <c r="AN87" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B88" t="s">
+        <v>4</v>
+      </c>
+      <c r="C88">
+        <v>68</v>
+      </c>
+      <c r="D88">
+        <v>68</v>
+      </c>
+      <c r="E88">
+        <v>126</v>
+      </c>
+      <c r="F88">
+        <v>126</v>
+      </c>
+      <c r="G88">
+        <v>686</v>
+      </c>
+      <c r="H88">
+        <v>686</v>
+      </c>
+      <c r="I88">
+        <v>21479</v>
+      </c>
+      <c r="J88">
+        <v>599</v>
+      </c>
+      <c r="K88">
+        <v>14053</v>
+      </c>
+      <c r="L88">
+        <v>6282</v>
+      </c>
+      <c r="M88">
+        <v>601</v>
+      </c>
+      <c r="N88">
+        <v>601</v>
+      </c>
+      <c r="O88">
+        <v>31185</v>
+      </c>
+      <c r="P88">
+        <v>30673</v>
+      </c>
+      <c r="Q88">
+        <v>2625</v>
+      </c>
+      <c r="R88">
+        <v>2513</v>
+      </c>
+      <c r="S88">
+        <v>5601</v>
+      </c>
+      <c r="T88">
+        <v>4664</v>
+      </c>
+      <c r="U88">
+        <v>886</v>
+      </c>
+      <c r="V88">
+        <v>197</v>
+      </c>
+      <c r="W88">
+        <v>10344</v>
+      </c>
+      <c r="X88">
+        <v>585</v>
+      </c>
+      <c r="Y88">
+        <v>6720</v>
+      </c>
+      <c r="Z88">
+        <v>3096</v>
+      </c>
+      <c r="AA88">
+        <v>14891</v>
+      </c>
+      <c r="AB88">
+        <v>8205</v>
+      </c>
+      <c r="AC88">
+        <v>3353</v>
+      </c>
+      <c r="AD88">
+        <v>478</v>
+      </c>
+      <c r="AE88">
+        <v>1728168</v>
+      </c>
+      <c r="AF88">
+        <v>1728168</v>
+      </c>
+      <c r="AG88" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH88" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI88" t="s">
+        <v>57</v>
+      </c>
+      <c r="AJ88" t="s">
+        <v>57</v>
+      </c>
+      <c r="AK88" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL88" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM88" t="s">
+        <v>57</v>
+      </c>
+      <c r="AN88" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="89" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B89" t="s">
+        <v>59</v>
+      </c>
+      <c r="C89">
+        <v>22002</v>
+      </c>
+      <c r="D89">
+        <v>22002</v>
+      </c>
+      <c r="E89">
+        <v>132229</v>
+      </c>
+      <c r="F89">
+        <v>133961</v>
+      </c>
+      <c r="G89">
+        <v>666084</v>
+      </c>
+      <c r="H89">
+        <v>666084</v>
+      </c>
+      <c r="I89">
+        <v>2842094</v>
+      </c>
+      <c r="J89">
+        <v>4029852</v>
+      </c>
+      <c r="K89">
+        <v>83772</v>
+      </c>
+      <c r="L89">
+        <v>108404</v>
+      </c>
+      <c r="M89">
+        <v>124482</v>
+      </c>
+      <c r="N89">
+        <v>124893</v>
+      </c>
+      <c r="O89">
+        <v>183180</v>
+      </c>
+      <c r="P89">
+        <v>210106</v>
+      </c>
+      <c r="Q89">
+        <v>921505</v>
+      </c>
+      <c r="R89">
+        <v>1186549</v>
+      </c>
+      <c r="S89">
+        <v>5720932</v>
+      </c>
+      <c r="T89">
+        <v>7035724</v>
+      </c>
+      <c r="U89">
+        <v>752425</v>
+      </c>
+      <c r="V89">
+        <v>786524</v>
+      </c>
+      <c r="W89">
+        <v>94815</v>
+      </c>
+      <c r="X89">
+        <v>119849</v>
+      </c>
+      <c r="Y89">
+        <v>35321</v>
+      </c>
+      <c r="Z89">
+        <v>42006</v>
+      </c>
+      <c r="AA89">
+        <v>37093</v>
+      </c>
+      <c r="AB89">
+        <v>44506</v>
+      </c>
+      <c r="AC89">
+        <v>23547</v>
+      </c>
+      <c r="AD89">
+        <v>29100</v>
+      </c>
+      <c r="AE89">
+        <v>1476785</v>
+      </c>
+      <c r="AF89">
+        <v>1476785</v>
+      </c>
+      <c r="AG89" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH89" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI89" t="s">
+        <v>57</v>
+      </c>
+      <c r="AJ89" t="s">
+        <v>57</v>
+      </c>
+      <c r="AK89" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL89" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM89" t="s">
+        <v>57</v>
+      </c>
+      <c r="AN89" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="90" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B90" t="s">
+        <v>3</v>
+      </c>
+      <c r="C90">
+        <f t="shared" ref="C90:AN90" si="4">C88+C89</f>
+        <v>22070</v>
+      </c>
+      <c r="D90">
+        <f t="shared" si="4"/>
+        <v>22070</v>
+      </c>
+      <c r="E90">
+        <f t="shared" si="4"/>
+        <v>132355</v>
+      </c>
+      <c r="F90">
+        <f t="shared" si="4"/>
+        <v>134087</v>
+      </c>
+      <c r="G90">
+        <f t="shared" si="4"/>
+        <v>666770</v>
+      </c>
+      <c r="H90">
+        <f t="shared" si="4"/>
+        <v>666770</v>
+      </c>
+      <c r="I90">
+        <f t="shared" si="4"/>
+        <v>2863573</v>
+      </c>
+      <c r="J90">
+        <f t="shared" si="4"/>
+        <v>4030451</v>
+      </c>
+      <c r="K90">
+        <f t="shared" si="4"/>
+        <v>97825</v>
+      </c>
+      <c r="L90">
+        <f t="shared" si="4"/>
+        <v>114686</v>
+      </c>
+      <c r="M90">
+        <f t="shared" si="4"/>
+        <v>125083</v>
+      </c>
+      <c r="N90">
+        <f t="shared" si="4"/>
+        <v>125494</v>
+      </c>
+      <c r="O90">
+        <f t="shared" si="4"/>
+        <v>214365</v>
+      </c>
+      <c r="P90">
+        <f t="shared" si="4"/>
+        <v>240779</v>
+      </c>
+      <c r="Q90">
+        <f t="shared" si="4"/>
+        <v>924130</v>
+      </c>
+      <c r="R90">
+        <f t="shared" si="4"/>
+        <v>1189062</v>
+      </c>
+      <c r="S90">
+        <f t="shared" si="4"/>
+        <v>5726533</v>
+      </c>
+      <c r="T90">
+        <f t="shared" si="4"/>
+        <v>7040388</v>
+      </c>
+      <c r="U90">
+        <f t="shared" si="4"/>
+        <v>753311</v>
+      </c>
+      <c r="V90">
+        <f t="shared" si="4"/>
+        <v>786721</v>
+      </c>
+      <c r="W90">
+        <f t="shared" si="4"/>
+        <v>105159</v>
+      </c>
+      <c r="X90">
+        <f t="shared" si="4"/>
+        <v>120434</v>
+      </c>
+      <c r="Y90">
+        <f t="shared" si="4"/>
+        <v>42041</v>
+      </c>
+      <c r="Z90">
+        <f t="shared" si="4"/>
+        <v>45102</v>
+      </c>
+      <c r="AA90">
+        <f t="shared" si="4"/>
+        <v>51984</v>
+      </c>
+      <c r="AB90">
+        <f t="shared" si="4"/>
+        <v>52711</v>
+      </c>
+      <c r="AC90">
+        <f t="shared" si="4"/>
+        <v>26900</v>
+      </c>
+      <c r="AD90">
+        <f t="shared" si="4"/>
+        <v>29578</v>
+      </c>
+      <c r="AE90">
+        <f t="shared" si="4"/>
+        <v>3204953</v>
+      </c>
+      <c r="AF90">
+        <f t="shared" si="4"/>
+        <v>3204953</v>
+      </c>
+      <c r="AG90" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AH90" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AI90" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AJ90" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AK90" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AL90" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AM90" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AN90" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="91" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B91" t="s">
+        <v>60</v>
+      </c>
+      <c r="C91">
+        <f t="shared" ref="C91:AN91" si="5">IFERROR(C89/C90, 0)</f>
+        <v>0.99691889442682369</v>
+      </c>
+      <c r="D91">
+        <f t="shared" si="5"/>
+        <v>0.99691889442682369</v>
+      </c>
+      <c r="E91">
+        <f t="shared" si="5"/>
+        <v>0.99904801480865857</v>
+      </c>
+      <c r="F91">
+        <f t="shared" si="5"/>
+        <v>0.99906031158874464</v>
+      </c>
+      <c r="G91">
+        <f t="shared" si="5"/>
+        <v>0.99897115947028214</v>
+      </c>
+      <c r="H91">
+        <f t="shared" si="5"/>
+        <v>0.99897115947028214</v>
+      </c>
+      <c r="I91">
+        <f t="shared" si="5"/>
+        <v>0.99249923085599701</v>
+      </c>
+      <c r="J91">
+        <f t="shared" si="5"/>
+        <v>0.9998513813962755</v>
+      </c>
+      <c r="K91">
+        <f t="shared" si="5"/>
+        <v>0.85634551495016609</v>
+      </c>
+      <c r="L91">
+        <f t="shared" si="5"/>
+        <v>0.94522435170814223</v>
+      </c>
+      <c r="M91">
+        <f t="shared" si="5"/>
+        <v>0.99519519039357862</v>
+      </c>
+      <c r="N91">
+        <f t="shared" si="5"/>
+        <v>0.99521092641879294</v>
+      </c>
+      <c r="O91">
+        <f t="shared" si="5"/>
+        <v>0.85452382618431177</v>
+      </c>
+      <c r="P91">
+        <f t="shared" si="5"/>
+        <v>0.87260932224155763</v>
+      </c>
+      <c r="Q91">
+        <f t="shared" si="5"/>
+        <v>0.99715949054786668</v>
+      </c>
+      <c r="R91">
+        <f t="shared" si="5"/>
+        <v>0.99788656941353771</v>
+      </c>
+      <c r="S91">
+        <f t="shared" si="5"/>
+        <v>0.99902192129164369</v>
+      </c>
+      <c r="T91">
+        <f t="shared" si="5"/>
+        <v>0.99933753651077184</v>
+      </c>
+      <c r="U91">
+        <f t="shared" si="5"/>
+        <v>0.99882385893741099</v>
+      </c>
+      <c r="V91">
+        <f t="shared" si="5"/>
+        <v>0.99974959356620707</v>
+      </c>
+      <c r="W91">
+        <f t="shared" si="5"/>
+        <v>0.90163466750349475</v>
+      </c>
+      <c r="X91">
+        <f t="shared" si="5"/>
+        <v>0.99514256771343645</v>
+      </c>
+      <c r="Y91">
+        <f t="shared" si="5"/>
+        <v>0.84015603815323137</v>
+      </c>
+      <c r="Z91">
+        <f t="shared" si="5"/>
+        <v>0.93135559398696288</v>
+      </c>
+      <c r="AA91">
+        <f t="shared" si="5"/>
+        <v>0.71354647583871955</v>
+      </c>
+      <c r="AB91">
+        <f t="shared" si="5"/>
+        <v>0.84433989110432361</v>
+      </c>
+      <c r="AC91">
+        <f t="shared" si="5"/>
+        <v>0.87535315985130113</v>
+      </c>
+      <c r="AD91">
+        <f t="shared" si="5"/>
+        <v>0.98383934005003715</v>
+      </c>
+      <c r="AE91">
+        <f t="shared" si="5"/>
+        <v>0.46078210819316229</v>
+      </c>
+      <c r="AF91">
+        <f t="shared" si="5"/>
+        <v>0.46078210819316229</v>
+      </c>
+      <c r="AG91">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AH91">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AI91">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AJ91">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AK91">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AL91">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AM91">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AN91">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B92" t="s">
+        <v>61</v>
+      </c>
+      <c r="C92">
+        <f t="shared" ref="C92:AN92" si="6">IFERROR(C88/C90, 0)</f>
+        <v>3.0811055731762575E-3</v>
+      </c>
+      <c r="D92">
+        <f t="shared" si="6"/>
+        <v>3.0811055731762575E-3</v>
+      </c>
+      <c r="E92">
+        <f t="shared" si="6"/>
+        <v>9.5198519134146798E-4</v>
+      </c>
+      <c r="F92">
+        <f t="shared" si="6"/>
+        <v>9.3968841125537897E-4</v>
+      </c>
+      <c r="G92">
+        <f t="shared" si="6"/>
+        <v>1.0288405297178937E-3</v>
+      </c>
+      <c r="H92">
+        <f t="shared" si="6"/>
+        <v>1.0288405297178937E-3</v>
+      </c>
+      <c r="I92">
+        <f t="shared" si="6"/>
+        <v>7.5007691440029641E-3</v>
+      </c>
+      <c r="J92">
+        <f t="shared" si="6"/>
+        <v>1.4861860372449633E-4</v>
+      </c>
+      <c r="K92">
+        <f t="shared" si="6"/>
+        <v>0.14365448504983389</v>
+      </c>
+      <c r="L92">
+        <f t="shared" si="6"/>
+        <v>5.477564829185777E-2</v>
+      </c>
+      <c r="M92">
+        <f t="shared" si="6"/>
+        <v>4.8048096064213361E-3</v>
+      </c>
+      <c r="N92">
+        <f t="shared" si="6"/>
+        <v>4.7890735812070699E-3</v>
+      </c>
+      <c r="O92">
+        <f t="shared" si="6"/>
+        <v>0.1454761738156882</v>
+      </c>
+      <c r="P92">
+        <f t="shared" si="6"/>
+        <v>0.1273906777584424</v>
+      </c>
+      <c r="Q92">
+        <f t="shared" si="6"/>
+        <v>2.8405094521333578E-3</v>
+      </c>
+      <c r="R92">
+        <f t="shared" si="6"/>
+        <v>2.1134305864622701E-3</v>
+      </c>
+      <c r="S92">
+        <f t="shared" si="6"/>
+        <v>9.780787083563476E-4</v>
+      </c>
+      <c r="T92">
+        <f t="shared" si="6"/>
+        <v>6.6246348922815047E-4</v>
+      </c>
+      <c r="U92">
+        <f t="shared" si="6"/>
+        <v>1.1761410625890237E-3</v>
+      </c>
+      <c r="V92">
+        <f t="shared" si="6"/>
+        <v>2.5040643379292026E-4</v>
+      </c>
+      <c r="W92">
+        <f t="shared" si="6"/>
+        <v>9.8365332496505295E-2</v>
+      </c>
+      <c r="X92">
+        <f t="shared" si="6"/>
+        <v>4.857432286563595E-3</v>
+      </c>
+      <c r="Y92">
+        <f t="shared" si="6"/>
+        <v>0.15984396184676863</v>
+      </c>
+      <c r="Z92">
+        <f t="shared" si="6"/>
+        <v>6.8644406013037118E-2</v>
+      </c>
+      <c r="AA92">
+        <f t="shared" si="6"/>
+        <v>0.28645352416128039</v>
+      </c>
+      <c r="AB92">
+        <f t="shared" si="6"/>
+        <v>0.15566010889567641</v>
+      </c>
+      <c r="AC92">
+        <f t="shared" si="6"/>
+        <v>0.12464684014869888</v>
+      </c>
+      <c r="AD92">
+        <f t="shared" si="6"/>
+        <v>1.6160659949962811E-2</v>
+      </c>
+      <c r="AE92">
+        <f t="shared" si="6"/>
+        <v>0.53921789180683777</v>
+      </c>
+      <c r="AF92">
+        <f t="shared" si="6"/>
+        <v>0.53921789180683777</v>
+      </c>
+      <c r="AG92">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AH92">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AI92">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AJ92">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AK92">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AL92">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AM92">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN92">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B93" t="s">
+        <v>58</v>
+      </c>
+      <c r="C93">
+        <v>128</v>
+      </c>
+      <c r="D93">
+        <v>128</v>
+      </c>
+      <c r="E93">
+        <v>128</v>
+      </c>
+      <c r="F93">
+        <v>128</v>
+      </c>
+      <c r="G93">
+        <v>128</v>
+      </c>
+      <c r="H93">
+        <v>128</v>
+      </c>
+      <c r="I93">
+        <v>128</v>
+      </c>
+      <c r="J93">
+        <v>128</v>
+      </c>
+      <c r="K93">
+        <v>128</v>
+      </c>
+      <c r="L93">
+        <v>128</v>
+      </c>
+      <c r="M93">
+        <v>128</v>
+      </c>
+      <c r="N93">
+        <v>128</v>
+      </c>
+      <c r="O93">
+        <v>128</v>
+      </c>
+      <c r="P93">
+        <v>128</v>
+      </c>
+      <c r="Q93">
+        <v>128</v>
+      </c>
+      <c r="R93">
+        <v>128</v>
+      </c>
+      <c r="S93">
+        <v>128</v>
+      </c>
+      <c r="T93">
+        <v>128</v>
+      </c>
+      <c r="U93">
+        <v>128</v>
+      </c>
+      <c r="V93">
+        <v>128</v>
+      </c>
+      <c r="W93">
+        <v>128</v>
+      </c>
+      <c r="X93">
+        <v>128</v>
+      </c>
+      <c r="Y93">
+        <v>128</v>
+      </c>
+      <c r="Z93">
+        <v>128</v>
+      </c>
+      <c r="AA93">
+        <v>128</v>
+      </c>
+      <c r="AB93">
+        <v>128</v>
+      </c>
+      <c r="AC93">
+        <v>128</v>
+      </c>
+      <c r="AD93">
+        <v>128</v>
+      </c>
+      <c r="AE93">
+        <v>128</v>
+      </c>
+      <c r="AF93">
+        <v>128</v>
+      </c>
+      <c r="AG93">
+        <v>128</v>
+      </c>
+      <c r="AH93">
+        <v>128</v>
+      </c>
+      <c r="AI93">
+        <v>128</v>
+      </c>
+      <c r="AJ93">
+        <v>128</v>
+      </c>
+      <c r="AK93">
+        <v>128</v>
+      </c>
+      <c r="AL93">
+        <v>128</v>
+      </c>
+      <c r="AM93">
+        <v>128</v>
+      </c>
+      <c r="AN93">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="94" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B94" t="s">
+        <v>9</v>
+      </c>
+      <c r="C94">
+        <v>68</v>
+      </c>
+      <c r="D94">
+        <v>68</v>
+      </c>
+      <c r="E94">
+        <v>126</v>
+      </c>
+      <c r="F94">
+        <v>126</v>
+      </c>
+      <c r="G94">
+        <v>686</v>
+      </c>
+      <c r="H94">
+        <v>686</v>
+      </c>
+      <c r="I94">
+        <v>361</v>
+      </c>
+      <c r="J94">
+        <v>361</v>
+      </c>
+      <c r="K94">
+        <v>1346</v>
+      </c>
+      <c r="L94">
+        <v>1346</v>
+      </c>
+      <c r="M94">
+        <v>601</v>
+      </c>
+      <c r="N94">
+        <v>601</v>
+      </c>
+      <c r="O94">
+        <v>2294</v>
+      </c>
+      <c r="P94">
+        <v>2294</v>
+      </c>
+      <c r="Q94">
+        <v>2197</v>
+      </c>
+      <c r="R94">
+        <v>2197</v>
+      </c>
+      <c r="S94">
+        <v>2277</v>
+      </c>
+      <c r="T94">
+        <v>2277</v>
+      </c>
+      <c r="U94">
+        <v>197</v>
+      </c>
+      <c r="V94">
+        <v>197</v>
+      </c>
+      <c r="W94">
+        <v>506</v>
+      </c>
+      <c r="X94">
+        <v>506</v>
+      </c>
+      <c r="Y94">
+        <v>680</v>
+      </c>
+      <c r="Z94">
+        <v>680</v>
+      </c>
+      <c r="AA94">
+        <v>618</v>
+      </c>
+      <c r="AB94">
+        <v>618</v>
+      </c>
+      <c r="AC94">
+        <v>478</v>
+      </c>
+      <c r="AD94">
+        <v>478</v>
+      </c>
+      <c r="AE94" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF94" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG94">
+        <v>125</v>
+      </c>
+      <c r="AH94">
+        <v>125</v>
+      </c>
+      <c r="AI94">
+        <v>188</v>
+      </c>
+      <c r="AJ94">
+        <v>188</v>
+      </c>
+      <c r="AK94">
+        <v>250</v>
+      </c>
+      <c r="AL94">
+        <v>250</v>
+      </c>
+      <c r="AM94">
+        <v>313</v>
+      </c>
+      <c r="AN94">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="95" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B95" t="s">
+        <v>8</v>
+      </c>
+      <c r="C95">
+        <f t="shared" ref="C95:AN95" si="7">IFERROR(C94/C88, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="D95">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="E95">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F95">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="G95">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="H95">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="I95">
+        <f t="shared" si="7"/>
+        <v>1.6807113925229294E-2</v>
+      </c>
+      <c r="J95">
+        <f t="shared" si="7"/>
+        <v>0.60267111853088484</v>
+      </c>
+      <c r="K95">
+        <f t="shared" si="7"/>
+        <v>9.5780260442610121E-2</v>
+      </c>
+      <c r="L95">
+        <f t="shared" si="7"/>
+        <v>0.2142629735752945</v>
+      </c>
+      <c r="M95">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="N95">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="O95">
+        <f t="shared" si="7"/>
+        <v>7.3561006894340225E-2</v>
+      </c>
+      <c r="P95">
+        <f t="shared" si="7"/>
+        <v>7.478890229191798E-2</v>
+      </c>
+      <c r="Q95">
+        <f t="shared" si="7"/>
+        <v>0.836952380952381</v>
+      </c>
+      <c r="R95">
+        <f t="shared" si="7"/>
+        <v>0.87425387982491043</v>
+      </c>
+      <c r="S95">
+        <f t="shared" si="7"/>
+        <v>0.40653454740224959</v>
+      </c>
+      <c r="T95">
+        <f t="shared" si="7"/>
+        <v>0.4882075471698113</v>
+      </c>
+      <c r="U95">
+        <f t="shared" si="7"/>
+        <v>0.22234762979683972</v>
+      </c>
+      <c r="V95">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="W95">
+        <f t="shared" si="7"/>
+        <v>4.8917246713070378E-2</v>
+      </c>
+      <c r="X95">
+        <f t="shared" si="7"/>
+        <v>0.86495726495726499</v>
+      </c>
+      <c r="Y95">
+        <f t="shared" si="7"/>
+        <v>0.10119047619047619</v>
+      </c>
+      <c r="Z95">
+        <f t="shared" si="7"/>
+        <v>0.21963824289405684</v>
+      </c>
+      <c r="AA95">
+        <f t="shared" si="7"/>
+        <v>4.150157813444362E-2</v>
+      </c>
+      <c r="AB95">
+        <f t="shared" si="7"/>
+        <v>7.5319926873857398E-2</v>
+      </c>
+      <c r="AC95">
+        <f t="shared" si="7"/>
+        <v>0.14255890247539516</v>
+      </c>
+      <c r="AD95">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="AE95">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AF95">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AG95">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AH95">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AI95">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AJ95">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AK95">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AL95">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AM95">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AN95">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B96" t="s">
+        <v>5</v>
+      </c>
+      <c r="C96">
+        <v>1086</v>
+      </c>
+      <c r="D96">
+        <v>1086</v>
+      </c>
+      <c r="E96">
+        <v>2003</v>
+      </c>
+      <c r="F96">
+        <v>2003</v>
+      </c>
+      <c r="G96">
+        <v>10974</v>
+      </c>
+      <c r="H96">
+        <v>10974</v>
+      </c>
+      <c r="I96">
+        <v>4562</v>
+      </c>
+      <c r="J96">
+        <v>4562</v>
+      </c>
+      <c r="K96">
+        <v>9278</v>
+      </c>
+      <c r="L96">
+        <v>9278</v>
+      </c>
+      <c r="M96">
+        <v>9604</v>
+      </c>
+      <c r="N96">
+        <v>9604</v>
+      </c>
+      <c r="O96">
+        <v>71</v>
+      </c>
+      <c r="P96">
+        <v>71</v>
+      </c>
+      <c r="Q96">
+        <v>35152</v>
+      </c>
+      <c r="R96">
+        <v>35152</v>
+      </c>
+      <c r="S96">
+        <v>36417</v>
+      </c>
+      <c r="T96">
+        <v>36417</v>
+      </c>
+      <c r="U96">
+        <v>3140</v>
+      </c>
+      <c r="V96">
+        <v>3140</v>
+      </c>
+      <c r="W96">
+        <v>8297</v>
+      </c>
+      <c r="X96">
+        <v>8297</v>
+      </c>
+      <c r="Y96">
+        <v>10879</v>
+      </c>
+      <c r="Z96">
+        <v>10879</v>
+      </c>
+      <c r="AA96">
+        <v>9877</v>
+      </c>
+      <c r="AB96">
+        <v>9877</v>
+      </c>
+      <c r="AC96">
+        <v>7716</v>
+      </c>
+      <c r="AD96">
+        <v>7716</v>
+      </c>
+      <c r="AE96">
+        <v>400727</v>
+      </c>
+      <c r="AF96">
+        <v>400727</v>
+      </c>
+      <c r="AG96">
+        <v>2000</v>
+      </c>
+      <c r="AH96">
+        <v>2000</v>
+      </c>
+      <c r="AI96">
+        <v>3000</v>
+      </c>
+      <c r="AJ96">
+        <v>3000</v>
+      </c>
+      <c r="AK96">
+        <v>4000</v>
+      </c>
+      <c r="AL96">
+        <v>4000</v>
+      </c>
+      <c r="AM96">
+        <v>5000</v>
+      </c>
+      <c r="AN96">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="97" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B97" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97">
+        <v>1086</v>
+      </c>
+      <c r="D97">
+        <v>1086</v>
+      </c>
+      <c r="E97">
+        <v>2003</v>
+      </c>
+      <c r="F97">
+        <v>2003</v>
+      </c>
+      <c r="G97">
+        <v>10974</v>
+      </c>
+      <c r="H97">
+        <v>10974</v>
+      </c>
+      <c r="I97">
+        <v>5761</v>
+      </c>
+      <c r="J97">
+        <v>5761</v>
+      </c>
+      <c r="K97">
+        <v>21534</v>
+      </c>
+      <c r="L97">
+        <v>21534</v>
+      </c>
+      <c r="M97">
+        <v>9604</v>
+      </c>
+      <c r="N97">
+        <v>9604</v>
+      </c>
+      <c r="O97">
+        <v>36699</v>
+      </c>
+      <c r="P97">
+        <v>36699</v>
+      </c>
+      <c r="Q97">
+        <v>35152</v>
+      </c>
+      <c r="R97">
+        <v>35152</v>
+      </c>
+      <c r="S97">
+        <v>36417</v>
+      </c>
+      <c r="T97">
+        <v>36417</v>
+      </c>
+      <c r="U97">
+        <v>3140</v>
+      </c>
+      <c r="V97">
+        <v>3140</v>
+      </c>
+      <c r="W97">
+        <v>8297</v>
+      </c>
+      <c r="X97">
+        <v>8297</v>
+      </c>
+      <c r="Y97">
+        <v>10879</v>
+      </c>
+      <c r="Z97">
+        <v>10879</v>
+      </c>
+      <c r="AA97">
+        <v>9877</v>
+      </c>
+      <c r="AB97">
+        <v>9877</v>
+      </c>
+      <c r="AC97">
+        <v>7716</v>
+      </c>
+      <c r="AD97">
+        <v>7716</v>
+      </c>
+      <c r="AE97">
+        <v>400727</v>
+      </c>
+      <c r="AF97">
+        <v>400727</v>
+      </c>
+      <c r="AG97">
+        <v>2000</v>
+      </c>
+      <c r="AH97">
+        <v>2000</v>
+      </c>
+      <c r="AI97">
+        <v>3000</v>
+      </c>
+      <c r="AJ97">
+        <v>3000</v>
+      </c>
+      <c r="AK97">
+        <v>4000</v>
+      </c>
+      <c r="AL97">
+        <v>4000</v>
+      </c>
+      <c r="AM97">
+        <v>5000</v>
+      </c>
+      <c r="AN97">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="98" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B98" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98">
+        <v>1.8712968332943301E-2</v>
+      </c>
+      <c r="D98">
+        <v>1.8712968332943301E-2</v>
+      </c>
+      <c r="E98">
+        <v>2.09079790199872E-2</v>
+      </c>
+      <c r="F98">
+        <v>2.09079790199872E-2</v>
+      </c>
+      <c r="G98">
+        <v>3.55936820230424E-3</v>
+      </c>
+      <c r="H98">
+        <v>3.55936820230424E-3</v>
+      </c>
+      <c r="I98">
+        <v>9.3714321632839104E-2</v>
+      </c>
+      <c r="J98">
+        <v>9.3714321632839104E-2</v>
+      </c>
+      <c r="K98">
+        <v>4.8376702439189201E-4</v>
+      </c>
+      <c r="L98">
+        <v>4.8376702439189201E-4</v>
+      </c>
+      <c r="M98">
+        <v>9.2440311469554599E-4</v>
+      </c>
+      <c r="N98">
+        <v>9.2440311469554599E-4</v>
+      </c>
+      <c r="O98">
+        <v>8.1568020619973106E-2</v>
+      </c>
+      <c r="P98">
+        <v>8.1568020619973106E-2</v>
+      </c>
+      <c r="Q98">
+        <v>6.1830283475066002E-4</v>
+      </c>
+      <c r="R98">
+        <v>6.1830283475066002E-4</v>
+      </c>
+      <c r="S98">
+        <v>3.27610610455435E-3</v>
+      </c>
+      <c r="T98">
+        <v>3.27610610455435E-3</v>
+      </c>
+      <c r="U98">
+        <v>5.5089455961702297E-2</v>
+      </c>
+      <c r="V98">
+        <v>5.5089455961702297E-2</v>
+      </c>
+      <c r="W98">
+        <v>1.50622726900785E-3</v>
+      </c>
+      <c r="X98">
+        <v>1.50622726900785E-3</v>
+      </c>
+      <c r="Y98">
+        <v>3.3792232823938402E-4</v>
+      </c>
+      <c r="Z98">
+        <v>3.3792232823938402E-4</v>
+      </c>
+      <c r="AA98">
+        <v>5.3273467559045498E-4</v>
+      </c>
+      <c r="AB98">
+        <v>5.3273467559045498E-4</v>
+      </c>
+      <c r="AC98">
+        <v>4.4454965693740002E-4</v>
+      </c>
+      <c r="AD98">
+        <v>4.4454965693740002E-4</v>
+      </c>
+      <c r="AE98" s="1">
+        <v>1.99302377500994E-5</v>
+      </c>
+      <c r="AF98" s="1">
+        <v>1.99302377500994E-5</v>
+      </c>
+      <c r="AG98">
+        <v>1</v>
+      </c>
+      <c r="AH98">
+        <v>1</v>
+      </c>
+      <c r="AI98">
+        <v>1</v>
+      </c>
+      <c r="AJ98">
+        <v>1</v>
+      </c>
+      <c r="AK98">
+        <v>1</v>
+      </c>
+      <c r="AL98">
+        <v>1</v>
+      </c>
+      <c r="AM98">
+        <v>1</v>
+      </c>
+      <c r="AN98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B99" t="s">
+        <v>56</v>
+      </c>
+      <c r="C99">
+        <v>4</v>
+      </c>
+      <c r="D99">
+        <v>4</v>
+      </c>
+      <c r="E99">
+        <v>4</v>
+      </c>
+      <c r="F99">
+        <v>4</v>
+      </c>
+      <c r="G99">
+        <v>4</v>
+      </c>
+      <c r="H99">
+        <v>4</v>
+      </c>
+      <c r="I99">
+        <v>4</v>
+      </c>
+      <c r="J99">
+        <v>4</v>
+      </c>
+      <c r="K99">
+        <v>4</v>
+      </c>
+      <c r="L99">
+        <v>4</v>
+      </c>
+      <c r="M99">
+        <v>4</v>
+      </c>
+      <c r="N99">
+        <v>4</v>
+      </c>
+      <c r="O99">
+        <v>4</v>
+      </c>
+      <c r="P99">
+        <v>4</v>
+      </c>
+      <c r="Q99">
+        <v>4</v>
+      </c>
+      <c r="R99">
+        <v>4</v>
+      </c>
+      <c r="S99">
+        <v>4</v>
+      </c>
+      <c r="T99">
+        <v>4</v>
+      </c>
+      <c r="U99">
+        <v>4</v>
+      </c>
+      <c r="V99">
+        <v>4</v>
+      </c>
+      <c r="W99">
+        <v>4</v>
+      </c>
+      <c r="X99">
+        <v>4</v>
+      </c>
+      <c r="Y99">
+        <v>4</v>
+      </c>
+      <c r="Z99">
+        <v>4</v>
+      </c>
+      <c r="AA99">
+        <v>4</v>
+      </c>
+      <c r="AB99">
+        <v>4</v>
+      </c>
+      <c r="AC99">
+        <v>4</v>
+      </c>
+      <c r="AD99">
+        <v>4</v>
+      </c>
+      <c r="AE99">
+        <v>4</v>
+      </c>
+      <c r="AF99">
+        <v>4</v>
+      </c>
+      <c r="AG99">
+        <v>4</v>
+      </c>
+      <c r="AH99">
+        <v>4</v>
+      </c>
+      <c r="AI99">
+        <v>4</v>
+      </c>
+      <c r="AJ99">
+        <v>4</v>
+      </c>
+      <c r="AK99">
+        <v>4</v>
+      </c>
+      <c r="AL99">
+        <v>4</v>
+      </c>
+      <c r="AM99">
+        <v>4</v>
+      </c>
+      <c r="AN99">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B104" t="s">
+        <v>27</v>
+      </c>
+      <c r="C104" t="s">
+        <v>28</v>
+      </c>
+      <c r="D104" t="s">
+        <v>29</v>
+      </c>
+      <c r="E104" t="s">
+        <v>28</v>
+      </c>
+      <c r="F104" t="s">
+        <v>30</v>
+      </c>
+      <c r="G104" t="s">
+        <v>31</v>
+      </c>
+      <c r="H104" t="s">
+        <v>32</v>
+      </c>
+      <c r="I104" t="s">
+        <v>31</v>
+      </c>
+      <c r="J104" t="s">
+        <v>33</v>
+      </c>
+      <c r="K104" t="s">
+        <v>34</v>
+      </c>
+      <c r="L104" t="s">
+        <v>35</v>
+      </c>
+      <c r="M104" t="s">
+        <v>36</v>
+      </c>
+      <c r="N104" t="s">
+        <v>36</v>
+      </c>
+      <c r="O104" t="s">
+        <v>42</v>
+      </c>
+      <c r="P104" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>36</v>
+      </c>
+      <c r="R104" t="s">
+        <v>45</v>
+      </c>
+      <c r="S104" t="s">
+        <v>45</v>
+      </c>
+      <c r="T104" t="s">
+        <v>45</v>
+      </c>
+      <c r="U104" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="105" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B105" t="s">
+        <v>26</v>
+      </c>
+      <c r="C105" t="s">
+        <v>14</v>
+      </c>
+      <c r="D105" t="s">
+        <v>15</v>
+      </c>
+      <c r="E105" t="s">
+        <v>16</v>
+      </c>
+      <c r="F105" t="s">
+        <v>17</v>
+      </c>
+      <c r="G105" t="s">
+        <v>18</v>
+      </c>
+      <c r="H105" t="s">
+        <v>19</v>
+      </c>
+      <c r="I105" t="s">
+        <v>20</v>
+      </c>
+      <c r="J105" t="s">
+        <v>21</v>
+      </c>
+      <c r="K105" t="s">
+        <v>23</v>
+      </c>
+      <c r="L105" t="s">
+        <v>24</v>
+      </c>
+      <c r="M105" t="s">
+        <v>37</v>
+      </c>
+      <c r="N105" t="s">
+        <v>41</v>
+      </c>
+      <c r="O105" t="s">
+        <v>40</v>
+      </c>
+      <c r="P105" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>38</v>
+      </c>
+      <c r="R105" t="s">
+        <v>46</v>
+      </c>
+      <c r="S105" t="s">
+        <v>47</v>
+      </c>
+      <c r="T105" t="s">
+        <v>48</v>
+      </c>
+      <c r="U105" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="106" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B106" t="s">
+        <v>50</v>
+      </c>
+      <c r="C106">
+        <f>C91*100</f>
+        <v>99.691889442682367</v>
+      </c>
+      <c r="D106">
+        <f>E91*100</f>
+        <v>99.904801480865856</v>
+      </c>
+      <c r="E106">
+        <f>G91*100</f>
+        <v>99.897115947028212</v>
+      </c>
+      <c r="F106">
+        <f>I91*100</f>
+        <v>99.249923085599704</v>
+      </c>
+      <c r="G106">
+        <f>K91*100</f>
+        <v>85.634551495016609</v>
+      </c>
+      <c r="H106">
+        <f>M91*100</f>
+        <v>99.51951903935786</v>
+      </c>
+      <c r="I106">
+        <f>O91*100</f>
+        <v>85.452382618431173</v>
+      </c>
+      <c r="J106">
+        <f>Q91*100</f>
+        <v>99.715949054786662</v>
+      </c>
+      <c r="K106">
+        <f>S91*100</f>
+        <v>99.902192129164362</v>
+      </c>
+      <c r="L106">
+        <f>U91*100</f>
+        <v>99.882385893741102</v>
+      </c>
+      <c r="M106">
+        <f>W91*100</f>
+        <v>90.163466750349471</v>
+      </c>
+      <c r="N106">
+        <f>Y91*100</f>
+        <v>84.015603815323132</v>
+      </c>
+      <c r="O106">
+        <f>AA91*100</f>
+        <v>71.354647583871952</v>
+      </c>
+      <c r="P106">
+        <f>AC91*100</f>
+        <v>87.535315985130111</v>
+      </c>
+      <c r="Q106">
+        <f>AE91*100</f>
+        <v>46.078210819316226</v>
+      </c>
+      <c r="R106">
+        <f>AG91*100</f>
+        <v>0</v>
+      </c>
+      <c r="S106">
+        <f>AI91*100</f>
+        <v>0</v>
+      </c>
+      <c r="T106">
+        <f>AK91*100</f>
+        <v>0</v>
+      </c>
+      <c r="U106">
+        <f>AM91*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B107" t="s">
+        <v>51</v>
+      </c>
+      <c r="C107">
+        <f>D91*100</f>
+        <v>99.691889442682367</v>
+      </c>
+      <c r="D107">
+        <f>F91*100</f>
+        <v>99.90603115887447</v>
+      </c>
+      <c r="E107">
+        <f>H91*100</f>
+        <v>99.897115947028212</v>
+      </c>
+      <c r="F107">
+        <f>J91*100</f>
+        <v>99.985138139627551</v>
+      </c>
+      <c r="G107">
+        <f>L91*100</f>
+        <v>94.522435170814219</v>
+      </c>
+      <c r="H107">
+        <f>N91*100</f>
+        <v>99.521092641879292</v>
+      </c>
+      <c r="I107">
+        <f>P91*100</f>
+        <v>87.260932224155766</v>
+      </c>
+      <c r="J107">
+        <f>R91*100</f>
+        <v>99.788656941353764</v>
+      </c>
+      <c r="K107">
+        <f>T91*100</f>
+        <v>99.933753651077183</v>
+      </c>
+      <c r="L107">
+        <f>V91*100</f>
+        <v>99.974959356620701</v>
+      </c>
+      <c r="M107">
+        <f>X91*100</f>
+        <v>99.514256771343639</v>
+      </c>
+      <c r="N107">
+        <f>Z91*100</f>
+        <v>93.135559398696287</v>
+      </c>
+      <c r="O107">
+        <f>AB91*100</f>
+        <v>84.433989110432364</v>
+      </c>
+      <c r="P107">
+        <f>AD91*100</f>
+        <v>98.383934005003709</v>
+      </c>
+      <c r="Q107">
+        <f>AF91*100</f>
+        <v>46.078210819316226</v>
+      </c>
+      <c r="R107">
+        <f>AH91*100</f>
+        <v>0</v>
+      </c>
+      <c r="S107">
+        <f>AJ91*100</f>
+        <v>0</v>
+      </c>
+      <c r="T107">
+        <f>AL91*100</f>
+        <v>0</v>
+      </c>
+      <c r="U107">
+        <f>AN91*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B108" t="s">
+        <v>52</v>
+      </c>
+      <c r="C108">
+        <f>IFERROR(((C88-D88)/C88)*100, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D108">
+        <f>IFERROR(((E88-F88)/E88)*100, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="E108">
+        <f>IFERROR(((G88-H88)/G88)*100, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="F108">
+        <f>IFERROR(((I88-J88)/I88)*100, 0)</f>
+        <v>97.211229573071364</v>
+      </c>
+      <c r="G108">
+        <f>IFERROR(((K88-L88)/K88)*100, 0)</f>
+        <v>55.297801181242434</v>
+      </c>
+      <c r="H108">
+        <f>IFERROR(((M88-N88)/M88)*100, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="I108">
+        <f>IFERROR(((O88-P88)/O88)*100, 0)</f>
+        <v>1.6418149751483084</v>
+      </c>
+      <c r="J108">
+        <f>IFERROR(((Q88-R88)/Q88)*100, 0)</f>
+        <v>4.2666666666666666</v>
+      </c>
+      <c r="K108">
+        <f>IFERROR(((S88-T88)/S88)*100, 0)</f>
+        <v>16.729155507945009</v>
+      </c>
+      <c r="L108">
+        <f>IFERROR(((U88-V88)/U88)*100, 0)</f>
+        <v>77.765237020316022</v>
+      </c>
+      <c r="M108">
+        <f>IFERROR(((W88-X88)/W88)*100, 0)</f>
+        <v>94.344547563805108</v>
+      </c>
+      <c r="N108">
+        <f>IFERROR(((Y88-Z88)/Y88)*100, 0)</f>
+        <v>53.928571428571423</v>
+      </c>
+      <c r="O108">
+        <f>IFERROR(((AA88-AB88)/AA88)*100, 0)</f>
+        <v>44.899603787522665</v>
+      </c>
+      <c r="P108">
+        <f>IFERROR(((AC88-AD88)/AC88)*100, 0)</f>
+        <v>85.744109752460488</v>
+      </c>
+      <c r="Q108">
+        <f>IFERROR(((AE88-AF88)/AE88)*100, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="R108">
+        <f>IFERROR(((AG88-AH88)/AG88)*100, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="S108">
+        <f>IFERROR(((AI88-AJ88)/AI88)*100, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="T108">
+        <f>IFERROR(((AK88-AL88)/AK88)*100, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="U108">
+        <f>IFERROR(((AM88-AN88)/AM88)*100, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B109" t="s">
+        <v>62</v>
+      </c>
+      <c r="C109">
+        <f>C95</f>
+        <v>1</v>
+      </c>
+      <c r="D109">
+        <f>E95</f>
+        <v>1</v>
+      </c>
+      <c r="E109">
+        <f>G95</f>
+        <v>1</v>
+      </c>
+      <c r="F109">
+        <f>I95</f>
+        <v>1.6807113925229294E-2</v>
+      </c>
+      <c r="G109">
+        <f>K95</f>
+        <v>9.5780260442610121E-2</v>
+      </c>
+      <c r="H109">
+        <f>M95</f>
+        <v>1</v>
+      </c>
+      <c r="I109">
+        <f>O95</f>
+        <v>7.3561006894340225E-2</v>
+      </c>
+      <c r="J109">
+        <f>Q95</f>
+        <v>0.836952380952381</v>
+      </c>
+      <c r="K109">
+        <f>S95</f>
+        <v>0.40653454740224959</v>
+      </c>
+      <c r="L109">
+        <f>U95</f>
+        <v>0.22234762979683972</v>
+      </c>
+      <c r="M109">
+        <f>W95</f>
+        <v>4.8917246713070378E-2</v>
+      </c>
+      <c r="N109">
+        <f>Y95</f>
+        <v>0.10119047619047619</v>
+      </c>
+      <c r="O109">
+        <f>AA95</f>
+        <v>4.150157813444362E-2</v>
+      </c>
+      <c r="P109">
+        <f>AC95</f>
+        <v>0.14255890247539516</v>
+      </c>
+      <c r="Q109">
+        <f>AE95</f>
+        <v>0</v>
+      </c>
+      <c r="R109">
+        <f>AG95</f>
+        <v>0</v>
+      </c>
+      <c r="S109">
+        <f>AI95</f>
+        <v>0</v>
+      </c>
+      <c r="T109">
+        <f>AK95</f>
+        <v>0</v>
+      </c>
+      <c r="U109">
+        <f>AM95</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B110" t="s">
+        <v>63</v>
+      </c>
+      <c r="C110">
+        <f>D95</f>
+        <v>1</v>
+      </c>
+      <c r="D110">
+        <f>F95</f>
+        <v>1</v>
+      </c>
+      <c r="E110">
+        <f>H95</f>
+        <v>1</v>
+      </c>
+      <c r="F110">
+        <f>J95</f>
+        <v>0.60267111853088484</v>
+      </c>
+      <c r="G110">
+        <f>L95</f>
+        <v>0.2142629735752945</v>
+      </c>
+      <c r="H110">
+        <f>N95</f>
+        <v>1</v>
+      </c>
+      <c r="I110">
+        <f>P95</f>
+        <v>7.478890229191798E-2</v>
+      </c>
+      <c r="J110">
+        <f>R95</f>
+        <v>0.87425387982491043</v>
+      </c>
+      <c r="K110">
+        <f>T95</f>
+        <v>0.4882075471698113</v>
+      </c>
+      <c r="L110">
+        <f>V95</f>
+        <v>1</v>
+      </c>
+      <c r="M110">
+        <f>X95</f>
+        <v>0.86495726495726499</v>
+      </c>
+      <c r="N110">
+        <f>Z95</f>
+        <v>0.21963824289405684</v>
+      </c>
+      <c r="O110">
+        <f>AB95</f>
+        <v>7.5319926873857398E-2</v>
+      </c>
+      <c r="P110">
+        <f>AD95</f>
+        <v>1</v>
+      </c>
+      <c r="Q110">
+        <f>AF95</f>
+        <v>0</v>
+      </c>
+      <c r="R110">
+        <f>AH95</f>
+        <v>0</v>
+      </c>
+      <c r="S110">
+        <f>AJ95</f>
+        <v>0</v>
+      </c>
+      <c r="T110">
+        <f>AL95</f>
+        <v>0</v>
+      </c>
+      <c r="U110">
+        <f>AN95</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="78">
+    <mergeCell ref="AK86:AL86"/>
+    <mergeCell ref="AM86:AN86"/>
+    <mergeCell ref="AA86:AB86"/>
+    <mergeCell ref="AC86:AD86"/>
+    <mergeCell ref="AE86:AF86"/>
+    <mergeCell ref="AG86:AH86"/>
+    <mergeCell ref="AI86:AJ86"/>
+    <mergeCell ref="AG85:AH85"/>
+    <mergeCell ref="AI85:AJ85"/>
+    <mergeCell ref="AK85:AL85"/>
+    <mergeCell ref="AM85:AN85"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="E86:F86"/>
+    <mergeCell ref="G86:H86"/>
+    <mergeCell ref="I86:J86"/>
+    <mergeCell ref="K86:L86"/>
+    <mergeCell ref="M86:N86"/>
+    <mergeCell ref="O86:P86"/>
+    <mergeCell ref="Q86:R86"/>
+    <mergeCell ref="S86:T86"/>
+    <mergeCell ref="U86:V86"/>
+    <mergeCell ref="W86:X86"/>
+    <mergeCell ref="Y86:Z86"/>
+    <mergeCell ref="B84:AN84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="E85:F85"/>
+    <mergeCell ref="G85:H85"/>
+    <mergeCell ref="I85:J85"/>
+    <mergeCell ref="K85:L85"/>
+    <mergeCell ref="M85:N85"/>
+    <mergeCell ref="O85:P85"/>
+    <mergeCell ref="Q85:R85"/>
+    <mergeCell ref="S85:T85"/>
+    <mergeCell ref="U85:V85"/>
+    <mergeCell ref="W85:X85"/>
+    <mergeCell ref="Y85:Z85"/>
+    <mergeCell ref="AA85:AB85"/>
+    <mergeCell ref="AC85:AD85"/>
+    <mergeCell ref="AE85:AF85"/>
+    <mergeCell ref="B2:AN2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="W3:X3"/>
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AG3:AH3"/>
+    <mergeCell ref="AI3:AJ3"/>
+    <mergeCell ref="AK3:AL3"/>
+    <mergeCell ref="AM3:AN3"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="U4:V4"/>
+    <mergeCell ref="W4:X4"/>
+    <mergeCell ref="AM4:AN4"/>
+    <mergeCell ref="AA4:AB4"/>
+    <mergeCell ref="AC4:AD4"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AG4:AH4"/>
+    <mergeCell ref="AI4:AJ4"/>
+    <mergeCell ref="AK4:AL4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/docs/cacheBandit_metrics.xlsx
+++ b/docs/cacheBandit_metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91988\Documents\Amruth\Files\Git\cacheBandit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{909F447A-5CC2-4576-836F-4ACFE0684599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675385A6-149D-4854-8554-E40826A3A93C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C4CDEA3B-1686-49FD-8414-9D1FD93CDC23}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="80">
   <si>
     <t>Thread Count</t>
   </si>
@@ -222,6 +222,51 @@
   <si>
     <t>DYNAMIC: MULTI-WARP Virtual Sets</t>
   </si>
+  <si>
+    <t>airfoil1</t>
+  </si>
+  <si>
+    <t>2D/3D problem</t>
+  </si>
+  <si>
+    <t>diag</t>
+  </si>
+  <si>
+    <t>shock-9</t>
+  </si>
+  <si>
+    <t>DYNAMIC: MULTI-WARP Virtual Sets | Diagonal Matrix Study</t>
+  </si>
+  <si>
+    <t>Chem97ZtZ</t>
+  </si>
+  <si>
+    <t>Statistical/Mathematical</t>
+  </si>
+  <si>
+    <t>crack</t>
+  </si>
+  <si>
+    <t>big_dual</t>
+  </si>
+  <si>
+    <t>Remarks:</t>
+  </si>
+  <si>
+    <t>sinc15</t>
+  </si>
+  <si>
+    <t>Materials</t>
+  </si>
+  <si>
+    <t>Weighted Pearson Correlation</t>
+  </si>
+  <si>
+    <t>Diagonal matrices, i.e., matrices which exhibit strong (weighted) pearson corelation between its x (rows) and y (cols) values. Exhibit 0 or in certain cases negative DRAM access reduction as shown below</t>
+  </si>
+  <si>
+    <t>Correlation positive lim</t>
+  </si>
 </sst>
 </file>
 
@@ -236,7 +281,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -255,6 +300,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -268,9 +325,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -280,6 +340,11 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2952,7 +3017,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -3015,7 +3080,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="75000"/>
@@ -3060,9 +3125,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$C$23:$Q$23</c:f>
+              <c:f>Sheet1!$C$23:$R$23</c:f>
               <c:strCache>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>bcsstk10</c:v>
                 </c:pt>
@@ -3107,16 +3172,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>amazon0312</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>sinc15</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$26:$Q$26</c:f>
+              <c:f>Sheet1!$C$26:$R$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3161,6 +3229,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>-0.50284463084607511</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>47.625052543085324</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3199,7 +3270,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -3212,7 +3283,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US"/>
+                  <a:rPr lang="en-US" sz="1600"/>
                   <a:t>Matrix</a:t>
                 </a:r>
               </a:p>
@@ -3231,7 +3302,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -3269,7 +3340,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -3295,6 +3366,8 @@
         <c:axId val="2069590255"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="100"/>
+          <c:min val="-100"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -3319,7 +3392,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -3332,7 +3405,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000">
                         <a:lumMod val="65000"/>
@@ -3358,7 +3431,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -3390,7 +3463,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -3583,9 +3656,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$C$23:$Q$23</c:f>
+              <c:f>Sheet1!$C$23:$R$23</c:f>
               <c:strCache>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>bcsstk10</c:v>
                 </c:pt>
@@ -3630,16 +3703,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>amazon0312</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>sinc15</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$24:$Q$24</c:f>
+              <c:f>Sheet1!$C$24:$R$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>99.691889442682367</c:v>
                 </c:pt>
@@ -3684,6 +3760,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46.078210819316226</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>99.60703147712556</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3735,9 +3814,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$C$23:$Q$23</c:f>
+              <c:f>Sheet1!$C$23:$R$23</c:f>
               <c:strCache>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>bcsstk10</c:v>
                 </c:pt>
@@ -3782,16 +3861,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>amazon0312</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>sinc15</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$25:$Q$25</c:f>
+              <c:f>Sheet1!$C$25:$R$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>99.691889442682367</c:v>
                 </c:pt>
@@ -3836,6 +3918,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>49.251804673890618</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>99.821700201624736</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4188,7 +4273,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -4201,7 +4286,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US" sz="2000"/>
               <a:t>Cache Efficiency</a:t>
             </a:r>
           </a:p>
@@ -4220,7 +4305,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -4269,9 +4354,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$C$23:$Q$23</c:f>
+              <c:f>Sheet1!$C$23:$R$23</c:f>
               <c:strCache>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>bcsstk10</c:v>
                 </c:pt>
@@ -4316,16 +4401,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>amazon0312</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>sinc15</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$27:$Q$27</c:f>
+              <c:f>Sheet1!$C$27:$R$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -4370,6 +4458,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.3030685161832703</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4406,9 +4497,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$C$23:$Q$23</c:f>
+              <c:f>Sheet1!$C$23:$R$23</c:f>
               <c:strCache>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>bcsstk10</c:v>
                 </c:pt>
@@ -4453,16 +4544,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>amazon0312</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>sinc15</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$28:$Q$28</c:f>
+              <c:f>Sheet1!$C$28:$R$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -4507,6 +4601,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.5786516853932584</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4543,7 +4640,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -4556,7 +4653,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US"/>
+                  <a:rPr lang="en-US" sz="1600"/>
                   <a:t>Matrix</a:t>
                 </a:r>
               </a:p>
@@ -4575,7 +4672,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -4613,7 +4710,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -4664,7 +4761,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -4677,14 +4774,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US"/>
+                  <a:rPr lang="en-US" sz="1600"/>
                   <a:t>Efficiency</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:rPr lang="en-US" sz="1600" baseline="0"/>
                   <a:t> (normalized)</a:t>
                 </a:r>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="en-US" sz="1600"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -4701,7 +4798,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -4733,7 +4830,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -4776,7 +4873,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -4972,9 +5069,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$C$105:$Q$105</c:f>
+              <c:f>Sheet1!$C$105:$R$105</c:f>
               <c:strCache>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>bcsstk10</c:v>
                 </c:pt>
@@ -5019,16 +5116,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>amazon0312</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>sinc15</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$108:$Q$108</c:f>
+              <c:f>Sheet1!$C$108:$R$108</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5073,6 +5173,9 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>47.625052543085324</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5181,7 +5284,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -5296,7 +5399,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -5316,6 +5419,967 @@
         <c:crossBetween val="between"/>
         <c:minorUnit val="5"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2000"/>
+              <a:t>DRAM Access Reduction v.</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="2000" baseline="0"/>
+              <a:t> Matrix Correlation</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="2000"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$180</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>DRAM Access Reduction</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="#,##0.0" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$177:$J$177</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>bcsstk17</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>shock-9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>fv1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>airfoil1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>diag</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>big_dual</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Chem97ZtZ</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>crack</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$180:$J$180</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>-29.300291545189506</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-8.7051618547681535</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.7413479052823311</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15.137614678899084</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>67.035611164581326</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E65F-45F0-9E28-9BAEFAD9E1A0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:axId val="1558316512"/>
+        <c:axId val="1558316992"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$183</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Weighted Pearson Correlation</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$177:$J$177</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>bcsstk17</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>shock-9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>fv1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>airfoil1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>diag</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>big_dual</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Chem97ZtZ</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>crack</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$183:$J$183</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.99458258408401501</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.99938137434990404</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.99939327039289805</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.97656686079871402</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.92697750688552205</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.65126395359005196</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-0.75453921168305105</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-0.59031282106315597</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E65F-45F0-9E28-9BAEFAD9E1A0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Correlation Positive Limit</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$177:$J$177</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>bcsstk17</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>shock-9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>fv1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>airfoil1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>diag</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>big_dual</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Chem97ZtZ</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>crack</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$184:$J$184</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-E65F-45F0-9E28-9BAEFAD9E1A0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>Correlation Negative Limit</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$177:$J$177</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>bcsstk17</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>shock-9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>fv1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>airfoil1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>diag</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>big_dual</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Chem97ZtZ</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>crack</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$185:$J$185</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>-0.8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-0.8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-0.8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-0.8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-E65F-45F0-9E28-9BAEFAD9E1A0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1558261792"/>
+        <c:axId val="1558269472"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1558316512"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1600"/>
+                  <a:t>Matrix</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1558316992"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1558316992"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="100"/>
+          <c:min val="-100"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Reduction (%)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1558316512"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1558269472"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1600"/>
+                  <a:t>Weighted</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1600" baseline="0"/>
+                  <a:t> Correlation</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" sz="1600"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1558261792"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="1558261792"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1558269472"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -5688,6 +6752,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -9210,6 +10314,509 @@
 </file>
 
 <file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -9868,13 +11475,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>201386</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>139881</xdr:rowOff>
+      <xdr:rowOff>139880</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>125186</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>65314</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>88348</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>99391</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9901,16 +11508,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>559904</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:rowOff>45002</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>83820</xdr:rowOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>219212</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>183211</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9937,16 +11544,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>293914</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>65314</xdr:rowOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>227653</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>54271</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>293914</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>152401</xdr:rowOff>
+      <xdr:col>54</xdr:col>
+      <xdr:colOff>132522</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>176696</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -10002,6 +11609,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>585304</xdr:colOff>
+      <xdr:row>189</xdr:row>
+      <xdr:rowOff>163444</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>519044</xdr:colOff>
+      <xdr:row>228</xdr:row>
+      <xdr:rowOff>77304</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B997C99B-E145-8CC1-EE04-BA70780EEE7F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10343,209 +11986,209 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:40" x14ac:dyDescent="0.3">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="3"/>
-      <c r="AB2" s="3"/>
-      <c r="AC2" s="3"/>
-      <c r="AD2" s="3"/>
-      <c r="AE2" s="3"/>
-      <c r="AF2" s="3"/>
-      <c r="AG2" s="3"/>
-      <c r="AH2" s="3"/>
-      <c r="AI2" s="3"/>
-      <c r="AJ2" s="3"/>
-      <c r="AK2" s="3"/>
-      <c r="AL2" s="3"/>
-      <c r="AM2" s="3"/>
-      <c r="AN2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="4"/>
+      <c r="AB2" s="4"/>
+      <c r="AC2" s="4"/>
+      <c r="AD2" s="4"/>
+      <c r="AE2" s="4"/>
+      <c r="AF2" s="4"/>
+      <c r="AG2" s="4"/>
+      <c r="AH2" s="4"/>
+      <c r="AI2" s="4"/>
+      <c r="AJ2" s="4"/>
+      <c r="AK2" s="4"/>
+      <c r="AL2" s="4"/>
+      <c r="AM2" s="4"/>
+      <c r="AN2" s="4"/>
     </row>
     <row r="3" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="3"/>
+      <c r="E3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2" t="s">
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2" t="s">
+      <c r="H3" s="3"/>
+      <c r="I3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2" t="s">
+      <c r="J3" s="3"/>
+      <c r="K3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2" t="s">
+      <c r="L3" s="3"/>
+      <c r="M3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2" t="s">
+      <c r="N3" s="3"/>
+      <c r="O3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2" t="s">
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2" t="s">
+      <c r="R3" s="3"/>
+      <c r="S3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="T3" s="2"/>
-      <c r="U3" s="2" t="s">
+      <c r="T3" s="3"/>
+      <c r="U3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="V3" s="2"/>
-      <c r="W3" s="2" t="s">
+      <c r="V3" s="3"/>
+      <c r="W3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="X3" s="2"/>
-      <c r="Y3" s="2" t="s">
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="Z3" s="2"/>
-      <c r="AA3" s="2" t="s">
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AB3" s="2"/>
-      <c r="AC3" s="2" t="s">
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="AD3" s="2"/>
-      <c r="AE3" s="2" t="s">
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AF3" s="2"/>
-      <c r="AG3" s="2" t="s">
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AH3" s="2"/>
-      <c r="AI3" s="2" t="s">
+      <c r="AH3" s="3"/>
+      <c r="AI3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AJ3" s="2"/>
-      <c r="AK3" s="2" t="s">
+      <c r="AJ3" s="3"/>
+      <c r="AK3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AL3" s="2"/>
-      <c r="AM3" s="2" t="s">
+      <c r="AL3" s="3"/>
+      <c r="AM3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AN3" s="2"/>
+      <c r="AN3" s="3"/>
     </row>
     <row r="4" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="s">
+      <c r="D4" s="3"/>
+      <c r="E4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2" t="s">
+      <c r="F4" s="3"/>
+      <c r="G4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2" t="s">
+      <c r="H4" s="3"/>
+      <c r="I4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2" t="s">
+      <c r="J4" s="3"/>
+      <c r="K4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2" t="s">
+      <c r="L4" s="3"/>
+      <c r="M4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2" t="s">
+      <c r="N4" s="3"/>
+      <c r="O4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2" t="s">
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2" t="s">
+      <c r="R4" s="3"/>
+      <c r="S4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2" t="s">
+      <c r="T4" s="3"/>
+      <c r="U4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="V4" s="2"/>
-      <c r="W4" s="2" t="s">
+      <c r="V4" s="3"/>
+      <c r="W4" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="X4" s="2"/>
-      <c r="Y4" s="2" t="s">
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="Z4" s="2"/>
-      <c r="AA4" s="2" t="s">
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB4" s="2"/>
-      <c r="AC4" s="2" t="s">
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AD4" s="2"/>
-      <c r="AE4" s="2" t="s">
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AF4" s="2"/>
-      <c r="AG4" s="2" t="s">
+      <c r="AF4" s="3"/>
+      <c r="AG4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AH4" s="2"/>
-      <c r="AI4" s="2" t="s">
+      <c r="AH4" s="3"/>
+      <c r="AI4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AJ4" s="2"/>
-      <c r="AK4" s="2" t="s">
+      <c r="AJ4" s="3"/>
+      <c r="AK4" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="AL4" s="2"/>
-      <c r="AM4" s="2" t="s">
+      <c r="AL4" s="3"/>
+      <c r="AM4" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AN4" s="2"/>
+      <c r="AN4" s="3"/>
     </row>
     <row r="5" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
@@ -12614,209 +14257,209 @@
       </c>
     </row>
     <row r="63" spans="2:40" x14ac:dyDescent="0.3">
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
-      <c r="J63" s="4"/>
-      <c r="K63" s="4"/>
-      <c r="L63" s="4"/>
-      <c r="M63" s="4"/>
-      <c r="N63" s="4"/>
-      <c r="O63" s="4"/>
-      <c r="P63" s="4"/>
-      <c r="Q63" s="4"/>
-      <c r="R63" s="4"/>
-      <c r="S63" s="4"/>
-      <c r="T63" s="4"/>
-      <c r="U63" s="4"/>
-      <c r="V63" s="4"/>
-      <c r="W63" s="4"/>
-      <c r="X63" s="4"/>
-      <c r="Y63" s="4"/>
-      <c r="Z63" s="4"/>
-      <c r="AA63" s="4"/>
-      <c r="AB63" s="4"/>
-      <c r="AC63" s="4"/>
-      <c r="AD63" s="4"/>
-      <c r="AE63" s="4"/>
-      <c r="AF63" s="4"/>
-      <c r="AG63" s="4"/>
-      <c r="AH63" s="4"/>
-      <c r="AI63" s="4"/>
-      <c r="AJ63" s="4"/>
-      <c r="AK63" s="4"/>
-      <c r="AL63" s="4"/>
-      <c r="AM63" s="4"/>
-      <c r="AN63" s="4"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5"/>
+      <c r="J63" s="5"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="5"/>
+      <c r="M63" s="5"/>
+      <c r="N63" s="5"/>
+      <c r="O63" s="5"/>
+      <c r="P63" s="5"/>
+      <c r="Q63" s="5"/>
+      <c r="R63" s="5"/>
+      <c r="S63" s="5"/>
+      <c r="T63" s="5"/>
+      <c r="U63" s="5"/>
+      <c r="V63" s="5"/>
+      <c r="W63" s="5"/>
+      <c r="X63" s="5"/>
+      <c r="Y63" s="5"/>
+      <c r="Z63" s="5"/>
+      <c r="AA63" s="5"/>
+      <c r="AB63" s="5"/>
+      <c r="AC63" s="5"/>
+      <c r="AD63" s="5"/>
+      <c r="AE63" s="5"/>
+      <c r="AF63" s="5"/>
+      <c r="AG63" s="5"/>
+      <c r="AH63" s="5"/>
+      <c r="AI63" s="5"/>
+      <c r="AJ63" s="5"/>
+      <c r="AK63" s="5"/>
+      <c r="AL63" s="5"/>
+      <c r="AM63" s="5"/>
+      <c r="AN63" s="5"/>
     </row>
     <row r="64" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>27</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2" t="s">
+      <c r="D64" s="3"/>
+      <c r="E64" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2" t="s">
+      <c r="F64" s="3"/>
+      <c r="G64" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H64" s="2"/>
-      <c r="I64" s="2" t="s">
+      <c r="H64" s="3"/>
+      <c r="I64" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J64" s="2"/>
-      <c r="K64" s="2" t="s">
+      <c r="J64" s="3"/>
+      <c r="K64" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="L64" s="2"/>
-      <c r="M64" s="2" t="s">
+      <c r="L64" s="3"/>
+      <c r="M64" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2" t="s">
+      <c r="N64" s="3"/>
+      <c r="O64" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="P64" s="2"/>
-      <c r="Q64" s="2" t="s">
+      <c r="P64" s="3"/>
+      <c r="Q64" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="R64" s="2"/>
-      <c r="S64" s="2" t="s">
+      <c r="R64" s="3"/>
+      <c r="S64" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="T64" s="2"/>
-      <c r="U64" s="2" t="s">
+      <c r="T64" s="3"/>
+      <c r="U64" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="V64" s="2"/>
-      <c r="W64" s="2" t="s">
+      <c r="V64" s="3"/>
+      <c r="W64" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="X64" s="2"/>
-      <c r="Y64" s="2" t="s">
+      <c r="X64" s="3"/>
+      <c r="Y64" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="Z64" s="2"/>
-      <c r="AA64" s="2" t="s">
+      <c r="Z64" s="3"/>
+      <c r="AA64" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AB64" s="2"/>
-      <c r="AC64" s="2" t="s">
+      <c r="AB64" s="3"/>
+      <c r="AC64" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="AD64" s="2"/>
-      <c r="AE64" s="2" t="s">
+      <c r="AD64" s="3"/>
+      <c r="AE64" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AF64" s="2"/>
-      <c r="AG64" s="2" t="s">
+      <c r="AF64" s="3"/>
+      <c r="AG64" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AH64" s="2"/>
-      <c r="AI64" s="2" t="s">
+      <c r="AH64" s="3"/>
+      <c r="AI64" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AJ64" s="2"/>
-      <c r="AK64" s="2" t="s">
+      <c r="AJ64" s="3"/>
+      <c r="AK64" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AL64" s="2"/>
-      <c r="AM64" s="2" t="s">
+      <c r="AL64" s="3"/>
+      <c r="AM64" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AN64" s="2"/>
+      <c r="AN64" s="3"/>
     </row>
     <row r="65" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
         <v>26</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2" t="s">
+      <c r="D65" s="3"/>
+      <c r="E65" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2" t="s">
+      <c r="F65" s="3"/>
+      <c r="G65" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2" t="s">
+      <c r="H65" s="3"/>
+      <c r="I65" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J65" s="2"/>
-      <c r="K65" s="2" t="s">
+      <c r="J65" s="3"/>
+      <c r="K65" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L65" s="2"/>
-      <c r="M65" s="2" t="s">
+      <c r="L65" s="3"/>
+      <c r="M65" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2" t="s">
+      <c r="N65" s="3"/>
+      <c r="O65" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="P65" s="2"/>
-      <c r="Q65" s="2" t="s">
+      <c r="P65" s="3"/>
+      <c r="Q65" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="R65" s="2"/>
-      <c r="S65" s="2" t="s">
+      <c r="R65" s="3"/>
+      <c r="S65" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T65" s="2"/>
-      <c r="U65" s="2" t="s">
+      <c r="T65" s="3"/>
+      <c r="U65" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="V65" s="2"/>
-      <c r="W65" s="2" t="s">
+      <c r="V65" s="3"/>
+      <c r="W65" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="X65" s="2"/>
-      <c r="Y65" s="2" t="s">
+      <c r="X65" s="3"/>
+      <c r="Y65" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="Z65" s="2"/>
-      <c r="AA65" s="2" t="s">
+      <c r="Z65" s="3"/>
+      <c r="AA65" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB65" s="2"/>
-      <c r="AC65" s="2" t="s">
+      <c r="AB65" s="3"/>
+      <c r="AC65" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AD65" s="2"/>
-      <c r="AE65" s="2" t="s">
+      <c r="AD65" s="3"/>
+      <c r="AE65" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AF65" s="2"/>
-      <c r="AG65" s="2" t="s">
+      <c r="AF65" s="3"/>
+      <c r="AG65" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AH65" s="2"/>
-      <c r="AI65" s="2" t="s">
+      <c r="AH65" s="3"/>
+      <c r="AI65" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AJ65" s="2"/>
-      <c r="AK65" s="2" t="s">
+      <c r="AJ65" s="3"/>
+      <c r="AK65" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="AL65" s="2"/>
-      <c r="AM65" s="2" t="s">
+      <c r="AL65" s="3"/>
+      <c r="AM65" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AN65" s="2"/>
+      <c r="AN65" s="3"/>
     </row>
     <row r="66" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
@@ -14886,28 +16529,46 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="AK3:AL3"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="AI4:AJ4"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="U4:V4"/>
-    <mergeCell ref="W4:X4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AC4:AD4"/>
-    <mergeCell ref="AA4:AB4"/>
-    <mergeCell ref="AI3:AJ3"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="W3:X3"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="AG65:AH65"/>
+    <mergeCell ref="AI65:AJ65"/>
+    <mergeCell ref="AK65:AL65"/>
+    <mergeCell ref="AM65:AN65"/>
+    <mergeCell ref="W65:X65"/>
+    <mergeCell ref="Y65:Z65"/>
+    <mergeCell ref="AA65:AB65"/>
+    <mergeCell ref="AC65:AD65"/>
+    <mergeCell ref="AE65:AF65"/>
+    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="O65:P65"/>
+    <mergeCell ref="Q65:R65"/>
+    <mergeCell ref="S65:T65"/>
+    <mergeCell ref="U65:V65"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="AE64:AF64"/>
+    <mergeCell ref="AG64:AH64"/>
+    <mergeCell ref="AI64:AJ64"/>
+    <mergeCell ref="AK64:AL64"/>
+    <mergeCell ref="AM64:AN64"/>
+    <mergeCell ref="B2:AN2"/>
+    <mergeCell ref="B63:AN63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="K64:L64"/>
+    <mergeCell ref="M64:N64"/>
+    <mergeCell ref="O64:P64"/>
+    <mergeCell ref="Q64:R64"/>
+    <mergeCell ref="S64:T64"/>
+    <mergeCell ref="U64:V64"/>
+    <mergeCell ref="W64:X64"/>
+    <mergeCell ref="Y64:Z64"/>
+    <mergeCell ref="AA64:AB64"/>
+    <mergeCell ref="AC64:AD64"/>
     <mergeCell ref="AM3:AN3"/>
     <mergeCell ref="AM4:AN4"/>
     <mergeCell ref="C3:D3"/>
@@ -14924,46 +16585,28 @@
     <mergeCell ref="AE3:AF3"/>
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="O4:P4"/>
-    <mergeCell ref="B2:AN2"/>
-    <mergeCell ref="B63:AN63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="K64:L64"/>
-    <mergeCell ref="M64:N64"/>
-    <mergeCell ref="O64:P64"/>
-    <mergeCell ref="Q64:R64"/>
-    <mergeCell ref="S64:T64"/>
-    <mergeCell ref="U64:V64"/>
-    <mergeCell ref="W64:X64"/>
-    <mergeCell ref="Y64:Z64"/>
-    <mergeCell ref="AA64:AB64"/>
-    <mergeCell ref="AC64:AD64"/>
-    <mergeCell ref="AE64:AF64"/>
-    <mergeCell ref="AG64:AH64"/>
-    <mergeCell ref="AI64:AJ64"/>
-    <mergeCell ref="AK64:AL64"/>
-    <mergeCell ref="AM64:AN64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="G65:H65"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="M65:N65"/>
-    <mergeCell ref="O65:P65"/>
-    <mergeCell ref="Q65:R65"/>
-    <mergeCell ref="S65:T65"/>
-    <mergeCell ref="U65:V65"/>
-    <mergeCell ref="AG65:AH65"/>
-    <mergeCell ref="AI65:AJ65"/>
-    <mergeCell ref="AK65:AL65"/>
-    <mergeCell ref="AM65:AN65"/>
-    <mergeCell ref="W65:X65"/>
-    <mergeCell ref="Y65:Z65"/>
-    <mergeCell ref="AA65:AB65"/>
-    <mergeCell ref="AC65:AD65"/>
-    <mergeCell ref="AE65:AF65"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="AK3:AL3"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="AI4:AJ4"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="U4:V4"/>
+    <mergeCell ref="W4:X4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AC4:AD4"/>
+    <mergeCell ref="AA4:AB4"/>
+    <mergeCell ref="AI3:AJ3"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="W3:X3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -14972,213 +16615,213 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CEFDD9D-FDB3-41CB-A695-1350C2A9CE69}">
-  <dimension ref="B2:AN110"/>
+  <dimension ref="B2:AN187"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:40" x14ac:dyDescent="0.3">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="3"/>
-      <c r="AB2" s="3"/>
-      <c r="AC2" s="3"/>
-      <c r="AD2" s="3"/>
-      <c r="AE2" s="3"/>
-      <c r="AF2" s="3"/>
-      <c r="AG2" s="3"/>
-      <c r="AH2" s="3"/>
-      <c r="AI2" s="3"/>
-      <c r="AJ2" s="3"/>
-      <c r="AK2" s="3"/>
-      <c r="AL2" s="3"/>
-      <c r="AM2" s="3"/>
-      <c r="AN2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="4"/>
+      <c r="AB2" s="4"/>
+      <c r="AC2" s="4"/>
+      <c r="AD2" s="4"/>
+      <c r="AE2" s="4"/>
+      <c r="AF2" s="4"/>
+      <c r="AG2" s="4"/>
+      <c r="AH2" s="4"/>
+      <c r="AI2" s="4"/>
+      <c r="AJ2" s="4"/>
+      <c r="AK2" s="4"/>
+      <c r="AL2" s="4"/>
+      <c r="AM2" s="4"/>
+      <c r="AN2" s="4"/>
     </row>
     <row r="3" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="3"/>
+      <c r="E3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2" t="s">
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2" t="s">
+      <c r="H3" s="3"/>
+      <c r="I3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2" t="s">
+      <c r="J3" s="3"/>
+      <c r="K3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2" t="s">
+      <c r="L3" s="3"/>
+      <c r="M3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2" t="s">
+      <c r="N3" s="3"/>
+      <c r="O3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2" t="s">
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2" t="s">
+      <c r="R3" s="3"/>
+      <c r="S3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="T3" s="2"/>
-      <c r="U3" s="2" t="s">
+      <c r="T3" s="3"/>
+      <c r="U3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="V3" s="2"/>
-      <c r="W3" s="2" t="s">
+      <c r="V3" s="3"/>
+      <c r="W3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="X3" s="2"/>
-      <c r="Y3" s="2" t="s">
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="Z3" s="2"/>
-      <c r="AA3" s="2" t="s">
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AB3" s="2"/>
-      <c r="AC3" s="2" t="s">
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="AD3" s="2"/>
-      <c r="AE3" s="2" t="s">
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AF3" s="2"/>
-      <c r="AG3" s="2" t="s">
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH3" s="3"/>
+      <c r="AI3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AH3" s="2"/>
-      <c r="AI3" s="2" t="s">
+      <c r="AJ3" s="3"/>
+      <c r="AK3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AJ3" s="2"/>
-      <c r="AK3" s="2" t="s">
+      <c r="AL3" s="3"/>
+      <c r="AM3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AL3" s="2"/>
-      <c r="AM3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AN3" s="2"/>
+      <c r="AN3" s="3"/>
     </row>
     <row r="4" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="s">
+      <c r="D4" s="3"/>
+      <c r="E4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2" t="s">
+      <c r="F4" s="3"/>
+      <c r="G4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2" t="s">
+      <c r="H4" s="3"/>
+      <c r="I4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2" t="s">
+      <c r="J4" s="3"/>
+      <c r="K4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2" t="s">
+      <c r="L4" s="3"/>
+      <c r="M4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2" t="s">
+      <c r="N4" s="3"/>
+      <c r="O4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2" t="s">
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2" t="s">
+      <c r="R4" s="3"/>
+      <c r="S4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2" t="s">
+      <c r="T4" s="3"/>
+      <c r="U4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="V4" s="2"/>
-      <c r="W4" s="2" t="s">
+      <c r="V4" s="3"/>
+      <c r="W4" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="X4" s="2"/>
-      <c r="Y4" s="2" t="s">
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="Z4" s="2"/>
-      <c r="AA4" s="2" t="s">
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB4" s="2"/>
-      <c r="AC4" s="2" t="s">
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AD4" s="2"/>
-      <c r="AE4" s="2" t="s">
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AF4" s="2"/>
-      <c r="AG4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH4" s="2"/>
-      <c r="AI4" s="2" t="s">
+      <c r="AF4" s="3"/>
+      <c r="AG4" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH4" s="3"/>
+      <c r="AI4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AJ4" s="2"/>
-      <c r="AK4" s="2" t="s">
+      <c r="AJ4" s="3"/>
+      <c r="AK4" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="AL4" s="2"/>
-      <c r="AM4" s="2" t="s">
+      <c r="AL4" s="3"/>
+      <c r="AM4" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AN4" s="2"/>
+      <c r="AN4" s="3"/>
     </row>
     <row r="5" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
@@ -15275,7 +16918,7 @@
         <v>13</v>
       </c>
       <c r="AG5" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="AH5" t="s">
         <v>13</v>
@@ -15393,11 +17036,11 @@
       <c r="AF6">
         <v>1736858</v>
       </c>
-      <c r="AG6" t="s">
-        <v>57</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>57</v>
+      <c r="AG6">
+        <v>2379</v>
+      </c>
+      <c r="AH6">
+        <v>1246</v>
       </c>
       <c r="AI6" t="s">
         <v>57</v>
@@ -15512,11 +17155,11 @@
       <c r="AF7">
         <v>1685644</v>
       </c>
-      <c r="AG7" t="s">
-        <v>57</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>57</v>
+      <c r="AG7">
+        <v>603013</v>
+      </c>
+      <c r="AH7">
+        <v>697577</v>
       </c>
       <c r="AI7" t="s">
         <v>57</v>
@@ -15661,13 +17304,13 @@
         <f t="shared" si="0"/>
         <v>3422502</v>
       </c>
-      <c r="AG8" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AH8" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+      <c r="AG8">
+        <f t="shared" ref="AG8:AH8" si="1">AG6+AG7</f>
+        <v>605392</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="1"/>
+        <v>698823</v>
       </c>
       <c r="AI8" t="e">
         <f t="shared" si="0"/>
@@ -15699,155 +17342,155 @@
         <v>60</v>
       </c>
       <c r="C9">
-        <f t="shared" ref="C9:AN9" si="1">IFERROR(C7/C8, 0)</f>
+        <f t="shared" ref="C9:AN9" si="2">IFERROR(C7/C8, 0)</f>
         <v>0.99691889442682369</v>
       </c>
       <c r="D9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.99691889442682369</v>
       </c>
       <c r="E9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.99904801480865857</v>
       </c>
       <c r="F9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.99906031158874464</v>
       </c>
       <c r="G9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.99897115947028214</v>
       </c>
       <c r="H9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.99870745493943103</v>
       </c>
       <c r="I9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.99249923085599701</v>
       </c>
       <c r="J9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.9998513813962755</v>
       </c>
       <c r="K9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.85634551495016609</v>
       </c>
       <c r="L9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.94522435170814223</v>
       </c>
       <c r="M9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.99519519039357862</v>
       </c>
       <c r="N9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.99521092641879294</v>
       </c>
       <c r="O9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.85452382618431177</v>
       </c>
       <c r="P9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.87260932224155763</v>
       </c>
       <c r="Q9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.99715949054786668</v>
       </c>
       <c r="R9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.99788656941353771</v>
       </c>
       <c r="S9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.99902192129164369</v>
       </c>
       <c r="T9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.99933753651077184</v>
       </c>
       <c r="U9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.99882385893741099</v>
       </c>
       <c r="V9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.99974959356620707</v>
       </c>
       <c r="W9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.90163466750349475</v>
       </c>
       <c r="X9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.99514256771343645</v>
       </c>
       <c r="Y9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.84015603815323137</v>
       </c>
       <c r="Z9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.93135559398696288</v>
       </c>
       <c r="AA9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.71354647583871955</v>
       </c>
       <c r="AB9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.84433989110432361</v>
       </c>
       <c r="AC9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.87535315985130113</v>
       </c>
       <c r="AD9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.98383934005003715</v>
       </c>
       <c r="AE9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.46078210819316229</v>
       </c>
       <c r="AF9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.4925180467389062</v>
       </c>
       <c r="AG9">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="AG9:AH9" si="3">IFERROR(AG7/AG8, 0)</f>
+        <v>0.99607031477125563</v>
+      </c>
+      <c r="AH9">
+        <f t="shared" si="3"/>
+        <v>0.9982170020162473</v>
+      </c>
+      <c r="AI9">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AH9">
-        <f t="shared" si="1"/>
+      <c r="AJ9">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AI9">
-        <f t="shared" si="1"/>
+      <c r="AK9">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AJ9">
-        <f t="shared" si="1"/>
+      <c r="AL9">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK9">
-        <f t="shared" si="1"/>
+      <c r="AM9">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AL9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="AN9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -15856,155 +17499,155 @@
         <v>61</v>
       </c>
       <c r="C10">
-        <f t="shared" ref="C10:AN10" si="2">IFERROR(C6/C8, 0)</f>
+        <f t="shared" ref="C10:AN10" si="4">IFERROR(C6/C8, 0)</f>
         <v>3.0811055731762575E-3</v>
       </c>
       <c r="D10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.0811055731762575E-3</v>
       </c>
       <c r="E10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9.5198519134146798E-4</v>
       </c>
       <c r="F10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9.3968841125537897E-4</v>
       </c>
       <c r="G10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.0288405297178937E-3</v>
       </c>
       <c r="H10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.2925450605689238E-3</v>
       </c>
       <c r="I10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>7.5007691440029641E-3</v>
       </c>
       <c r="J10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.4861860372449633E-4</v>
       </c>
       <c r="K10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.14365448504983389</v>
       </c>
       <c r="L10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.477564829185777E-2</v>
       </c>
       <c r="M10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4.8048096064213361E-3</v>
       </c>
       <c r="N10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4.7890735812070699E-3</v>
       </c>
       <c r="O10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.1454761738156882</v>
       </c>
       <c r="P10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.1273906777584424</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.8405094521333578E-3</v>
       </c>
       <c r="R10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.1134305864622701E-3</v>
       </c>
       <c r="S10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9.780787083563476E-4</v>
       </c>
       <c r="T10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>6.6246348922815047E-4</v>
       </c>
       <c r="U10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.1761410625890237E-3</v>
       </c>
       <c r="V10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.5040643379292026E-4</v>
       </c>
       <c r="W10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9.8365332496505295E-2</v>
       </c>
       <c r="X10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4.857432286563595E-3</v>
       </c>
       <c r="Y10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.15984396184676863</v>
       </c>
       <c r="Z10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>6.8644406013037118E-2</v>
       </c>
       <c r="AA10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28645352416128039</v>
       </c>
       <c r="AB10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.15566010889567641</v>
       </c>
       <c r="AC10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.12464684014869888</v>
       </c>
       <c r="AD10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.6160659949962811E-2</v>
       </c>
       <c r="AE10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.53921789180683777</v>
       </c>
       <c r="AF10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5074819532610938</v>
       </c>
       <c r="AG10">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="AG10:AH10" si="5">IFERROR(AG6/AG8, 0)</f>
+        <v>3.9296852287443512E-3</v>
+      </c>
+      <c r="AH10">
+        <f t="shared" si="5"/>
+        <v>1.7829979837526812E-3</v>
+      </c>
+      <c r="AI10">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AH10">
-        <f t="shared" si="2"/>
+      <c r="AJ10">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AI10">
-        <f t="shared" si="2"/>
+      <c r="AK10">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AJ10">
-        <f t="shared" si="2"/>
+      <c r="AL10">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AK10">
-        <f t="shared" si="2"/>
+      <c r="AM10">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AL10">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AM10">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
       <c r="AN10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -16222,10 +17865,10 @@
         <v>44</v>
       </c>
       <c r="AG12">
-        <v>125</v>
+        <v>721</v>
       </c>
       <c r="AH12">
-        <v>125</v>
+        <v>721</v>
       </c>
       <c r="AI12">
         <v>188</v>
@@ -16251,155 +17894,155 @@
         <v>8</v>
       </c>
       <c r="C13">
-        <f t="shared" ref="C13:AN13" si="3">IFERROR(C12/C6, 0)</f>
+        <f t="shared" ref="C13:AN13" si="6">IFERROR(C12/C6, 0)</f>
         <v>1</v>
       </c>
       <c r="D13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="F13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.77339346110484786</v>
       </c>
       <c r="I13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1.6807113925229294E-2</v>
       </c>
       <c r="J13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.60267111853088484</v>
       </c>
       <c r="K13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>9.5780260442610121E-2</v>
       </c>
       <c r="L13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.2142629735752945</v>
       </c>
       <c r="M13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="N13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>7.3561006894340225E-2</v>
       </c>
       <c r="P13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>7.478890229191798E-2</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.836952380952381</v>
       </c>
       <c r="R13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.87425387982491043</v>
       </c>
       <c r="S13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.40653454740224959</v>
       </c>
       <c r="T13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.4882075471698113</v>
       </c>
       <c r="U13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.22234762979683972</v>
       </c>
       <c r="V13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="W13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>4.8917246713070378E-2</v>
       </c>
       <c r="X13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.86495726495726499</v>
       </c>
       <c r="Y13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.10119047619047619</v>
       </c>
       <c r="Z13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.21963824289405684</v>
       </c>
       <c r="AA13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>4.150157813444362E-2</v>
       </c>
       <c r="AB13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>7.5319926873857398E-2</v>
       </c>
       <c r="AC13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.14255890247539516</v>
       </c>
       <c r="AD13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AE13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AF13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AG13">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="AG13:AH13" si="7">IFERROR(AG12/AG6, 0)</f>
+        <v>0.3030685161832703</v>
+      </c>
+      <c r="AH13">
+        <f t="shared" si="7"/>
+        <v>0.5786516853932584</v>
+      </c>
+      <c r="AI13">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AH13">
-        <f t="shared" si="3"/>
+      <c r="AJ13">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AI13">
-        <f t="shared" si="3"/>
+      <c r="AK13">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AJ13">
-        <f t="shared" si="3"/>
+      <c r="AL13">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AK13">
-        <f t="shared" si="3"/>
+      <c r="AM13">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AL13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
       <c r="AN13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -16498,10 +18141,10 @@
         <v>400727</v>
       </c>
       <c r="AG14">
-        <v>2000</v>
+        <v>11532</v>
       </c>
       <c r="AH14">
-        <v>2000</v>
+        <v>11532</v>
       </c>
       <c r="AI14">
         <v>3000</v>
@@ -16617,10 +18260,10 @@
         <v>400727</v>
       </c>
       <c r="AG15">
-        <v>2000</v>
+        <v>11532</v>
       </c>
       <c r="AH15">
-        <v>2000</v>
+        <v>11532</v>
       </c>
       <c r="AI15">
         <v>3000</v>
@@ -16735,11 +18378,11 @@
       <c r="AF16" s="1">
         <v>1.99302377500994E-5</v>
       </c>
-      <c r="AG16">
-        <v>1</v>
-      </c>
-      <c r="AH16">
-        <v>1</v>
+      <c r="AG16" s="1">
+        <v>4.1446449692715799E-3</v>
+      </c>
+      <c r="AH16" s="1">
+        <v>4.1446449692715799E-3</v>
       </c>
       <c r="AI16">
         <v>1</v>
@@ -16929,7 +18572,7 @@
         <v>36</v>
       </c>
       <c r="R22" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="S22" t="s">
         <v>45</v>
@@ -16991,7 +18634,7 @@
         <v>38</v>
       </c>
       <c r="R23" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="S23" t="s">
         <v>47</v>
@@ -17069,7 +18712,7 @@
       </c>
       <c r="R24">
         <f>AG9*100</f>
-        <v>0</v>
+        <v>99.60703147712556</v>
       </c>
       <c r="S24">
         <f>AI9*100</f>
@@ -17150,7 +18793,7 @@
       </c>
       <c r="R25">
         <f>AH9*100</f>
-        <v>0</v>
+        <v>99.821700201624736</v>
       </c>
       <c r="S25">
         <f>AJ9*100</f>
@@ -17231,7 +18874,7 @@
       </c>
       <c r="R26">
         <f>IFERROR(((AG6-AH6)/AG6)*100, 0)</f>
-        <v>0</v>
+        <v>47.625052543085324</v>
       </c>
       <c r="S26">
         <f>IFERROR(((AI6-AJ6)/AI6)*100, 0)</f>
@@ -17312,7 +18955,7 @@
       </c>
       <c r="R27">
         <f>AG13</f>
-        <v>0</v>
+        <v>0.3030685161832703</v>
       </c>
       <c r="S27">
         <f>AI13</f>
@@ -17393,7 +19036,7 @@
       </c>
       <c r="R28">
         <f>AH13</f>
-        <v>0</v>
+        <v>0.5786516853932584</v>
       </c>
       <c r="S28">
         <f>AJ13</f>
@@ -17409,209 +19052,209 @@
       </c>
     </row>
     <row r="84" spans="2:40" x14ac:dyDescent="0.3">
-      <c r="B84" s="4" t="s">
+      <c r="B84" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
-      <c r="F84" s="4"/>
-      <c r="G84" s="4"/>
-      <c r="H84" s="4"/>
-      <c r="I84" s="4"/>
-      <c r="J84" s="4"/>
-      <c r="K84" s="4"/>
-      <c r="L84" s="4"/>
-      <c r="M84" s="4"/>
-      <c r="N84" s="4"/>
-      <c r="O84" s="4"/>
-      <c r="P84" s="4"/>
-      <c r="Q84" s="4"/>
-      <c r="R84" s="4"/>
-      <c r="S84" s="4"/>
-      <c r="T84" s="4"/>
-      <c r="U84" s="4"/>
-      <c r="V84" s="4"/>
-      <c r="W84" s="4"/>
-      <c r="X84" s="4"/>
-      <c r="Y84" s="4"/>
-      <c r="Z84" s="4"/>
-      <c r="AA84" s="4"/>
-      <c r="AB84" s="4"/>
-      <c r="AC84" s="4"/>
-      <c r="AD84" s="4"/>
-      <c r="AE84" s="4"/>
-      <c r="AF84" s="4"/>
-      <c r="AG84" s="4"/>
-      <c r="AH84" s="4"/>
-      <c r="AI84" s="4"/>
-      <c r="AJ84" s="4"/>
-      <c r="AK84" s="4"/>
-      <c r="AL84" s="4"/>
-      <c r="AM84" s="4"/>
-      <c r="AN84" s="4"/>
+      <c r="C84" s="5"/>
+      <c r="D84" s="5"/>
+      <c r="E84" s="5"/>
+      <c r="F84" s="5"/>
+      <c r="G84" s="5"/>
+      <c r="H84" s="5"/>
+      <c r="I84" s="5"/>
+      <c r="J84" s="5"/>
+      <c r="K84" s="5"/>
+      <c r="L84" s="5"/>
+      <c r="M84" s="5"/>
+      <c r="N84" s="5"/>
+      <c r="O84" s="5"/>
+      <c r="P84" s="5"/>
+      <c r="Q84" s="5"/>
+      <c r="R84" s="5"/>
+      <c r="S84" s="5"/>
+      <c r="T84" s="5"/>
+      <c r="U84" s="5"/>
+      <c r="V84" s="5"/>
+      <c r="W84" s="5"/>
+      <c r="X84" s="5"/>
+      <c r="Y84" s="5"/>
+      <c r="Z84" s="5"/>
+      <c r="AA84" s="5"/>
+      <c r="AB84" s="5"/>
+      <c r="AC84" s="5"/>
+      <c r="AD84" s="5"/>
+      <c r="AE84" s="5"/>
+      <c r="AF84" s="5"/>
+      <c r="AG84" s="5"/>
+      <c r="AH84" s="5"/>
+      <c r="AI84" s="5"/>
+      <c r="AJ84" s="5"/>
+      <c r="AK84" s="5"/>
+      <c r="AL84" s="5"/>
+      <c r="AM84" s="5"/>
+      <c r="AN84" s="5"/>
     </row>
     <row r="85" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B85" t="s">
         <v>27</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C85" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2" t="s">
+      <c r="D85" s="3"/>
+      <c r="E85" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2" t="s">
+      <c r="F85" s="3"/>
+      <c r="G85" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H85" s="2"/>
-      <c r="I85" s="2" t="s">
+      <c r="H85" s="3"/>
+      <c r="I85" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J85" s="2"/>
-      <c r="K85" s="2" t="s">
+      <c r="J85" s="3"/>
+      <c r="K85" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="L85" s="2"/>
-      <c r="M85" s="2" t="s">
+      <c r="L85" s="3"/>
+      <c r="M85" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2" t="s">
+      <c r="N85" s="3"/>
+      <c r="O85" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="P85" s="2"/>
-      <c r="Q85" s="2" t="s">
+      <c r="P85" s="3"/>
+      <c r="Q85" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="R85" s="2"/>
-      <c r="S85" s="2" t="s">
+      <c r="R85" s="3"/>
+      <c r="S85" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="T85" s="2"/>
-      <c r="U85" s="2" t="s">
+      <c r="T85" s="3"/>
+      <c r="U85" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="V85" s="2"/>
-      <c r="W85" s="2" t="s">
+      <c r="V85" s="3"/>
+      <c r="W85" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="X85" s="2"/>
-      <c r="Y85" s="2" t="s">
+      <c r="X85" s="3"/>
+      <c r="Y85" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="Z85" s="2"/>
-      <c r="AA85" s="2" t="s">
+      <c r="Z85" s="3"/>
+      <c r="AA85" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AB85" s="2"/>
-      <c r="AC85" s="2" t="s">
+      <c r="AB85" s="3"/>
+      <c r="AC85" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="AD85" s="2"/>
-      <c r="AE85" s="2" t="s">
+      <c r="AD85" s="3"/>
+      <c r="AE85" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AF85" s="2"/>
-      <c r="AG85" s="2" t="s">
+      <c r="AF85" s="3"/>
+      <c r="AG85" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH85" s="3"/>
+      <c r="AI85" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AH85" s="2"/>
-      <c r="AI85" s="2" t="s">
+      <c r="AJ85" s="3"/>
+      <c r="AK85" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AJ85" s="2"/>
-      <c r="AK85" s="2" t="s">
+      <c r="AL85" s="3"/>
+      <c r="AM85" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AL85" s="2"/>
-      <c r="AM85" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AN85" s="2"/>
+      <c r="AN85" s="3"/>
     </row>
     <row r="86" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B86" t="s">
         <v>26</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C86" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2" t="s">
+      <c r="D86" s="3"/>
+      <c r="E86" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2" t="s">
+      <c r="F86" s="3"/>
+      <c r="G86" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H86" s="2"/>
-      <c r="I86" s="2" t="s">
+      <c r="H86" s="3"/>
+      <c r="I86" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J86" s="2"/>
-      <c r="K86" s="2" t="s">
+      <c r="J86" s="3"/>
+      <c r="K86" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L86" s="2"/>
-      <c r="M86" s="2" t="s">
+      <c r="L86" s="3"/>
+      <c r="M86" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2" t="s">
+      <c r="N86" s="3"/>
+      <c r="O86" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="P86" s="2"/>
-      <c r="Q86" s="2" t="s">
+      <c r="P86" s="3"/>
+      <c r="Q86" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="R86" s="2"/>
-      <c r="S86" s="2" t="s">
+      <c r="R86" s="3"/>
+      <c r="S86" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T86" s="2"/>
-      <c r="U86" s="2" t="s">
+      <c r="T86" s="3"/>
+      <c r="U86" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="V86" s="2"/>
-      <c r="W86" s="2" t="s">
+      <c r="V86" s="3"/>
+      <c r="W86" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="X86" s="2"/>
-      <c r="Y86" s="2" t="s">
+      <c r="X86" s="3"/>
+      <c r="Y86" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="Z86" s="2"/>
-      <c r="AA86" s="2" t="s">
+      <c r="Z86" s="3"/>
+      <c r="AA86" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB86" s="2"/>
-      <c r="AC86" s="2" t="s">
+      <c r="AB86" s="3"/>
+      <c r="AC86" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AD86" s="2"/>
-      <c r="AE86" s="2" t="s">
+      <c r="AD86" s="3"/>
+      <c r="AE86" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AF86" s="2"/>
-      <c r="AG86" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH86" s="2"/>
-      <c r="AI86" s="2" t="s">
+      <c r="AF86" s="3"/>
+      <c r="AG86" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH86" s="3"/>
+      <c r="AI86" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AJ86" s="2"/>
-      <c r="AK86" s="2" t="s">
+      <c r="AJ86" s="3"/>
+      <c r="AK86" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="AL86" s="2"/>
-      <c r="AM86" s="2" t="s">
+      <c r="AL86" s="3"/>
+      <c r="AM86" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AN86" s="2"/>
+      <c r="AN86" s="3"/>
     </row>
     <row r="87" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B87" t="s">
@@ -17708,7 +19351,7 @@
         <v>13</v>
       </c>
       <c r="AG87" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="AH87" t="s">
         <v>13</v>
@@ -17826,11 +19469,11 @@
       <c r="AF88">
         <v>1728168</v>
       </c>
-      <c r="AG88" t="s">
-        <v>57</v>
-      </c>
-      <c r="AH88" t="s">
-        <v>57</v>
+      <c r="AG88">
+        <v>2379</v>
+      </c>
+      <c r="AH88">
+        <v>1246</v>
       </c>
       <c r="AI88" t="s">
         <v>57</v>
@@ -17945,11 +19588,11 @@
       <c r="AF89">
         <v>1476785</v>
       </c>
-      <c r="AG89" t="s">
-        <v>57</v>
-      </c>
-      <c r="AH89" t="s">
-        <v>57</v>
+      <c r="AG89">
+        <v>603013</v>
+      </c>
+      <c r="AH89">
+        <v>697577</v>
       </c>
       <c r="AI89" t="s">
         <v>57</v>
@@ -17975,155 +19618,155 @@
         <v>3</v>
       </c>
       <c r="C90">
-        <f t="shared" ref="C90:AN90" si="4">C88+C89</f>
+        <f t="shared" ref="C90:AN90" si="8">C88+C89</f>
         <v>22070</v>
       </c>
       <c r="D90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>22070</v>
       </c>
       <c r="E90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>132355</v>
       </c>
       <c r="F90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>134087</v>
       </c>
       <c r="G90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>666770</v>
       </c>
       <c r="H90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>666770</v>
       </c>
       <c r="I90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>2863573</v>
       </c>
       <c r="J90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>4030451</v>
       </c>
       <c r="K90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>97825</v>
       </c>
       <c r="L90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>114686</v>
       </c>
       <c r="M90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>125083</v>
       </c>
       <c r="N90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>125494</v>
       </c>
       <c r="O90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>214365</v>
       </c>
       <c r="P90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>240779</v>
       </c>
       <c r="Q90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>924130</v>
       </c>
       <c r="R90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1189062</v>
       </c>
       <c r="S90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>5726533</v>
       </c>
       <c r="T90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>7040388</v>
       </c>
       <c r="U90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>753311</v>
       </c>
       <c r="V90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>786721</v>
       </c>
       <c r="W90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>105159</v>
       </c>
       <c r="X90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>120434</v>
       </c>
       <c r="Y90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>42041</v>
       </c>
       <c r="Z90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>45102</v>
       </c>
       <c r="AA90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>51984</v>
       </c>
       <c r="AB90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>52711</v>
       </c>
       <c r="AC90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>26900</v>
       </c>
       <c r="AD90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>29578</v>
       </c>
       <c r="AE90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>3204953</v>
       </c>
       <c r="AF90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>3204953</v>
       </c>
-      <c r="AG90" t="e">
-        <f t="shared" si="4"/>
+      <c r="AG90">
+        <f t="shared" si="8"/>
+        <v>605392</v>
+      </c>
+      <c r="AH90">
+        <f t="shared" si="8"/>
+        <v>698823</v>
+      </c>
+      <c r="AI90" t="e">
+        <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
-      <c r="AH90" t="e">
-        <f t="shared" si="4"/>
+      <c r="AJ90" t="e">
+        <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
-      <c r="AI90" t="e">
-        <f t="shared" si="4"/>
+      <c r="AK90" t="e">
+        <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ90" t="e">
-        <f t="shared" si="4"/>
+      <c r="AL90" t="e">
+        <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
-      <c r="AK90" t="e">
-        <f t="shared" si="4"/>
+      <c r="AM90" t="e">
+        <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
-      <c r="AL90" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AM90" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
       <c r="AN90" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -18132,155 +19775,155 @@
         <v>60</v>
       </c>
       <c r="C91">
-        <f t="shared" ref="C91:AN91" si="5">IFERROR(C89/C90, 0)</f>
+        <f t="shared" ref="C91:AN91" si="9">IFERROR(C89/C90, 0)</f>
         <v>0.99691889442682369</v>
       </c>
       <c r="D91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.99691889442682369</v>
       </c>
       <c r="E91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.99904801480865857</v>
       </c>
       <c r="F91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.99906031158874464</v>
       </c>
       <c r="G91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.99897115947028214</v>
       </c>
       <c r="H91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.99897115947028214</v>
       </c>
       <c r="I91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.99249923085599701</v>
       </c>
       <c r="J91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.9998513813962755</v>
       </c>
       <c r="K91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.85634551495016609</v>
       </c>
       <c r="L91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.94522435170814223</v>
       </c>
       <c r="M91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.99519519039357862</v>
       </c>
       <c r="N91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.99521092641879294</v>
       </c>
       <c r="O91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.85452382618431177</v>
       </c>
       <c r="P91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.87260932224155763</v>
       </c>
       <c r="Q91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.99715949054786668</v>
       </c>
       <c r="R91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.99788656941353771</v>
       </c>
       <c r="S91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.99902192129164369</v>
       </c>
       <c r="T91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.99933753651077184</v>
       </c>
       <c r="U91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.99882385893741099</v>
       </c>
       <c r="V91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.99974959356620707</v>
       </c>
       <c r="W91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.90163466750349475</v>
       </c>
       <c r="X91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.99514256771343645</v>
       </c>
       <c r="Y91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.84015603815323137</v>
       </c>
       <c r="Z91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.93135559398696288</v>
       </c>
       <c r="AA91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.71354647583871955</v>
       </c>
       <c r="AB91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.84433989110432361</v>
       </c>
       <c r="AC91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.87535315985130113</v>
       </c>
       <c r="AD91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.98383934005003715</v>
       </c>
       <c r="AE91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.46078210819316229</v>
       </c>
       <c r="AF91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0.46078210819316229</v>
       </c>
       <c r="AG91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
+        <v>0.99607031477125563</v>
+      </c>
+      <c r="AH91">
+        <f t="shared" si="9"/>
+        <v>0.9982170020162473</v>
+      </c>
+      <c r="AI91">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AH91">
-        <f t="shared" si="5"/>
+      <c r="AJ91">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AI91">
-        <f t="shared" si="5"/>
+      <c r="AK91">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AJ91">
-        <f t="shared" si="5"/>
+      <c r="AL91">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AK91">
-        <f t="shared" si="5"/>
+      <c r="AM91">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AL91">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AM91">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
       <c r="AN91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -18289,155 +19932,155 @@
         <v>61</v>
       </c>
       <c r="C92">
-        <f t="shared" ref="C92:AN92" si="6">IFERROR(C88/C90, 0)</f>
+        <f t="shared" ref="C92:AN92" si="10">IFERROR(C88/C90, 0)</f>
         <v>3.0811055731762575E-3</v>
       </c>
       <c r="D92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3.0811055731762575E-3</v>
       </c>
       <c r="E92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9.5198519134146798E-4</v>
       </c>
       <c r="F92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9.3968841125537897E-4</v>
       </c>
       <c r="G92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.0288405297178937E-3</v>
       </c>
       <c r="H92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.0288405297178937E-3</v>
       </c>
       <c r="I92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>7.5007691440029641E-3</v>
       </c>
       <c r="J92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.4861860372449633E-4</v>
       </c>
       <c r="K92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.14365448504983389</v>
       </c>
       <c r="L92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>5.477564829185777E-2</v>
       </c>
       <c r="M92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4.8048096064213361E-3</v>
       </c>
       <c r="N92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4.7890735812070699E-3</v>
       </c>
       <c r="O92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.1454761738156882</v>
       </c>
       <c r="P92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.1273906777584424</v>
       </c>
       <c r="Q92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.8405094521333578E-3</v>
       </c>
       <c r="R92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.1134305864622701E-3</v>
       </c>
       <c r="S92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9.780787083563476E-4</v>
       </c>
       <c r="T92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>6.6246348922815047E-4</v>
       </c>
       <c r="U92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.1761410625890237E-3</v>
       </c>
       <c r="V92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>2.5040643379292026E-4</v>
       </c>
       <c r="W92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>9.8365332496505295E-2</v>
       </c>
       <c r="X92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>4.857432286563595E-3</v>
       </c>
       <c r="Y92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.15984396184676863</v>
       </c>
       <c r="Z92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>6.8644406013037118E-2</v>
       </c>
       <c r="AA92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.28645352416128039</v>
       </c>
       <c r="AB92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.15566010889567641</v>
       </c>
       <c r="AC92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.12464684014869888</v>
       </c>
       <c r="AD92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>1.6160659949962811E-2</v>
       </c>
       <c r="AE92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.53921789180683777</v>
       </c>
       <c r="AF92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0.53921789180683777</v>
       </c>
       <c r="AG92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
+        <v>3.9296852287443512E-3</v>
+      </c>
+      <c r="AH92">
+        <f t="shared" si="10"/>
+        <v>1.7829979837526812E-3</v>
+      </c>
+      <c r="AI92">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AH92">
-        <f t="shared" si="6"/>
+      <c r="AJ92">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AI92">
-        <f t="shared" si="6"/>
+      <c r="AK92">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AJ92">
-        <f t="shared" si="6"/>
+      <c r="AL92">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AK92">
-        <f t="shared" si="6"/>
+      <c r="AM92">
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL92">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AM92">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
       <c r="AN92">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -18655,10 +20298,10 @@
         <v>44</v>
       </c>
       <c r="AG94">
-        <v>125</v>
+        <v>721</v>
       </c>
       <c r="AH94">
-        <v>125</v>
+        <v>721</v>
       </c>
       <c r="AI94">
         <v>188</v>
@@ -18684,155 +20327,155 @@
         <v>8</v>
       </c>
       <c r="C95">
-        <f t="shared" ref="C95:AN95" si="7">IFERROR(C94/C88, 0)</f>
+        <f t="shared" ref="C95:AN95" si="11">IFERROR(C94/C88, 0)</f>
         <v>1</v>
       </c>
       <c r="D95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="E95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="F95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="G95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="H95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="I95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1.6807113925229294E-2</v>
       </c>
       <c r="J95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.60267111853088484</v>
       </c>
       <c r="K95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>9.5780260442610121E-2</v>
       </c>
       <c r="L95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.2142629735752945</v>
       </c>
       <c r="M95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="N95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="O95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>7.3561006894340225E-2</v>
       </c>
       <c r="P95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>7.478890229191798E-2</v>
       </c>
       <c r="Q95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.836952380952381</v>
       </c>
       <c r="R95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.87425387982491043</v>
       </c>
       <c r="S95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.40653454740224959</v>
       </c>
       <c r="T95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.4882075471698113</v>
       </c>
       <c r="U95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.22234762979683972</v>
       </c>
       <c r="V95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="W95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>4.8917246713070378E-2</v>
       </c>
       <c r="X95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.86495726495726499</v>
       </c>
       <c r="Y95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.10119047619047619</v>
       </c>
       <c r="Z95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.21963824289405684</v>
       </c>
       <c r="AA95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>4.150157813444362E-2</v>
       </c>
       <c r="AB95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>7.5319926873857398E-2</v>
       </c>
       <c r="AC95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0.14255890247539516</v>
       </c>
       <c r="AD95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="AE95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AF95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AG95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
+        <v>0.3030685161832703</v>
+      </c>
+      <c r="AH95">
+        <f t="shared" si="11"/>
+        <v>0.5786516853932584</v>
+      </c>
+      <c r="AI95">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH95">
-        <f t="shared" si="7"/>
+      <c r="AJ95">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AI95">
-        <f t="shared" si="7"/>
+      <c r="AK95">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AJ95">
-        <f t="shared" si="7"/>
+      <c r="AL95">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AK95">
-        <f t="shared" si="7"/>
+      <c r="AM95">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AL95">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AM95">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
       <c r="AN95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -18931,10 +20574,10 @@
         <v>400727</v>
       </c>
       <c r="AG96">
-        <v>2000</v>
+        <v>11532</v>
       </c>
       <c r="AH96">
-        <v>2000</v>
+        <v>11532</v>
       </c>
       <c r="AI96">
         <v>3000</v>
@@ -19050,10 +20693,10 @@
         <v>400727</v>
       </c>
       <c r="AG97">
-        <v>2000</v>
+        <v>11532</v>
       </c>
       <c r="AH97">
-        <v>2000</v>
+        <v>11532</v>
       </c>
       <c r="AI97">
         <v>3000</v>
@@ -19168,11 +20811,11 @@
       <c r="AF98" s="1">
         <v>1.99302377500994E-5</v>
       </c>
-      <c r="AG98">
-        <v>1</v>
-      </c>
-      <c r="AH98">
-        <v>1</v>
+      <c r="AG98" s="1">
+        <v>4.1446449692715799E-3</v>
+      </c>
+      <c r="AH98" s="1">
+        <v>4.1446449692715799E-3</v>
       </c>
       <c r="AI98">
         <v>1</v>
@@ -19362,7 +21005,7 @@
         <v>36</v>
       </c>
       <c r="R104" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="S104" t="s">
         <v>45</v>
@@ -19424,7 +21067,7 @@
         <v>38</v>
       </c>
       <c r="R105" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="S105" t="s">
         <v>47</v>
@@ -19502,7 +21145,7 @@
       </c>
       <c r="R106">
         <f>AG91*100</f>
-        <v>0</v>
+        <v>99.60703147712556</v>
       </c>
       <c r="S106">
         <f>AI91*100</f>
@@ -19583,7 +21226,7 @@
       </c>
       <c r="R107">
         <f>AH91*100</f>
-        <v>0</v>
+        <v>99.821700201624736</v>
       </c>
       <c r="S107">
         <f>AJ91*100</f>
@@ -19664,7 +21307,7 @@
       </c>
       <c r="R108">
         <f>IFERROR(((AG88-AH88)/AG88)*100, 0)</f>
-        <v>0</v>
+        <v>47.625052543085324</v>
       </c>
       <c r="S108">
         <f>IFERROR(((AI88-AJ88)/AI88)*100, 0)</f>
@@ -19745,7 +21388,7 @@
       </c>
       <c r="R109">
         <f>AG95</f>
-        <v>0</v>
+        <v>0.3030685161832703</v>
       </c>
       <c r="S109">
         <f>AI95</f>
@@ -19826,7 +21469,7 @@
       </c>
       <c r="R110">
         <f>AH95</f>
-        <v>0</v>
+        <v>0.5786516853932584</v>
       </c>
       <c r="S110">
         <f>AJ95</f>
@@ -19841,15 +21484,1415 @@
         <v>0</v>
       </c>
     </row>
+    <row r="156" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B156" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C156" s="6"/>
+      <c r="D156" s="6"/>
+      <c r="E156" s="6"/>
+      <c r="F156" s="6"/>
+      <c r="G156" s="6"/>
+      <c r="H156" s="6"/>
+      <c r="I156" s="6"/>
+      <c r="J156" s="6"/>
+      <c r="K156" s="6"/>
+      <c r="L156" s="6"/>
+      <c r="M156" s="6"/>
+      <c r="N156" s="6"/>
+      <c r="O156" s="6"/>
+      <c r="P156" s="6"/>
+      <c r="Q156" s="7"/>
+      <c r="R156" s="7"/>
+      <c r="S156" s="7"/>
+      <c r="T156" s="7"/>
+      <c r="U156" s="7"/>
+      <c r="V156" s="7"/>
+      <c r="W156" s="7"/>
+      <c r="X156" s="7"/>
+      <c r="Y156" s="7"/>
+      <c r="Z156" s="7"/>
+      <c r="AA156" s="7"/>
+      <c r="AB156" s="7"/>
+      <c r="AC156" s="7"/>
+      <c r="AD156" s="7"/>
+      <c r="AE156" s="7"/>
+      <c r="AF156" s="7"/>
+      <c r="AG156" s="7"/>
+      <c r="AH156" s="7"/>
+      <c r="AI156" s="7"/>
+      <c r="AJ156" s="7"/>
+      <c r="AK156" s="7"/>
+      <c r="AL156" s="7"/>
+      <c r="AM156" s="7"/>
+      <c r="AN156" s="7"/>
+    </row>
+    <row r="157" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B157" t="s">
+        <v>27</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D157" s="3"/>
+      <c r="E157" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F157" s="3"/>
+      <c r="G157" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H157" s="3"/>
+      <c r="I157" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J157" s="3"/>
+      <c r="K157" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L157" s="3"/>
+      <c r="M157" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="N157" s="3"/>
+      <c r="O157" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P157" s="3"/>
+      <c r="Q157" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="R157" s="2"/>
+      <c r="S157" s="3"/>
+      <c r="T157" s="3"/>
+      <c r="U157" s="3"/>
+      <c r="V157" s="3"/>
+      <c r="W157" s="3"/>
+      <c r="X157" s="3"/>
+      <c r="Y157" s="3"/>
+      <c r="Z157" s="3"/>
+      <c r="AA157" s="3"/>
+      <c r="AB157" s="3"/>
+      <c r="AC157" s="3"/>
+      <c r="AD157" s="3"/>
+      <c r="AE157" s="3"/>
+      <c r="AF157" s="3"/>
+      <c r="AG157" s="3"/>
+      <c r="AH157" s="3"/>
+      <c r="AI157" s="3"/>
+      <c r="AJ157" s="3"/>
+      <c r="AK157" s="3"/>
+      <c r="AL157" s="3"/>
+      <c r="AM157" s="3"/>
+      <c r="AN157" s="3"/>
+    </row>
+    <row r="158" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B158" t="s">
+        <v>26</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D158" s="3"/>
+      <c r="E158" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F158" s="3"/>
+      <c r="G158" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H158" s="3"/>
+      <c r="I158" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J158" s="3"/>
+      <c r="K158" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L158" s="3"/>
+      <c r="M158" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N158" s="3"/>
+      <c r="O158" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="P158" s="3"/>
+      <c r="Q158" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R158" s="2"/>
+      <c r="S158" s="3"/>
+      <c r="T158" s="3"/>
+      <c r="U158" s="3"/>
+      <c r="V158" s="3"/>
+      <c r="W158" s="3"/>
+      <c r="X158" s="3"/>
+      <c r="Y158" s="3"/>
+      <c r="Z158" s="3"/>
+      <c r="AA158" s="3"/>
+      <c r="AB158" s="3"/>
+      <c r="AC158" s="3"/>
+      <c r="AD158" s="3"/>
+      <c r="AE158" s="3"/>
+      <c r="AF158" s="3"/>
+      <c r="AG158" s="3"/>
+      <c r="AH158" s="3"/>
+      <c r="AI158" s="3"/>
+      <c r="AJ158" s="3"/>
+      <c r="AK158" s="3"/>
+      <c r="AL158" s="3"/>
+      <c r="AM158" s="3"/>
+      <c r="AN158" s="3"/>
+    </row>
+    <row r="159" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B159" t="s">
+        <v>25</v>
+      </c>
+      <c r="C159" t="s">
+        <v>1</v>
+      </c>
+      <c r="D159" t="s">
+        <v>13</v>
+      </c>
+      <c r="E159" t="s">
+        <v>1</v>
+      </c>
+      <c r="F159" t="s">
+        <v>13</v>
+      </c>
+      <c r="G159" t="s">
+        <v>1</v>
+      </c>
+      <c r="H159" t="s">
+        <v>13</v>
+      </c>
+      <c r="I159" t="s">
+        <v>1</v>
+      </c>
+      <c r="J159" t="s">
+        <v>13</v>
+      </c>
+      <c r="K159" t="s">
+        <v>1</v>
+      </c>
+      <c r="L159" t="s">
+        <v>13</v>
+      </c>
+      <c r="M159" t="s">
+        <v>1</v>
+      </c>
+      <c r="N159" t="s">
+        <v>13</v>
+      </c>
+      <c r="O159" t="s">
+        <v>1</v>
+      </c>
+      <c r="P159" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q159" t="s">
+        <v>1</v>
+      </c>
+      <c r="R159" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="160" spans="2:40" x14ac:dyDescent="0.3">
+      <c r="B160" t="s">
+        <v>4</v>
+      </c>
+      <c r="C160">
+        <v>686</v>
+      </c>
+      <c r="D160">
+        <v>887</v>
+      </c>
+      <c r="E160">
+        <v>2286</v>
+      </c>
+      <c r="F160">
+        <v>2485</v>
+      </c>
+      <c r="G160">
+        <v>601</v>
+      </c>
+      <c r="H160">
+        <v>601</v>
+      </c>
+      <c r="I160">
+        <v>266</v>
+      </c>
+      <c r="J160">
+        <v>266</v>
+      </c>
+      <c r="K160">
+        <v>160</v>
+      </c>
+      <c r="L160">
+        <v>160</v>
+      </c>
+      <c r="M160">
+        <v>2196</v>
+      </c>
+      <c r="N160">
+        <v>2026</v>
+      </c>
+      <c r="O160">
+        <v>218</v>
+      </c>
+      <c r="P160">
+        <v>185</v>
+      </c>
+      <c r="Q160">
+        <v>6234</v>
+      </c>
+      <c r="R160">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="161" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B161" t="s">
+        <v>59</v>
+      </c>
+      <c r="C161">
+        <v>666084</v>
+      </c>
+      <c r="D161">
+        <v>685356</v>
+      </c>
+      <c r="E161">
+        <v>161495</v>
+      </c>
+      <c r="F161">
+        <v>163489</v>
+      </c>
+      <c r="G161">
+        <v>124482</v>
+      </c>
+      <c r="H161">
+        <v>124893</v>
+      </c>
+      <c r="I161">
+        <v>30175</v>
+      </c>
+      <c r="J161">
+        <v>30241</v>
+      </c>
+      <c r="K161">
+        <v>12228</v>
+      </c>
+      <c r="L161">
+        <v>12228</v>
+      </c>
+      <c r="M161">
+        <v>91107</v>
+      </c>
+      <c r="N161">
+        <v>95491</v>
+      </c>
+      <c r="O161">
+        <v>9273</v>
+      </c>
+      <c r="P161">
+        <v>9655</v>
+      </c>
+      <c r="Q161">
+        <v>54788</v>
+      </c>
+      <c r="R161">
+        <v>69404</v>
+      </c>
+    </row>
+    <row r="162" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B162" t="s">
+        <v>3</v>
+      </c>
+      <c r="C162">
+        <f t="shared" ref="C162:L162" si="12">C160+C161</f>
+        <v>666770</v>
+      </c>
+      <c r="D162">
+        <f t="shared" si="12"/>
+        <v>686243</v>
+      </c>
+      <c r="E162">
+        <f t="shared" si="12"/>
+        <v>163781</v>
+      </c>
+      <c r="F162">
+        <f t="shared" si="12"/>
+        <v>165974</v>
+      </c>
+      <c r="G162">
+        <f t="shared" si="12"/>
+        <v>125083</v>
+      </c>
+      <c r="H162">
+        <f t="shared" si="12"/>
+        <v>125494</v>
+      </c>
+      <c r="I162">
+        <f t="shared" si="12"/>
+        <v>30441</v>
+      </c>
+      <c r="J162">
+        <f t="shared" si="12"/>
+        <v>30507</v>
+      </c>
+      <c r="K162">
+        <f t="shared" si="12"/>
+        <v>12388</v>
+      </c>
+      <c r="L162">
+        <f t="shared" si="12"/>
+        <v>12388</v>
+      </c>
+      <c r="M162">
+        <f t="shared" ref="M162:N162" si="13">M160+M161</f>
+        <v>93303</v>
+      </c>
+      <c r="N162">
+        <f t="shared" si="13"/>
+        <v>97517</v>
+      </c>
+      <c r="O162">
+        <f t="shared" ref="O162:R162" si="14">O160+O161</f>
+        <v>9491</v>
+      </c>
+      <c r="P162">
+        <f t="shared" si="14"/>
+        <v>9840</v>
+      </c>
+      <c r="Q162">
+        <f t="shared" si="14"/>
+        <v>61022</v>
+      </c>
+      <c r="R162">
+        <f t="shared" si="14"/>
+        <v>71459</v>
+      </c>
+    </row>
+    <row r="163" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B163" t="s">
+        <v>60</v>
+      </c>
+      <c r="C163">
+        <f t="shared" ref="C163:L163" si="15">IFERROR(C161/C162, 0)</f>
+        <v>0.99897115947028214</v>
+      </c>
+      <c r="D163">
+        <f t="shared" si="15"/>
+        <v>0.99870745493943103</v>
+      </c>
+      <c r="E163">
+        <f t="shared" si="15"/>
+        <v>0.98604233702322008</v>
+      </c>
+      <c r="F163">
+        <f t="shared" si="15"/>
+        <v>0.98502777543470665</v>
+      </c>
+      <c r="G163">
+        <f t="shared" si="15"/>
+        <v>0.99519519039357862</v>
+      </c>
+      <c r="H163">
+        <f t="shared" si="15"/>
+        <v>0.99521092641879294</v>
+      </c>
+      <c r="I163">
+        <f t="shared" si="15"/>
+        <v>0.99126178509247398</v>
+      </c>
+      <c r="J163">
+        <f t="shared" si="15"/>
+        <v>0.99128068967777883</v>
+      </c>
+      <c r="K163">
+        <f t="shared" si="15"/>
+        <v>0.98708427510494023</v>
+      </c>
+      <c r="L163">
+        <f t="shared" si="15"/>
+        <v>0.98708427510494023</v>
+      </c>
+      <c r="M163">
+        <f t="shared" ref="M163:N163" si="16">IFERROR(M161/M162, 0)</f>
+        <v>0.97646377929970096</v>
+      </c>
+      <c r="N163">
+        <f t="shared" si="16"/>
+        <v>0.979224135278977</v>
+      </c>
+      <c r="O163">
+        <f t="shared" ref="O163:R163" si="17">IFERROR(O161/O162, 0)</f>
+        <v>0.977030871351807</v>
+      </c>
+      <c r="P163">
+        <f t="shared" si="17"/>
+        <v>0.98119918699186992</v>
+      </c>
+      <c r="Q163">
+        <f t="shared" si="17"/>
+        <v>0.89784012323424334</v>
+      </c>
+      <c r="R163">
+        <f t="shared" si="17"/>
+        <v>0.97124225080115867</v>
+      </c>
+    </row>
+    <row r="164" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B164" t="s">
+        <v>61</v>
+      </c>
+      <c r="C164">
+        <f t="shared" ref="C164:L164" si="18">IFERROR(C160/C162, 0)</f>
+        <v>1.0288405297178937E-3</v>
+      </c>
+      <c r="D164">
+        <f t="shared" si="18"/>
+        <v>1.2925450605689238E-3</v>
+      </c>
+      <c r="E164">
+        <f t="shared" si="18"/>
+        <v>1.3957662976779969E-2</v>
+      </c>
+      <c r="F164">
+        <f t="shared" si="18"/>
+        <v>1.497222456529336E-2</v>
+      </c>
+      <c r="G164">
+        <f t="shared" si="18"/>
+        <v>4.8048096064213361E-3</v>
+      </c>
+      <c r="H164">
+        <f t="shared" si="18"/>
+        <v>4.7890735812070699E-3</v>
+      </c>
+      <c r="I164">
+        <f t="shared" si="18"/>
+        <v>8.7382149075260346E-3</v>
+      </c>
+      <c r="J164">
+        <f t="shared" si="18"/>
+        <v>8.7193103222211292E-3</v>
+      </c>
+      <c r="K164">
+        <f t="shared" si="18"/>
+        <v>1.2915724895059735E-2</v>
+      </c>
+      <c r="L164">
+        <f t="shared" si="18"/>
+        <v>1.2915724895059735E-2</v>
+      </c>
+      <c r="M164">
+        <f t="shared" ref="M164:N164" si="19">IFERROR(M160/M162, 0)</f>
+        <v>2.3536220700299027E-2</v>
+      </c>
+      <c r="N164">
+        <f t="shared" si="19"/>
+        <v>2.0775864721023E-2</v>
+      </c>
+      <c r="O164">
+        <f t="shared" ref="O164:R164" si="20">IFERROR(O160/O162, 0)</f>
+        <v>2.2969128648193025E-2</v>
+      </c>
+      <c r="P164">
+        <f t="shared" si="20"/>
+        <v>1.8800813008130083E-2</v>
+      </c>
+      <c r="Q164">
+        <f t="shared" si="20"/>
+        <v>0.10215987676575661</v>
+      </c>
+      <c r="R164">
+        <f t="shared" si="20"/>
+        <v>2.8757749198841293E-2</v>
+      </c>
+    </row>
+    <row r="165" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B165" t="s">
+        <v>58</v>
+      </c>
+      <c r="C165">
+        <v>128</v>
+      </c>
+      <c r="D165">
+        <v>128</v>
+      </c>
+      <c r="E165">
+        <v>128</v>
+      </c>
+      <c r="F165">
+        <v>128</v>
+      </c>
+      <c r="G165">
+        <v>128</v>
+      </c>
+      <c r="H165">
+        <v>128</v>
+      </c>
+      <c r="I165">
+        <v>128</v>
+      </c>
+      <c r="J165">
+        <v>128</v>
+      </c>
+      <c r="K165">
+        <v>128</v>
+      </c>
+      <c r="L165">
+        <v>128</v>
+      </c>
+      <c r="M165">
+        <v>128</v>
+      </c>
+      <c r="N165">
+        <v>128</v>
+      </c>
+      <c r="O165">
+        <v>128</v>
+      </c>
+      <c r="P165">
+        <v>128</v>
+      </c>
+      <c r="Q165">
+        <v>128</v>
+      </c>
+      <c r="R165">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="166" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B166" t="s">
+        <v>9</v>
+      </c>
+      <c r="C166">
+        <v>686</v>
+      </c>
+      <c r="D166">
+        <v>686</v>
+      </c>
+      <c r="E166">
+        <v>2280</v>
+      </c>
+      <c r="F166">
+        <v>2280</v>
+      </c>
+      <c r="G166">
+        <v>601</v>
+      </c>
+      <c r="H166">
+        <v>601</v>
+      </c>
+      <c r="I166">
+        <v>266</v>
+      </c>
+      <c r="J166">
+        <v>266</v>
+      </c>
+      <c r="K166">
+        <v>160</v>
+      </c>
+      <c r="L166">
+        <v>160</v>
+      </c>
+      <c r="M166">
+        <v>1892</v>
+      </c>
+      <c r="N166">
+        <v>1892</v>
+      </c>
+      <c r="O166">
+        <v>159</v>
+      </c>
+      <c r="P166">
+        <v>159</v>
+      </c>
+      <c r="Q166">
+        <v>640</v>
+      </c>
+      <c r="R166">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="167" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B167" t="s">
+        <v>8</v>
+      </c>
+      <c r="C167">
+        <f t="shared" ref="C167:L167" si="21">IFERROR(C166/C160, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="D167">
+        <f t="shared" si="21"/>
+        <v>0.77339346110484786</v>
+      </c>
+      <c r="E167">
+        <f t="shared" si="21"/>
+        <v>0.99737532808398954</v>
+      </c>
+      <c r="F167">
+        <f t="shared" si="21"/>
+        <v>0.91750503018108653</v>
+      </c>
+      <c r="G167">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="H167">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="I167">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="J167">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="K167">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="L167">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="M167">
+        <f t="shared" ref="M167:N167" si="22">IFERROR(M166/M160, 0)</f>
+        <v>0.86156648451730422</v>
+      </c>
+      <c r="N167">
+        <f t="shared" si="22"/>
+        <v>0.93385982230997033</v>
+      </c>
+      <c r="O167">
+        <f t="shared" ref="O167:R167" si="23">IFERROR(O166/O160, 0)</f>
+        <v>0.72935779816513757</v>
+      </c>
+      <c r="P167">
+        <f t="shared" si="23"/>
+        <v>0.85945945945945945</v>
+      </c>
+      <c r="Q167">
+        <f t="shared" si="23"/>
+        <v>0.10266281681103626</v>
+      </c>
+      <c r="R167">
+        <f t="shared" si="23"/>
+        <v>0.31143552311435524</v>
+      </c>
+    </row>
+    <row r="168" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B168" t="s">
+        <v>5</v>
+      </c>
+      <c r="C168">
+        <v>10974</v>
+      </c>
+      <c r="D168">
+        <v>10974</v>
+      </c>
+      <c r="E168">
+        <v>36476</v>
+      </c>
+      <c r="F168">
+        <v>36476</v>
+      </c>
+      <c r="G168">
+        <v>9604</v>
+      </c>
+      <c r="H168">
+        <v>9604</v>
+      </c>
+      <c r="I168">
+        <v>4253</v>
+      </c>
+      <c r="J168">
+        <v>4253</v>
+      </c>
+      <c r="K168">
+        <v>2559</v>
+      </c>
+      <c r="L168">
+        <v>2559</v>
+      </c>
+      <c r="M168">
+        <v>30269</v>
+      </c>
+      <c r="N168">
+        <v>30269</v>
+      </c>
+      <c r="O168">
+        <v>2541</v>
+      </c>
+      <c r="P168">
+        <v>2541</v>
+      </c>
+      <c r="Q168">
+        <v>10240</v>
+      </c>
+      <c r="R168">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="169" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B169" t="s">
+        <v>6</v>
+      </c>
+      <c r="C169">
+        <v>10974</v>
+      </c>
+      <c r="D169">
+        <v>10974</v>
+      </c>
+      <c r="E169">
+        <v>36476</v>
+      </c>
+      <c r="F169">
+        <v>36476</v>
+      </c>
+      <c r="G169">
+        <v>9604</v>
+      </c>
+      <c r="H169">
+        <v>9604</v>
+      </c>
+      <c r="I169">
+        <v>4253</v>
+      </c>
+      <c r="J169">
+        <v>4253</v>
+      </c>
+      <c r="K169">
+        <v>2559</v>
+      </c>
+      <c r="L169">
+        <v>2559</v>
+      </c>
+      <c r="M169">
+        <v>30269</v>
+      </c>
+      <c r="N169">
+        <v>30269</v>
+      </c>
+      <c r="O169">
+        <v>2541</v>
+      </c>
+      <c r="P169">
+        <v>2541</v>
+      </c>
+      <c r="Q169">
+        <v>10240</v>
+      </c>
+      <c r="R169">
+        <v>10240</v>
+      </c>
+    </row>
+    <row r="170" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B170" t="s">
+        <v>7</v>
+      </c>
+      <c r="C170">
+        <v>3.55936820230424E-3</v>
+      </c>
+      <c r="D170">
+        <v>3.55936820230424E-3</v>
+      </c>
+      <c r="E170">
+        <v>1.0716283547529299E-4</v>
+      </c>
+      <c r="F170">
+        <v>1.0716283547529299E-4</v>
+      </c>
+      <c r="G170">
+        <v>9.2440311469554599E-4</v>
+      </c>
+      <c r="H170">
+        <v>9.2440311469554599E-4</v>
+      </c>
+      <c r="I170">
+        <v>1.3588007392079399E-3</v>
+      </c>
+      <c r="J170">
+        <v>1.3588007392079399E-3</v>
+      </c>
+      <c r="K170">
+        <v>1.24975547764435E-3</v>
+      </c>
+      <c r="L170">
+        <v>1.24975547764435E-3</v>
+      </c>
+      <c r="M170">
+        <v>9.2440311469554599E-4</v>
+      </c>
+      <c r="N170">
+        <v>9.2440311469554599E-4</v>
+      </c>
+      <c r="O170">
+        <v>9.2440311469554599E-4</v>
+      </c>
+      <c r="P170">
+        <v>9.2440311469554599E-4</v>
+      </c>
+      <c r="Q170">
+        <v>8.1568020619973106E-2</v>
+      </c>
+      <c r="R170">
+        <v>8.1568020619973106E-2</v>
+      </c>
+      <c r="AE170" s="1"/>
+      <c r="AF170" s="1"/>
+    </row>
+    <row r="171" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B171" t="s">
+        <v>56</v>
+      </c>
+      <c r="C171">
+        <v>4</v>
+      </c>
+      <c r="D171">
+        <v>4</v>
+      </c>
+      <c r="E171">
+        <v>4</v>
+      </c>
+      <c r="F171">
+        <v>4</v>
+      </c>
+      <c r="G171">
+        <v>4</v>
+      </c>
+      <c r="H171">
+        <v>4</v>
+      </c>
+      <c r="I171">
+        <v>4</v>
+      </c>
+      <c r="J171">
+        <v>4</v>
+      </c>
+      <c r="K171">
+        <v>4</v>
+      </c>
+      <c r="L171">
+        <v>4</v>
+      </c>
+      <c r="M171">
+        <v>4</v>
+      </c>
+      <c r="N171">
+        <v>4</v>
+      </c>
+      <c r="O171">
+        <v>4</v>
+      </c>
+      <c r="P171">
+        <v>4</v>
+      </c>
+      <c r="Q171">
+        <v>4</v>
+      </c>
+      <c r="R171">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B172" t="s">
+        <v>77</v>
+      </c>
+      <c r="C172">
+        <v>0.99458258408401501</v>
+      </c>
+      <c r="D172">
+        <v>0.99458258408401501</v>
+      </c>
+      <c r="E172">
+        <v>0.99938137434990404</v>
+      </c>
+      <c r="F172">
+        <v>0.99938137434990404</v>
+      </c>
+      <c r="G172">
+        <v>0.99939327039289805</v>
+      </c>
+      <c r="H172">
+        <v>0.99939327039289805</v>
+      </c>
+      <c r="I172">
+        <v>0.97656686079871402</v>
+      </c>
+      <c r="J172">
+        <v>0.97656686079871402</v>
+      </c>
+      <c r="K172">
+        <v>0.92697750688552205</v>
+      </c>
+      <c r="L172">
+        <v>0.92697750688552205</v>
+      </c>
+      <c r="M172">
+        <v>0.65126395359005196</v>
+      </c>
+      <c r="N172">
+        <v>0.65126395359005196</v>
+      </c>
+      <c r="O172">
+        <v>-0.75453921168305105</v>
+      </c>
+      <c r="P172">
+        <v>-0.75453921168305105</v>
+      </c>
+      <c r="Q172">
+        <v>-0.59031282106315597</v>
+      </c>
+      <c r="R172">
+        <v>-0.59031282106315597</v>
+      </c>
+    </row>
+    <row r="176" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B176" t="s">
+        <v>27</v>
+      </c>
+      <c r="C176" t="s">
+        <v>28</v>
+      </c>
+      <c r="D176" t="s">
+        <v>32</v>
+      </c>
+      <c r="E176" t="s">
+        <v>32</v>
+      </c>
+      <c r="F176" t="s">
+        <v>32</v>
+      </c>
+      <c r="G176" t="s">
+        <v>32</v>
+      </c>
+      <c r="H176" t="s">
+        <v>32</v>
+      </c>
+      <c r="I176" t="s">
+        <v>71</v>
+      </c>
+      <c r="J176" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="177" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B177" t="s">
+        <v>26</v>
+      </c>
+      <c r="C177" t="s">
+        <v>16</v>
+      </c>
+      <c r="D177" t="s">
+        <v>68</v>
+      </c>
+      <c r="E177" t="s">
+        <v>19</v>
+      </c>
+      <c r="F177" t="s">
+        <v>65</v>
+      </c>
+      <c r="G177" t="s">
+        <v>67</v>
+      </c>
+      <c r="H177" t="s">
+        <v>73</v>
+      </c>
+      <c r="I177" t="s">
+        <v>70</v>
+      </c>
+      <c r="J177" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="178" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B178" t="s">
+        <v>50</v>
+      </c>
+      <c r="C178">
+        <f>C163*100</f>
+        <v>99.897115947028212</v>
+      </c>
+      <c r="D178">
+        <f>E163*100</f>
+        <v>98.604233702322006</v>
+      </c>
+      <c r="E178">
+        <f>G163*100</f>
+        <v>99.51951903935786</v>
+      </c>
+      <c r="F178">
+        <f>I163*100</f>
+        <v>99.126178509247396</v>
+      </c>
+      <c r="G178">
+        <f>K163*100</f>
+        <v>98.708427510494019</v>
+      </c>
+      <c r="H178">
+        <f>M163*100</f>
+        <v>97.6463779299701</v>
+      </c>
+      <c r="I178">
+        <f>O163*100</f>
+        <v>97.703087135180695</v>
+      </c>
+      <c r="J178">
+        <f>Q163*100</f>
+        <v>89.784012323424335</v>
+      </c>
+    </row>
+    <row r="179" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B179" t="s">
+        <v>51</v>
+      </c>
+      <c r="C179">
+        <f>D163*100</f>
+        <v>99.870745493943105</v>
+      </c>
+      <c r="D179">
+        <f>F163*100</f>
+        <v>98.502777543470671</v>
+      </c>
+      <c r="E179">
+        <f>H163*100</f>
+        <v>99.521092641879292</v>
+      </c>
+      <c r="F179">
+        <f>J163*100</f>
+        <v>99.128068967777878</v>
+      </c>
+      <c r="G179">
+        <f>L163*100</f>
+        <v>98.708427510494019</v>
+      </c>
+      <c r="H179">
+        <f>N163*100</f>
+        <v>97.922413527897703</v>
+      </c>
+      <c r="I179">
+        <f>P163*100</f>
+        <v>98.119918699186996</v>
+      </c>
+      <c r="J179">
+        <f>R163*100</f>
+        <v>97.124225080115863</v>
+      </c>
+    </row>
+    <row r="180" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B180" t="s">
+        <v>52</v>
+      </c>
+      <c r="C180">
+        <f>IFERROR(((C160-D160)/C160)*100, 0)</f>
+        <v>-29.300291545189506</v>
+      </c>
+      <c r="D180">
+        <f>IFERROR(((E160-F160)/E160)*100, 0)</f>
+        <v>-8.7051618547681535</v>
+      </c>
+      <c r="E180">
+        <f>IFERROR(((G160-H160)/G160)*100, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="F180">
+        <f>IFERROR(((I160-J160)/I160)*100, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="G180">
+        <f>IFERROR(((K160-L160)/K160)*100, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="H180">
+        <f>IFERROR(((M160-N160)/M160)*100, 0)</f>
+        <v>7.7413479052823311</v>
+      </c>
+      <c r="I180">
+        <f>IFERROR(((O160-P160)/O160)*100, 0)</f>
+        <v>15.137614678899084</v>
+      </c>
+      <c r="J180">
+        <f>IFERROR(((Q160-R160)/Q160)*100, 0)</f>
+        <v>67.035611164581326</v>
+      </c>
+    </row>
+    <row r="181" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B181" t="s">
+        <v>62</v>
+      </c>
+      <c r="C181">
+        <f>C167</f>
+        <v>1</v>
+      </c>
+      <c r="D181">
+        <f>E167</f>
+        <v>0.99737532808398954</v>
+      </c>
+      <c r="E181">
+        <f>G167</f>
+        <v>1</v>
+      </c>
+      <c r="F181">
+        <f>I167</f>
+        <v>1</v>
+      </c>
+      <c r="G181">
+        <f>K167</f>
+        <v>1</v>
+      </c>
+      <c r="H181">
+        <f>M167</f>
+        <v>0.86156648451730422</v>
+      </c>
+      <c r="I181">
+        <f>O167</f>
+        <v>0.72935779816513757</v>
+      </c>
+      <c r="J181">
+        <f>Q167</f>
+        <v>0.10266281681103626</v>
+      </c>
+    </row>
+    <row r="182" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B182" t="s">
+        <v>63</v>
+      </c>
+      <c r="C182">
+        <f>D167</f>
+        <v>0.77339346110484786</v>
+      </c>
+      <c r="D182">
+        <f>F167</f>
+        <v>0.91750503018108653</v>
+      </c>
+      <c r="E182">
+        <f>H167</f>
+        <v>1</v>
+      </c>
+      <c r="F182">
+        <f>J167</f>
+        <v>1</v>
+      </c>
+      <c r="G182">
+        <f>L167</f>
+        <v>1</v>
+      </c>
+      <c r="H182">
+        <f>N167</f>
+        <v>0.93385982230997033</v>
+      </c>
+      <c r="I182">
+        <f>P167</f>
+        <v>0.85945945945945945</v>
+      </c>
+      <c r="J182">
+        <f>R167</f>
+        <v>0.31143552311435524</v>
+      </c>
+    </row>
+    <row r="183" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B183" t="s">
+        <v>77</v>
+      </c>
+      <c r="C183">
+        <f>C172</f>
+        <v>0.99458258408401501</v>
+      </c>
+      <c r="D183">
+        <f>E172</f>
+        <v>0.99938137434990404</v>
+      </c>
+      <c r="E183">
+        <f>G172</f>
+        <v>0.99939327039289805</v>
+      </c>
+      <c r="F183">
+        <f>I172</f>
+        <v>0.97656686079871402</v>
+      </c>
+      <c r="G183">
+        <f>K172</f>
+        <v>0.92697750688552205</v>
+      </c>
+      <c r="H183">
+        <f>M172</f>
+        <v>0.65126395359005196</v>
+      </c>
+      <c r="I183">
+        <f>O172</f>
+        <v>-0.75453921168305105</v>
+      </c>
+      <c r="J183">
+        <f>Q172</f>
+        <v>-0.59031282106315597</v>
+      </c>
+    </row>
+    <row r="184" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B184" t="s">
+        <v>79</v>
+      </c>
+      <c r="C184">
+        <v>0.8</v>
+      </c>
+      <c r="D184">
+        <v>0.8</v>
+      </c>
+      <c r="E184">
+        <v>0.8</v>
+      </c>
+      <c r="F184">
+        <v>0.8</v>
+      </c>
+      <c r="G184">
+        <v>0.8</v>
+      </c>
+      <c r="H184">
+        <v>0.8</v>
+      </c>
+      <c r="I184">
+        <v>0.8</v>
+      </c>
+      <c r="J184">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="185" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B185" t="s">
+        <v>79</v>
+      </c>
+      <c r="C185">
+        <v>-0.8</v>
+      </c>
+      <c r="D185">
+        <v>-0.8</v>
+      </c>
+      <c r="E185">
+        <v>-0.8</v>
+      </c>
+      <c r="F185">
+        <v>-0.8</v>
+      </c>
+      <c r="G185">
+        <v>-0.8</v>
+      </c>
+      <c r="H185">
+        <v>-0.8</v>
+      </c>
+      <c r="I185">
+        <v>-0.8</v>
+      </c>
+      <c r="J185">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="187" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B187" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C187" t="s">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="78">
-    <mergeCell ref="AK86:AL86"/>
-    <mergeCell ref="AM86:AN86"/>
-    <mergeCell ref="AA86:AB86"/>
-    <mergeCell ref="AC86:AD86"/>
-    <mergeCell ref="AE86:AF86"/>
-    <mergeCell ref="AG86:AH86"/>
-    <mergeCell ref="AI86:AJ86"/>
+  <mergeCells count="115">
+    <mergeCell ref="AK158:AL158"/>
+    <mergeCell ref="AM158:AN158"/>
+    <mergeCell ref="B156:P156"/>
+    <mergeCell ref="AA158:AB158"/>
+    <mergeCell ref="AC158:AD158"/>
+    <mergeCell ref="AE158:AF158"/>
+    <mergeCell ref="AG158:AH158"/>
+    <mergeCell ref="AI158:AJ158"/>
+    <mergeCell ref="AG157:AH157"/>
+    <mergeCell ref="AI157:AJ157"/>
+    <mergeCell ref="AK157:AL157"/>
+    <mergeCell ref="AM157:AN157"/>
+    <mergeCell ref="C158:D158"/>
+    <mergeCell ref="E158:F158"/>
+    <mergeCell ref="G158:H158"/>
+    <mergeCell ref="I158:J158"/>
+    <mergeCell ref="K158:L158"/>
+    <mergeCell ref="M158:N158"/>
+    <mergeCell ref="O158:P158"/>
+    <mergeCell ref="S158:T158"/>
+    <mergeCell ref="U158:V158"/>
+    <mergeCell ref="W158:X158"/>
+    <mergeCell ref="Y158:Z158"/>
+    <mergeCell ref="C157:D157"/>
+    <mergeCell ref="E157:F157"/>
+    <mergeCell ref="G157:H157"/>
+    <mergeCell ref="I157:J157"/>
+    <mergeCell ref="K157:L157"/>
+    <mergeCell ref="M157:N157"/>
+    <mergeCell ref="O157:P157"/>
+    <mergeCell ref="S157:T157"/>
+    <mergeCell ref="U157:V157"/>
+    <mergeCell ref="W157:X157"/>
+    <mergeCell ref="Y157:Z157"/>
+    <mergeCell ref="AA157:AB157"/>
+    <mergeCell ref="AC157:AD157"/>
+    <mergeCell ref="AE157:AF157"/>
+    <mergeCell ref="AM4:AN4"/>
+    <mergeCell ref="AA4:AB4"/>
+    <mergeCell ref="AC4:AD4"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AG4:AH4"/>
+    <mergeCell ref="AI4:AJ4"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="W3:X3"/>
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="U4:V4"/>
+    <mergeCell ref="W4:X4"/>
+    <mergeCell ref="B2:AN2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="AG3:AH3"/>
+    <mergeCell ref="AI3:AJ3"/>
+    <mergeCell ref="AK3:AL3"/>
+    <mergeCell ref="AM3:AN3"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="B84:AN84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="E85:F85"/>
+    <mergeCell ref="G85:H85"/>
+    <mergeCell ref="I85:J85"/>
+    <mergeCell ref="K85:L85"/>
+    <mergeCell ref="M85:N85"/>
+    <mergeCell ref="O85:P85"/>
+    <mergeCell ref="Q85:R85"/>
+    <mergeCell ref="S85:T85"/>
+    <mergeCell ref="U85:V85"/>
+    <mergeCell ref="W85:X85"/>
+    <mergeCell ref="Y85:Z85"/>
+    <mergeCell ref="AA85:AB85"/>
+    <mergeCell ref="AC85:AD85"/>
+    <mergeCell ref="AE85:AF85"/>
     <mergeCell ref="AG85:AH85"/>
     <mergeCell ref="AI85:AJ85"/>
     <mergeCell ref="AK85:AL85"/>
@@ -19866,61 +22909,13 @@
     <mergeCell ref="U86:V86"/>
     <mergeCell ref="W86:X86"/>
     <mergeCell ref="Y86:Z86"/>
-    <mergeCell ref="B84:AN84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="E85:F85"/>
-    <mergeCell ref="G85:H85"/>
-    <mergeCell ref="I85:J85"/>
-    <mergeCell ref="K85:L85"/>
-    <mergeCell ref="M85:N85"/>
-    <mergeCell ref="O85:P85"/>
-    <mergeCell ref="Q85:R85"/>
-    <mergeCell ref="S85:T85"/>
-    <mergeCell ref="U85:V85"/>
-    <mergeCell ref="W85:X85"/>
-    <mergeCell ref="Y85:Z85"/>
-    <mergeCell ref="AA85:AB85"/>
-    <mergeCell ref="AC85:AD85"/>
-    <mergeCell ref="AE85:AF85"/>
-    <mergeCell ref="B2:AN2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="W3:X3"/>
-    <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AG3:AH3"/>
-    <mergeCell ref="AI3:AJ3"/>
-    <mergeCell ref="AK3:AL3"/>
-    <mergeCell ref="AM3:AN3"/>
-    <mergeCell ref="AC3:AD3"/>
-    <mergeCell ref="AE3:AF3"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="U4:V4"/>
-    <mergeCell ref="W4:X4"/>
-    <mergeCell ref="AM4:AN4"/>
-    <mergeCell ref="AA4:AB4"/>
-    <mergeCell ref="AC4:AD4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AG4:AH4"/>
-    <mergeCell ref="AI4:AJ4"/>
-    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="AK86:AL86"/>
+    <mergeCell ref="AM86:AN86"/>
+    <mergeCell ref="AA86:AB86"/>
+    <mergeCell ref="AC86:AD86"/>
+    <mergeCell ref="AE86:AF86"/>
+    <mergeCell ref="AG86:AH86"/>
+    <mergeCell ref="AI86:AJ86"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/docs/cacheBandit_metrics.xlsx
+++ b/docs/cacheBandit_metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91988\Documents\Amruth\Files\Git\cacheBandit\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675385A6-149D-4854-8554-E40826A3A93C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F943A65-7185-4BB2-83DA-98580442DB87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C4CDEA3B-1686-49FD-8414-9D1FD93CDC23}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="83">
   <si>
     <t>Thread Count</t>
   </si>
@@ -267,6 +267,15 @@
   <si>
     <t>Correlation positive lim</t>
   </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>The reason for this is: Diagonal matrices are purely streaming in the case of SpMV, as there is no re-use of cache lines across warps. This leads to the absence of thrashing, resulting in the random part of the global policy negatively impacting the cache usage.</t>
+  </si>
+  <si>
+    <t>LRU</t>
+  </si>
 </sst>
 </file>
 
@@ -325,12 +334,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -343,8 +353,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -885,6 +893,709 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Cache Efficiency</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$109</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>LRU</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$105:$U$105</c:f>
+              <c:strCache>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>bcsstk10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>bcsstk13</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bcsstk17</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>c8_mat11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cq9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>fv1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>kl02</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>lhr34c</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>pdb1HYS</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>psmigr_1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>wiki-Vote</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>p2p-Gnutella04</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>ca-HepTh</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>as-735</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>amazon0312</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>sinc15</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Average</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$109:$U$109</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.6807113925229294E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.5780260442610121E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.3561006894340225E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.836952380952381</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.40653454740224959</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.22234762979683972</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.8917246713070378E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.10119047619047619</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.150157813444362E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.14255890247539516</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.3030685161832703</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.39307622869439407</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6B79-45CA-A76D-2552527AE457}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$110</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CacheBandit</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$105:$U$105</c:f>
+              <c:strCache>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>bcsstk10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>bcsstk13</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>bcsstk17</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>c8_mat11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cq9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>fv1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>kl02</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>lhr34c</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>pdb1HYS</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>psmigr_1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>wiki-Vote</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>p2p-Gnutella04</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>ca-HepTh</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>as-735</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>amazon0312</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>sinc15</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Average</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$110:$U$110</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.60267111853088484</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.2142629735752945</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.478890229191798E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.87425387982491043</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.4882075471698113</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.86495726495726499</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.21963824289405684</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7.5319926873857398E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.5786516853932584</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.62454697134445358</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6B79-45CA-A76D-2552527AE457}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1038553776"/>
+        <c:axId val="1038552336"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1038553776"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1600"/>
+                  <a:t>Mtrix</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1038552336"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1038552336"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Efficiency (normalized)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1038553776"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:minorUnit val="5.000000000000001E-2"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -3125,9 +3836,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$C$23:$R$23</c:f>
+              <c:f>Sheet1!$C$23:$U$23</c:f>
               <c:strCache>
-                <c:ptCount val="16"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>bcsstk10</c:v>
                 </c:pt>
@@ -3175,16 +3886,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>sinc15</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Average</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$26:$R$26</c:f>
+              <c:f>Sheet1!$C$26:$U$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3232,6 +3946,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>47.625052543085324</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>34.353165863987456</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4337,7 +5054,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Baseline Cache Efficiency</c:v>
+                  <c:v>LRU</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4354,9 +5071,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$C$23:$R$23</c:f>
+              <c:f>Sheet1!$C$23:$U$23</c:f>
               <c:strCache>
-                <c:ptCount val="16"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>bcsstk10</c:v>
                 </c:pt>
@@ -4404,16 +5121,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>sinc15</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Average</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$27:$R$27</c:f>
+              <c:f>Sheet1!$C$27:$U$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -4461,6 +5181,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0.3030685161832703</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.39307622869439407</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4480,7 +5203,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>CacheBandit Cache Efficiency</c:v>
+                  <c:v>CacheBandit</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4497,9 +5220,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$C$23:$R$23</c:f>
+              <c:f>Sheet1!$C$23:$U$23</c:f>
               <c:strCache>
-                <c:ptCount val="16"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>bcsstk10</c:v>
                 </c:pt>
@@ -4547,16 +5270,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>sinc15</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Average</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$28:$R$28</c:f>
+              <c:f>Sheet1!$C$28:$U$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -4604,6 +5330,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0.5786516853932584</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.61038406266350664</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5069,9 +5798,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$C$105:$R$105</c:f>
+              <c:f>Sheet1!$C$105:$U$105</c:f>
               <c:strCache>
-                <c:ptCount val="16"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>bcsstk10</c:v>
                 </c:pt>
@@ -5119,16 +5848,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>sinc15</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Average</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$108:$R$108</c:f>
+              <c:f>Sheet1!$C$108:$U$108</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5176,6 +5908,9 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>47.625052543085324</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>36.215861874989677</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6375,6 +7110,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1558269472"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -6433,6 +7169,46 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -7295,6 +8071,509 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
   <cs:axisTitle>
@@ -11650,6 +12929,42 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>11043</xdr:colOff>
+      <xdr:row>113</xdr:row>
+      <xdr:rowOff>30921</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>77304</xdr:colOff>
+      <xdr:row>148</xdr:row>
+      <xdr:rowOff>132521</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D41E1EF9-4DBB-6BB0-7F49-FCAAEFA69685}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -11986,209 +13301,209 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:40" x14ac:dyDescent="0.3">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
-      <c r="AD2" s="4"/>
-      <c r="AE2" s="4"/>
-      <c r="AF2" s="4"/>
-      <c r="AG2" s="4"/>
-      <c r="AH2" s="4"/>
-      <c r="AI2" s="4"/>
-      <c r="AJ2" s="4"/>
-      <c r="AK2" s="4"/>
-      <c r="AL2" s="4"/>
-      <c r="AM2" s="4"/>
-      <c r="AN2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="5"/>
+      <c r="AF2" s="5"/>
+      <c r="AG2" s="5"/>
+      <c r="AH2" s="5"/>
+      <c r="AI2" s="5"/>
+      <c r="AJ2" s="5"/>
+      <c r="AK2" s="5"/>
+      <c r="AL2" s="5"/>
+      <c r="AM2" s="5"/>
+      <c r="AN2" s="5"/>
     </row>
     <row r="3" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3" t="s">
+      <c r="D3" s="4"/>
+      <c r="E3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3" t="s">
+      <c r="F3" s="4"/>
+      <c r="G3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3" t="s">
+      <c r="H3" s="4"/>
+      <c r="I3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3" t="s">
+      <c r="J3" s="4"/>
+      <c r="K3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3" t="s">
+      <c r="L3" s="4"/>
+      <c r="M3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3" t="s">
+      <c r="N3" s="4"/>
+      <c r="O3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3" t="s">
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3" t="s">
+      <c r="R3" s="4"/>
+      <c r="S3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3" t="s">
+      <c r="T3" s="4"/>
+      <c r="U3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3" t="s">
+      <c r="V3" s="4"/>
+      <c r="W3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3" t="s">
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3" t="s">
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="3" t="s">
+      <c r="AB3" s="4"/>
+      <c r="AC3" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="AD3" s="3"/>
-      <c r="AE3" s="3" t="s">
+      <c r="AD3" s="4"/>
+      <c r="AE3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AF3" s="3"/>
-      <c r="AG3" s="3" t="s">
+      <c r="AF3" s="4"/>
+      <c r="AG3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="AH3" s="3"/>
-      <c r="AI3" s="3" t="s">
+      <c r="AH3" s="4"/>
+      <c r="AI3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="AJ3" s="3"/>
-      <c r="AK3" s="3" t="s">
+      <c r="AJ3" s="4"/>
+      <c r="AK3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="AL3" s="3"/>
-      <c r="AM3" s="3" t="s">
+      <c r="AL3" s="4"/>
+      <c r="AM3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="AN3" s="3"/>
+      <c r="AN3" s="4"/>
     </row>
     <row r="4" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3" t="s">
+      <c r="D4" s="4"/>
+      <c r="E4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3" t="s">
+      <c r="F4" s="4"/>
+      <c r="G4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3" t="s">
+      <c r="H4" s="4"/>
+      <c r="I4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3" t="s">
+      <c r="J4" s="4"/>
+      <c r="K4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3" t="s">
+      <c r="L4" s="4"/>
+      <c r="M4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3" t="s">
+      <c r="N4" s="4"/>
+      <c r="O4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3" t="s">
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3" t="s">
+      <c r="R4" s="4"/>
+      <c r="S4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3" t="s">
+      <c r="T4" s="4"/>
+      <c r="U4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3" t="s">
+      <c r="V4" s="4"/>
+      <c r="W4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3" t="s">
+      <c r="X4" s="4"/>
+      <c r="Y4" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3" t="s">
+      <c r="Z4" s="4"/>
+      <c r="AA4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="AB4" s="3"/>
-      <c r="AC4" s="3" t="s">
+      <c r="AB4" s="4"/>
+      <c r="AC4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="AD4" s="3"/>
-      <c r="AE4" s="3" t="s">
+      <c r="AD4" s="4"/>
+      <c r="AE4" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="AF4" s="3"/>
-      <c r="AG4" s="3" t="s">
+      <c r="AF4" s="4"/>
+      <c r="AG4" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="AH4" s="3"/>
-      <c r="AI4" s="3" t="s">
+      <c r="AH4" s="4"/>
+      <c r="AI4" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="AJ4" s="3"/>
-      <c r="AK4" s="3" t="s">
+      <c r="AJ4" s="4"/>
+      <c r="AK4" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="AL4" s="3"/>
-      <c r="AM4" s="3" t="s">
+      <c r="AL4" s="4"/>
+      <c r="AM4" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="AN4" s="3"/>
+      <c r="AN4" s="4"/>
     </row>
     <row r="5" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
@@ -14257,209 +15572,209 @@
       </c>
     </row>
     <row r="63" spans="2:40" x14ac:dyDescent="0.3">
-      <c r="B63" s="5" t="s">
+      <c r="B63" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
-      <c r="I63" s="5"/>
-      <c r="J63" s="5"/>
-      <c r="K63" s="5"/>
-      <c r="L63" s="5"/>
-      <c r="M63" s="5"/>
-      <c r="N63" s="5"/>
-      <c r="O63" s="5"/>
-      <c r="P63" s="5"/>
-      <c r="Q63" s="5"/>
-      <c r="R63" s="5"/>
-      <c r="S63" s="5"/>
-      <c r="T63" s="5"/>
-      <c r="U63" s="5"/>
-      <c r="V63" s="5"/>
-      <c r="W63" s="5"/>
-      <c r="X63" s="5"/>
-      <c r="Y63" s="5"/>
-      <c r="Z63" s="5"/>
-      <c r="AA63" s="5"/>
-      <c r="AB63" s="5"/>
-      <c r="AC63" s="5"/>
-      <c r="AD63" s="5"/>
-      <c r="AE63" s="5"/>
-      <c r="AF63" s="5"/>
-      <c r="AG63" s="5"/>
-      <c r="AH63" s="5"/>
-      <c r="AI63" s="5"/>
-      <c r="AJ63" s="5"/>
-      <c r="AK63" s="5"/>
-      <c r="AL63" s="5"/>
-      <c r="AM63" s="5"/>
-      <c r="AN63" s="5"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
+      <c r="K63" s="6"/>
+      <c r="L63" s="6"/>
+      <c r="M63" s="6"/>
+      <c r="N63" s="6"/>
+      <c r="O63" s="6"/>
+      <c r="P63" s="6"/>
+      <c r="Q63" s="6"/>
+      <c r="R63" s="6"/>
+      <c r="S63" s="6"/>
+      <c r="T63" s="6"/>
+      <c r="U63" s="6"/>
+      <c r="V63" s="6"/>
+      <c r="W63" s="6"/>
+      <c r="X63" s="6"/>
+      <c r="Y63" s="6"/>
+      <c r="Z63" s="6"/>
+      <c r="AA63" s="6"/>
+      <c r="AB63" s="6"/>
+      <c r="AC63" s="6"/>
+      <c r="AD63" s="6"/>
+      <c r="AE63" s="6"/>
+      <c r="AF63" s="6"/>
+      <c r="AG63" s="6"/>
+      <c r="AH63" s="6"/>
+      <c r="AI63" s="6"/>
+      <c r="AJ63" s="6"/>
+      <c r="AK63" s="6"/>
+      <c r="AL63" s="6"/>
+      <c r="AM63" s="6"/>
+      <c r="AN63" s="6"/>
     </row>
     <row r="64" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>27</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3" t="s">
+      <c r="D64" s="4"/>
+      <c r="E64" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3" t="s">
+      <c r="F64" s="4"/>
+      <c r="G64" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H64" s="3"/>
-      <c r="I64" s="3" t="s">
+      <c r="H64" s="4"/>
+      <c r="I64" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J64" s="3"/>
-      <c r="K64" s="3" t="s">
+      <c r="J64" s="4"/>
+      <c r="K64" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="L64" s="3"/>
-      <c r="M64" s="3" t="s">
+      <c r="L64" s="4"/>
+      <c r="M64" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="N64" s="3"/>
-      <c r="O64" s="3" t="s">
+      <c r="N64" s="4"/>
+      <c r="O64" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="P64" s="3"/>
-      <c r="Q64" s="3" t="s">
+      <c r="P64" s="4"/>
+      <c r="Q64" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="R64" s="3"/>
-      <c r="S64" s="3" t="s">
+      <c r="R64" s="4"/>
+      <c r="S64" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="T64" s="3"/>
-      <c r="U64" s="3" t="s">
+      <c r="T64" s="4"/>
+      <c r="U64" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="V64" s="3"/>
-      <c r="W64" s="3" t="s">
+      <c r="V64" s="4"/>
+      <c r="W64" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="X64" s="3"/>
-      <c r="Y64" s="3" t="s">
+      <c r="X64" s="4"/>
+      <c r="Y64" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="Z64" s="3"/>
-      <c r="AA64" s="3" t="s">
+      <c r="Z64" s="4"/>
+      <c r="AA64" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="AB64" s="3"/>
-      <c r="AC64" s="3" t="s">
+      <c r="AB64" s="4"/>
+      <c r="AC64" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="AD64" s="3"/>
-      <c r="AE64" s="3" t="s">
+      <c r="AD64" s="4"/>
+      <c r="AE64" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AF64" s="3"/>
-      <c r="AG64" s="3" t="s">
+      <c r="AF64" s="4"/>
+      <c r="AG64" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="AH64" s="3"/>
-      <c r="AI64" s="3" t="s">
+      <c r="AH64" s="4"/>
+      <c r="AI64" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="AJ64" s="3"/>
-      <c r="AK64" s="3" t="s">
+      <c r="AJ64" s="4"/>
+      <c r="AK64" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="AL64" s="3"/>
-      <c r="AM64" s="3" t="s">
+      <c r="AL64" s="4"/>
+      <c r="AM64" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="AN64" s="3"/>
+      <c r="AN64" s="4"/>
     </row>
     <row r="65" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
         <v>26</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C65" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3" t="s">
+      <c r="D65" s="4"/>
+      <c r="E65" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3" t="s">
+      <c r="F65" s="4"/>
+      <c r="G65" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3" t="s">
+      <c r="H65" s="4"/>
+      <c r="I65" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3" t="s">
+      <c r="J65" s="4"/>
+      <c r="K65" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L65" s="3"/>
-      <c r="M65" s="3" t="s">
+      <c r="L65" s="4"/>
+      <c r="M65" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="N65" s="3"/>
-      <c r="O65" s="3" t="s">
+      <c r="N65" s="4"/>
+      <c r="O65" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="P65" s="3"/>
-      <c r="Q65" s="3" t="s">
+      <c r="P65" s="4"/>
+      <c r="Q65" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="R65" s="3"/>
-      <c r="S65" s="3" t="s">
+      <c r="R65" s="4"/>
+      <c r="S65" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="T65" s="3"/>
-      <c r="U65" s="3" t="s">
+      <c r="T65" s="4"/>
+      <c r="U65" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="V65" s="3"/>
-      <c r="W65" s="3" t="s">
+      <c r="V65" s="4"/>
+      <c r="W65" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="X65" s="3"/>
-      <c r="Y65" s="3" t="s">
+      <c r="X65" s="4"/>
+      <c r="Y65" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="Z65" s="3"/>
-      <c r="AA65" s="3" t="s">
+      <c r="Z65" s="4"/>
+      <c r="AA65" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="AB65" s="3"/>
-      <c r="AC65" s="3" t="s">
+      <c r="AB65" s="4"/>
+      <c r="AC65" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="AD65" s="3"/>
-      <c r="AE65" s="3" t="s">
+      <c r="AD65" s="4"/>
+      <c r="AE65" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="AF65" s="3"/>
-      <c r="AG65" s="3" t="s">
+      <c r="AF65" s="4"/>
+      <c r="AG65" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="AH65" s="3"/>
-      <c r="AI65" s="3" t="s">
+      <c r="AH65" s="4"/>
+      <c r="AI65" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="AJ65" s="3"/>
-      <c r="AK65" s="3" t="s">
+      <c r="AJ65" s="4"/>
+      <c r="AK65" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="AL65" s="3"/>
-      <c r="AM65" s="3" t="s">
+      <c r="AL65" s="4"/>
+      <c r="AM65" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="AN65" s="3"/>
+      <c r="AN65" s="4"/>
     </row>
     <row r="66" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
@@ -16615,213 +17930,213 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CEFDD9D-FDB3-41CB-A695-1350C2A9CE69}">
-  <dimension ref="B2:AN187"/>
+  <dimension ref="B2:AN188"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:40" x14ac:dyDescent="0.3">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
-      <c r="AD2" s="4"/>
-      <c r="AE2" s="4"/>
-      <c r="AF2" s="4"/>
-      <c r="AG2" s="4"/>
-      <c r="AH2" s="4"/>
-      <c r="AI2" s="4"/>
-      <c r="AJ2" s="4"/>
-      <c r="AK2" s="4"/>
-      <c r="AL2" s="4"/>
-      <c r="AM2" s="4"/>
-      <c r="AN2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="5"/>
+      <c r="AF2" s="5"/>
+      <c r="AG2" s="5"/>
+      <c r="AH2" s="5"/>
+      <c r="AI2" s="5"/>
+      <c r="AJ2" s="5"/>
+      <c r="AK2" s="5"/>
+      <c r="AL2" s="5"/>
+      <c r="AM2" s="5"/>
+      <c r="AN2" s="5"/>
     </row>
     <row r="3" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3" t="s">
+      <c r="D3" s="4"/>
+      <c r="E3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3" t="s">
+      <c r="F3" s="4"/>
+      <c r="G3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3" t="s">
+      <c r="H3" s="4"/>
+      <c r="I3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3" t="s">
+      <c r="J3" s="4"/>
+      <c r="K3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3" t="s">
+      <c r="L3" s="4"/>
+      <c r="M3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3" t="s">
+      <c r="N3" s="4"/>
+      <c r="O3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3" t="s">
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3" t="s">
+      <c r="R3" s="4"/>
+      <c r="S3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3" t="s">
+      <c r="T3" s="4"/>
+      <c r="U3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3" t="s">
+      <c r="V3" s="4"/>
+      <c r="W3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3" t="s">
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3" t="s">
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="3" t="s">
+      <c r="AB3" s="4"/>
+      <c r="AC3" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="AD3" s="3"/>
-      <c r="AE3" s="3" t="s">
+      <c r="AD3" s="4"/>
+      <c r="AE3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AF3" s="3"/>
-      <c r="AG3" s="3" t="s">
+      <c r="AF3" s="4"/>
+      <c r="AG3" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="AH3" s="3"/>
-      <c r="AI3" s="3" t="s">
+      <c r="AH3" s="4"/>
+      <c r="AI3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="AJ3" s="3"/>
-      <c r="AK3" s="3" t="s">
+      <c r="AJ3" s="4"/>
+      <c r="AK3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="AL3" s="3"/>
-      <c r="AM3" s="3" t="s">
+      <c r="AL3" s="4"/>
+      <c r="AM3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="AN3" s="3"/>
+      <c r="AN3" s="4"/>
     </row>
     <row r="4" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3" t="s">
+      <c r="D4" s="4"/>
+      <c r="E4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3" t="s">
+      <c r="F4" s="4"/>
+      <c r="G4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3" t="s">
+      <c r="H4" s="4"/>
+      <c r="I4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3" t="s">
+      <c r="J4" s="4"/>
+      <c r="K4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3" t="s">
+      <c r="L4" s="4"/>
+      <c r="M4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3" t="s">
+      <c r="N4" s="4"/>
+      <c r="O4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3" t="s">
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3" t="s">
+      <c r="R4" s="4"/>
+      <c r="S4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3" t="s">
+      <c r="T4" s="4"/>
+      <c r="U4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3" t="s">
+      <c r="V4" s="4"/>
+      <c r="W4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3" t="s">
+      <c r="X4" s="4"/>
+      <c r="Y4" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3" t="s">
+      <c r="Z4" s="4"/>
+      <c r="AA4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="AB4" s="3"/>
-      <c r="AC4" s="3" t="s">
+      <c r="AB4" s="4"/>
+      <c r="AC4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="AD4" s="3"/>
-      <c r="AE4" s="3" t="s">
+      <c r="AD4" s="4"/>
+      <c r="AE4" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="AF4" s="3"/>
-      <c r="AG4" s="3" t="s">
+      <c r="AF4" s="4"/>
+      <c r="AG4" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="AH4" s="3"/>
-      <c r="AI4" s="3" t="s">
+      <c r="AH4" s="4"/>
+      <c r="AI4" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="AJ4" s="3"/>
-      <c r="AK4" s="3" t="s">
+      <c r="AJ4" s="4"/>
+      <c r="AK4" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="AL4" s="3"/>
-      <c r="AM4" s="3" t="s">
+      <c r="AL4" s="4"/>
+      <c r="AM4" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="AN4" s="3"/>
+      <c r="AN4" s="4"/>
     </row>
     <row r="5" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
@@ -18574,14 +19889,8 @@
       <c r="R22" t="s">
         <v>76</v>
       </c>
-      <c r="S22" t="s">
-        <v>45</v>
-      </c>
-      <c r="T22" t="s">
-        <v>45</v>
-      </c>
       <c r="U22" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="2:40" x14ac:dyDescent="0.3">
@@ -18636,14 +19945,8 @@
       <c r="R23" t="s">
         <v>75</v>
       </c>
-      <c r="S23" t="s">
-        <v>47</v>
-      </c>
-      <c r="T23" t="s">
-        <v>48</v>
-      </c>
       <c r="U23" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="2:40" x14ac:dyDescent="0.3">
@@ -18714,18 +20017,6 @@
         <f>AG9*100</f>
         <v>99.60703147712556</v>
       </c>
-      <c r="S24">
-        <f>AI9*100</f>
-        <v>0</v>
-      </c>
-      <c r="T24">
-        <f>AK9*100</f>
-        <v>0</v>
-      </c>
-      <c r="U24">
-        <f>AM9*100</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="25" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
@@ -18795,18 +20086,6 @@
         <f>AH9*100</f>
         <v>99.821700201624736</v>
       </c>
-      <c r="S25">
-        <f>AJ9*100</f>
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <f>AL9*100</f>
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <f>AN9*100</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="26" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
@@ -18876,22 +20155,14 @@
         <f>IFERROR(((AG6-AH6)/AG6)*100, 0)</f>
         <v>47.625052543085324</v>
       </c>
-      <c r="S26">
-        <f>IFERROR(((AI6-AJ6)/AI6)*100, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <f>IFERROR(((AK6-AL6)/AK6)*100, 0)</f>
-        <v>0</v>
-      </c>
       <c r="U26">
-        <f>IFERROR(((AM6-AN6)/AM6)*100, 0)</f>
-        <v>0</v>
+        <f>SUM(C26:R26)/COLUMNS(C26:R26)</f>
+        <v>34.353165863987456</v>
       </c>
     </row>
     <row r="27" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="C27">
         <f>C13</f>
@@ -18957,22 +20228,14 @@
         <f>AG13</f>
         <v>0.3030685161832703</v>
       </c>
-      <c r="S27">
-        <f>AI13</f>
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <f>AK13</f>
-        <v>0</v>
-      </c>
       <c r="U27">
-        <f>AM13</f>
-        <v>0</v>
+        <f>SUM(C27:R27)/COLUMNS(C27:R27)</f>
+        <v>0.39307622869439407</v>
       </c>
     </row>
     <row r="28" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="C28">
         <f>D13</f>
@@ -19038,223 +20301,215 @@
         <f>AH13</f>
         <v>0.5786516853932584</v>
       </c>
-      <c r="S28">
-        <f>AJ13</f>
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <f>AL13</f>
-        <v>0</v>
-      </c>
       <c r="U28">
-        <f>AN13</f>
-        <v>0</v>
+        <f>SUM(C28:R28)/COLUMNS(C28:R28)</f>
+        <v>0.61038406266350664</v>
       </c>
     </row>
     <row r="84" spans="2:40" x14ac:dyDescent="0.3">
-      <c r="B84" s="5" t="s">
+      <c r="B84" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C84" s="5"/>
-      <c r="D84" s="5"/>
-      <c r="E84" s="5"/>
-      <c r="F84" s="5"/>
-      <c r="G84" s="5"/>
-      <c r="H84" s="5"/>
-      <c r="I84" s="5"/>
-      <c r="J84" s="5"/>
-      <c r="K84" s="5"/>
-      <c r="L84" s="5"/>
-      <c r="M84" s="5"/>
-      <c r="N84" s="5"/>
-      <c r="O84" s="5"/>
-      <c r="P84" s="5"/>
-      <c r="Q84" s="5"/>
-      <c r="R84" s="5"/>
-      <c r="S84" s="5"/>
-      <c r="T84" s="5"/>
-      <c r="U84" s="5"/>
-      <c r="V84" s="5"/>
-      <c r="W84" s="5"/>
-      <c r="X84" s="5"/>
-      <c r="Y84" s="5"/>
-      <c r="Z84" s="5"/>
-      <c r="AA84" s="5"/>
-      <c r="AB84" s="5"/>
-      <c r="AC84" s="5"/>
-      <c r="AD84" s="5"/>
-      <c r="AE84" s="5"/>
-      <c r="AF84" s="5"/>
-      <c r="AG84" s="5"/>
-      <c r="AH84" s="5"/>
-      <c r="AI84" s="5"/>
-      <c r="AJ84" s="5"/>
-      <c r="AK84" s="5"/>
-      <c r="AL84" s="5"/>
-      <c r="AM84" s="5"/>
-      <c r="AN84" s="5"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="6"/>
+      <c r="G84" s="6"/>
+      <c r="H84" s="6"/>
+      <c r="I84" s="6"/>
+      <c r="J84" s="6"/>
+      <c r="K84" s="6"/>
+      <c r="L84" s="6"/>
+      <c r="M84" s="6"/>
+      <c r="N84" s="6"/>
+      <c r="O84" s="6"/>
+      <c r="P84" s="6"/>
+      <c r="Q84" s="6"/>
+      <c r="R84" s="6"/>
+      <c r="S84" s="6"/>
+      <c r="T84" s="6"/>
+      <c r="U84" s="6"/>
+      <c r="V84" s="6"/>
+      <c r="W84" s="6"/>
+      <c r="X84" s="6"/>
+      <c r="Y84" s="6"/>
+      <c r="Z84" s="6"/>
+      <c r="AA84" s="6"/>
+      <c r="AB84" s="6"/>
+      <c r="AC84" s="6"/>
+      <c r="AD84" s="6"/>
+      <c r="AE84" s="6"/>
+      <c r="AF84" s="6"/>
+      <c r="AG84" s="6"/>
+      <c r="AH84" s="6"/>
+      <c r="AI84" s="6"/>
+      <c r="AJ84" s="6"/>
+      <c r="AK84" s="6"/>
+      <c r="AL84" s="6"/>
+      <c r="AM84" s="6"/>
+      <c r="AN84" s="6"/>
     </row>
     <row r="85" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B85" t="s">
         <v>27</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C85" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D85" s="3"/>
-      <c r="E85" s="3" t="s">
+      <c r="D85" s="4"/>
+      <c r="E85" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F85" s="3"/>
-      <c r="G85" s="3" t="s">
+      <c r="F85" s="4"/>
+      <c r="G85" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H85" s="3"/>
-      <c r="I85" s="3" t="s">
+      <c r="H85" s="4"/>
+      <c r="I85" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J85" s="3"/>
-      <c r="K85" s="3" t="s">
+      <c r="J85" s="4"/>
+      <c r="K85" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="L85" s="3"/>
-      <c r="M85" s="3" t="s">
+      <c r="L85" s="4"/>
+      <c r="M85" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="N85" s="3"/>
-      <c r="O85" s="3" t="s">
+      <c r="N85" s="4"/>
+      <c r="O85" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="P85" s="3"/>
-      <c r="Q85" s="3" t="s">
+      <c r="P85" s="4"/>
+      <c r="Q85" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="R85" s="3"/>
-      <c r="S85" s="3" t="s">
+      <c r="R85" s="4"/>
+      <c r="S85" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="T85" s="3"/>
-      <c r="U85" s="3" t="s">
+      <c r="T85" s="4"/>
+      <c r="U85" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="V85" s="3"/>
-      <c r="W85" s="3" t="s">
+      <c r="V85" s="4"/>
+      <c r="W85" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="X85" s="3"/>
-      <c r="Y85" s="3" t="s">
+      <c r="X85" s="4"/>
+      <c r="Y85" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="Z85" s="3"/>
-      <c r="AA85" s="3" t="s">
+      <c r="Z85" s="4"/>
+      <c r="AA85" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="AB85" s="3"/>
-      <c r="AC85" s="3" t="s">
+      <c r="AB85" s="4"/>
+      <c r="AC85" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="AD85" s="3"/>
-      <c r="AE85" s="3" t="s">
+      <c r="AD85" s="4"/>
+      <c r="AE85" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AF85" s="3"/>
-      <c r="AG85" s="3" t="s">
+      <c r="AF85" s="4"/>
+      <c r="AG85" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="AH85" s="3"/>
-      <c r="AI85" s="3" t="s">
+      <c r="AH85" s="4"/>
+      <c r="AI85" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="AJ85" s="3"/>
-      <c r="AK85" s="3" t="s">
+      <c r="AJ85" s="4"/>
+      <c r="AK85" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="AL85" s="3"/>
-      <c r="AM85" s="3" t="s">
+      <c r="AL85" s="4"/>
+      <c r="AM85" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="AN85" s="3"/>
+      <c r="AN85" s="4"/>
     </row>
     <row r="86" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B86" t="s">
         <v>26</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="C86" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D86" s="3"/>
-      <c r="E86" s="3" t="s">
+      <c r="D86" s="4"/>
+      <c r="E86" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F86" s="3"/>
-      <c r="G86" s="3" t="s">
+      <c r="F86" s="4"/>
+      <c r="G86" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H86" s="3"/>
-      <c r="I86" s="3" t="s">
+      <c r="H86" s="4"/>
+      <c r="I86" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J86" s="3"/>
-      <c r="K86" s="3" t="s">
+      <c r="J86" s="4"/>
+      <c r="K86" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L86" s="3"/>
-      <c r="M86" s="3" t="s">
+      <c r="L86" s="4"/>
+      <c r="M86" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="N86" s="3"/>
-      <c r="O86" s="3" t="s">
+      <c r="N86" s="4"/>
+      <c r="O86" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="P86" s="3"/>
-      <c r="Q86" s="3" t="s">
+      <c r="P86" s="4"/>
+      <c r="Q86" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="R86" s="3"/>
-      <c r="S86" s="3" t="s">
+      <c r="R86" s="4"/>
+      <c r="S86" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="T86" s="3"/>
-      <c r="U86" s="3" t="s">
+      <c r="T86" s="4"/>
+      <c r="U86" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="V86" s="3"/>
-      <c r="W86" s="3" t="s">
+      <c r="V86" s="4"/>
+      <c r="W86" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="X86" s="3"/>
-      <c r="Y86" s="3" t="s">
+      <c r="X86" s="4"/>
+      <c r="Y86" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="Z86" s="3"/>
-      <c r="AA86" s="3" t="s">
+      <c r="Z86" s="4"/>
+      <c r="AA86" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="AB86" s="3"/>
-      <c r="AC86" s="3" t="s">
+      <c r="AB86" s="4"/>
+      <c r="AC86" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="AD86" s="3"/>
-      <c r="AE86" s="3" t="s">
+      <c r="AD86" s="4"/>
+      <c r="AE86" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="AF86" s="3"/>
-      <c r="AG86" s="3" t="s">
+      <c r="AF86" s="4"/>
+      <c r="AG86" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="AH86" s="3"/>
-      <c r="AI86" s="3" t="s">
+      <c r="AH86" s="4"/>
+      <c r="AI86" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="AJ86" s="3"/>
-      <c r="AK86" s="3" t="s">
+      <c r="AJ86" s="4"/>
+      <c r="AK86" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="AL86" s="3"/>
-      <c r="AM86" s="3" t="s">
+      <c r="AL86" s="4"/>
+      <c r="AM86" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="AN86" s="3"/>
+      <c r="AN86" s="4"/>
     </row>
     <row r="87" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B87" t="s">
@@ -21007,14 +22262,8 @@
       <c r="R104" t="s">
         <v>76</v>
       </c>
-      <c r="S104" t="s">
-        <v>45</v>
-      </c>
-      <c r="T104" t="s">
-        <v>45</v>
-      </c>
       <c r="U104" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
     </row>
     <row r="105" spans="2:40" x14ac:dyDescent="0.3">
@@ -21069,14 +22318,8 @@
       <c r="R105" t="s">
         <v>75</v>
       </c>
-      <c r="S105" t="s">
-        <v>47</v>
-      </c>
-      <c r="T105" t="s">
-        <v>48</v>
-      </c>
       <c r="U105" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
     </row>
     <row r="106" spans="2:40" x14ac:dyDescent="0.3">
@@ -21147,18 +22390,6 @@
         <f>AG91*100</f>
         <v>99.60703147712556</v>
       </c>
-      <c r="S106">
-        <f>AI91*100</f>
-        <v>0</v>
-      </c>
-      <c r="T106">
-        <f>AK91*100</f>
-        <v>0</v>
-      </c>
-      <c r="U106">
-        <f>AM91*100</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="107" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B107" t="s">
@@ -21228,18 +22459,6 @@
         <f>AH91*100</f>
         <v>99.821700201624736</v>
       </c>
-      <c r="S107">
-        <f>AJ91*100</f>
-        <v>0</v>
-      </c>
-      <c r="T107">
-        <f>AL91*100</f>
-        <v>0</v>
-      </c>
-      <c r="U107">
-        <f>AN91*100</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="108" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B108" t="s">
@@ -21309,22 +22528,14 @@
         <f>IFERROR(((AG88-AH88)/AG88)*100, 0)</f>
         <v>47.625052543085324</v>
       </c>
-      <c r="S108">
-        <f>IFERROR(((AI88-AJ88)/AI88)*100, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="T108">
-        <f>IFERROR(((AK88-AL88)/AK88)*100, 0)</f>
-        <v>0</v>
-      </c>
       <c r="U108">
-        <f>IFERROR(((AM88-AN88)/AM88)*100, 0)</f>
-        <v>0</v>
+        <f>SUM(C108:R108)/COLUMNS(C108:R108)</f>
+        <v>36.215861874989677</v>
       </c>
     </row>
     <row r="109" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B109" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="C109">
         <f>C95</f>
@@ -21390,22 +22601,14 @@
         <f>AG95</f>
         <v>0.3030685161832703</v>
       </c>
-      <c r="S109">
-        <f>AI95</f>
-        <v>0</v>
-      </c>
-      <c r="T109">
-        <f>AK95</f>
-        <v>0</v>
-      </c>
       <c r="U109">
-        <f>AM95</f>
-        <v>0</v>
+        <f>SUM(C109:R109)/COLUMNS(C109:R109)</f>
+        <v>0.39307622869439407</v>
       </c>
     </row>
     <row r="110" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B110" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="C110">
         <f>D95</f>
@@ -21471,179 +22674,147 @@
         <f>AH95</f>
         <v>0.5786516853932584</v>
       </c>
-      <c r="S110">
-        <f>AJ95</f>
-        <v>0</v>
-      </c>
-      <c r="T110">
-        <f>AL95</f>
-        <v>0</v>
-      </c>
       <c r="U110">
-        <f>AN95</f>
-        <v>0</v>
+        <f>SUM(C110:R110)/COLUMNS(C110:R110)</f>
+        <v>0.62454697134445358</v>
       </c>
     </row>
     <row r="156" spans="2:40" x14ac:dyDescent="0.3">
-      <c r="B156" s="6" t="s">
+      <c r="B156" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C156" s="6"/>
-      <c r="D156" s="6"/>
-      <c r="E156" s="6"/>
-      <c r="F156" s="6"/>
-      <c r="G156" s="6"/>
-      <c r="H156" s="6"/>
-      <c r="I156" s="6"/>
-      <c r="J156" s="6"/>
-      <c r="K156" s="6"/>
-      <c r="L156" s="6"/>
-      <c r="M156" s="6"/>
-      <c r="N156" s="6"/>
-      <c r="O156" s="6"/>
-      <c r="P156" s="6"/>
-      <c r="Q156" s="7"/>
-      <c r="R156" s="7"/>
-      <c r="S156" s="7"/>
-      <c r="T156" s="7"/>
-      <c r="U156" s="7"/>
-      <c r="V156" s="7"/>
-      <c r="W156" s="7"/>
-      <c r="X156" s="7"/>
-      <c r="Y156" s="7"/>
-      <c r="Z156" s="7"/>
-      <c r="AA156" s="7"/>
-      <c r="AB156" s="7"/>
-      <c r="AC156" s="7"/>
-      <c r="AD156" s="7"/>
-      <c r="AE156" s="7"/>
-      <c r="AF156" s="7"/>
-      <c r="AG156" s="7"/>
-      <c r="AH156" s="7"/>
-      <c r="AI156" s="7"/>
-      <c r="AJ156" s="7"/>
-      <c r="AK156" s="7"/>
-      <c r="AL156" s="7"/>
-      <c r="AM156" s="7"/>
-      <c r="AN156" s="7"/>
+      <c r="C156" s="7"/>
+      <c r="D156" s="7"/>
+      <c r="E156" s="7"/>
+      <c r="F156" s="7"/>
+      <c r="G156" s="7"/>
+      <c r="H156" s="7"/>
+      <c r="I156" s="7"/>
+      <c r="J156" s="7"/>
+      <c r="K156" s="7"/>
+      <c r="L156" s="7"/>
+      <c r="M156" s="7"/>
+      <c r="N156" s="7"/>
+      <c r="O156" s="7"/>
+      <c r="P156" s="7"/>
     </row>
     <row r="157" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B157" t="s">
         <v>27</v>
       </c>
-      <c r="C157" s="3" t="s">
+      <c r="C157" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D157" s="3"/>
-      <c r="E157" s="3" t="s">
+      <c r="D157" s="4"/>
+      <c r="E157" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F157" s="3"/>
-      <c r="G157" s="3" t="s">
+      <c r="F157" s="4"/>
+      <c r="G157" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H157" s="3"/>
-      <c r="I157" s="3" t="s">
+      <c r="H157" s="4"/>
+      <c r="I157" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="J157" s="3"/>
-      <c r="K157" s="3" t="s">
+      <c r="J157" s="4"/>
+      <c r="K157" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="L157" s="3"/>
-      <c r="M157" s="3" t="s">
+      <c r="L157" s="4"/>
+      <c r="M157" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="N157" s="3"/>
-      <c r="O157" s="3" t="s">
+      <c r="N157" s="4"/>
+      <c r="O157" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="P157" s="3"/>
+      <c r="P157" s="4"/>
       <c r="Q157" s="2" t="s">
         <v>66</v>
       </c>
       <c r="R157" s="2"/>
-      <c r="S157" s="3"/>
-      <c r="T157" s="3"/>
-      <c r="U157" s="3"/>
-      <c r="V157" s="3"/>
-      <c r="W157" s="3"/>
-      <c r="X157" s="3"/>
-      <c r="Y157" s="3"/>
-      <c r="Z157" s="3"/>
-      <c r="AA157" s="3"/>
-      <c r="AB157" s="3"/>
-      <c r="AC157" s="3"/>
-      <c r="AD157" s="3"/>
-      <c r="AE157" s="3"/>
-      <c r="AF157" s="3"/>
-      <c r="AG157" s="3"/>
-      <c r="AH157" s="3"/>
-      <c r="AI157" s="3"/>
-      <c r="AJ157" s="3"/>
-      <c r="AK157" s="3"/>
-      <c r="AL157" s="3"/>
-      <c r="AM157" s="3"/>
-      <c r="AN157" s="3"/>
+      <c r="S157" s="4"/>
+      <c r="T157" s="4"/>
+      <c r="U157" s="4"/>
+      <c r="V157" s="4"/>
+      <c r="W157" s="4"/>
+      <c r="X157" s="4"/>
+      <c r="Y157" s="4"/>
+      <c r="Z157" s="4"/>
+      <c r="AA157" s="4"/>
+      <c r="AB157" s="4"/>
+      <c r="AC157" s="4"/>
+      <c r="AD157" s="4"/>
+      <c r="AE157" s="4"/>
+      <c r="AF157" s="4"/>
+      <c r="AG157" s="4"/>
+      <c r="AH157" s="4"/>
+      <c r="AI157" s="4"/>
+      <c r="AJ157" s="4"/>
+      <c r="AK157" s="4"/>
+      <c r="AL157" s="4"/>
+      <c r="AM157" s="4"/>
+      <c r="AN157" s="4"/>
     </row>
     <row r="158" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B158" t="s">
         <v>26</v>
       </c>
-      <c r="C158" s="3" t="s">
+      <c r="C158" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D158" s="3"/>
-      <c r="E158" s="3" t="s">
+      <c r="D158" s="4"/>
+      <c r="E158" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="F158" s="3"/>
-      <c r="G158" s="3" t="s">
+      <c r="F158" s="4"/>
+      <c r="G158" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H158" s="3"/>
-      <c r="I158" s="3" t="s">
+      <c r="H158" s="4"/>
+      <c r="I158" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="J158" s="3"/>
-      <c r="K158" s="3" t="s">
+      <c r="J158" s="4"/>
+      <c r="K158" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="L158" s="3"/>
-      <c r="M158" s="3" t="s">
+      <c r="L158" s="4"/>
+      <c r="M158" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="N158" s="3"/>
-      <c r="O158" s="3" t="s">
+      <c r="N158" s="4"/>
+      <c r="O158" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="P158" s="3"/>
+      <c r="P158" s="4"/>
       <c r="Q158" s="2" t="s">
         <v>72</v>
       </c>
       <c r="R158" s="2"/>
-      <c r="S158" s="3"/>
-      <c r="T158" s="3"/>
-      <c r="U158" s="3"/>
-      <c r="V158" s="3"/>
-      <c r="W158" s="3"/>
-      <c r="X158" s="3"/>
-      <c r="Y158" s="3"/>
-      <c r="Z158" s="3"/>
-      <c r="AA158" s="3"/>
-      <c r="AB158" s="3"/>
-      <c r="AC158" s="3"/>
-      <c r="AD158" s="3"/>
-      <c r="AE158" s="3"/>
-      <c r="AF158" s="3"/>
-      <c r="AG158" s="3"/>
-      <c r="AH158" s="3"/>
-      <c r="AI158" s="3"/>
-      <c r="AJ158" s="3"/>
-      <c r="AK158" s="3"/>
-      <c r="AL158" s="3"/>
-      <c r="AM158" s="3"/>
-      <c r="AN158" s="3"/>
+      <c r="S158" s="4"/>
+      <c r="T158" s="4"/>
+      <c r="U158" s="4"/>
+      <c r="V158" s="4"/>
+      <c r="W158" s="4"/>
+      <c r="X158" s="4"/>
+      <c r="Y158" s="4"/>
+      <c r="Z158" s="4"/>
+      <c r="AA158" s="4"/>
+      <c r="AB158" s="4"/>
+      <c r="AC158" s="4"/>
+      <c r="AD158" s="4"/>
+      <c r="AE158" s="4"/>
+      <c r="AF158" s="4"/>
+      <c r="AG158" s="4"/>
+      <c r="AH158" s="4"/>
+      <c r="AI158" s="4"/>
+      <c r="AJ158" s="4"/>
+      <c r="AK158" s="4"/>
+      <c r="AL158" s="4"/>
+      <c r="AM158" s="4"/>
+      <c r="AN158" s="4"/>
     </row>
     <row r="159" spans="2:40" x14ac:dyDescent="0.3">
       <c r="B159" t="s">
@@ -22792,11 +23963,16 @@
       </c>
     </row>
     <row r="187" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B187" s="8" t="s">
+      <c r="B187" s="3" t="s">
         <v>74</v>
       </c>
       <c r="C187" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="188" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C188" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -22825,18 +24001,6 @@
     <mergeCell ref="W158:X158"/>
     <mergeCell ref="Y158:Z158"/>
     <mergeCell ref="C157:D157"/>
-    <mergeCell ref="E157:F157"/>
-    <mergeCell ref="G157:H157"/>
-    <mergeCell ref="I157:J157"/>
-    <mergeCell ref="K157:L157"/>
-    <mergeCell ref="M157:N157"/>
-    <mergeCell ref="O157:P157"/>
-    <mergeCell ref="S157:T157"/>
-    <mergeCell ref="U157:V157"/>
-    <mergeCell ref="W157:X157"/>
-    <mergeCell ref="Y157:Z157"/>
-    <mergeCell ref="AA157:AB157"/>
-    <mergeCell ref="AC157:AD157"/>
     <mergeCell ref="AE157:AF157"/>
     <mergeCell ref="AM4:AN4"/>
     <mergeCell ref="AA4:AB4"/>
@@ -22845,17 +24009,37 @@
     <mergeCell ref="AG4:AH4"/>
     <mergeCell ref="AI4:AJ4"/>
     <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B84:AN84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="E85:F85"/>
+    <mergeCell ref="G85:H85"/>
+    <mergeCell ref="I85:J85"/>
+    <mergeCell ref="K85:L85"/>
+    <mergeCell ref="M85:N85"/>
+    <mergeCell ref="O85:P85"/>
+    <mergeCell ref="Q85:R85"/>
+    <mergeCell ref="S85:T85"/>
+    <mergeCell ref="U85:V85"/>
+    <mergeCell ref="W85:X85"/>
+    <mergeCell ref="Y85:Z85"/>
+    <mergeCell ref="E157:F157"/>
+    <mergeCell ref="G157:H157"/>
+    <mergeCell ref="I157:J157"/>
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="W3:X3"/>
     <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="Y157:Z157"/>
+    <mergeCell ref="AA157:AB157"/>
+    <mergeCell ref="AC157:AD157"/>
+    <mergeCell ref="K157:L157"/>
+    <mergeCell ref="M157:N157"/>
+    <mergeCell ref="O157:P157"/>
+    <mergeCell ref="S157:T157"/>
+    <mergeCell ref="U157:V157"/>
+    <mergeCell ref="W157:X157"/>
     <mergeCell ref="O4:P4"/>
     <mergeCell ref="Q4:R4"/>
     <mergeCell ref="S4:T4"/>
@@ -22877,26 +24061,19 @@
     <mergeCell ref="AM3:AN3"/>
     <mergeCell ref="AC3:AD3"/>
     <mergeCell ref="AE3:AF3"/>
-    <mergeCell ref="B84:AN84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="E85:F85"/>
-    <mergeCell ref="G85:H85"/>
-    <mergeCell ref="I85:J85"/>
-    <mergeCell ref="K85:L85"/>
-    <mergeCell ref="M85:N85"/>
-    <mergeCell ref="O85:P85"/>
-    <mergeCell ref="Q85:R85"/>
-    <mergeCell ref="S85:T85"/>
-    <mergeCell ref="U85:V85"/>
-    <mergeCell ref="W85:X85"/>
-    <mergeCell ref="Y85:Z85"/>
-    <mergeCell ref="AA85:AB85"/>
-    <mergeCell ref="AC85:AD85"/>
-    <mergeCell ref="AE85:AF85"/>
-    <mergeCell ref="AG85:AH85"/>
-    <mergeCell ref="AI85:AJ85"/>
-    <mergeCell ref="AK85:AL85"/>
-    <mergeCell ref="AM85:AN85"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="U86:V86"/>
+    <mergeCell ref="W86:X86"/>
+    <mergeCell ref="Y86:Z86"/>
+    <mergeCell ref="AK86:AL86"/>
+    <mergeCell ref="AM86:AN86"/>
+    <mergeCell ref="AA86:AB86"/>
+    <mergeCell ref="AC86:AD86"/>
+    <mergeCell ref="AE86:AF86"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="Y4:Z4"/>
     <mergeCell ref="C86:D86"/>
     <mergeCell ref="E86:F86"/>
     <mergeCell ref="G86:H86"/>
@@ -22906,16 +24083,15 @@
     <mergeCell ref="O86:P86"/>
     <mergeCell ref="Q86:R86"/>
     <mergeCell ref="S86:T86"/>
-    <mergeCell ref="U86:V86"/>
-    <mergeCell ref="W86:X86"/>
-    <mergeCell ref="Y86:Z86"/>
-    <mergeCell ref="AK86:AL86"/>
-    <mergeCell ref="AM86:AN86"/>
-    <mergeCell ref="AA86:AB86"/>
-    <mergeCell ref="AC86:AD86"/>
-    <mergeCell ref="AE86:AF86"/>
     <mergeCell ref="AG86:AH86"/>
     <mergeCell ref="AI86:AJ86"/>
+    <mergeCell ref="AA85:AB85"/>
+    <mergeCell ref="AC85:AD85"/>
+    <mergeCell ref="AE85:AF85"/>
+    <mergeCell ref="AG85:AH85"/>
+    <mergeCell ref="AI85:AJ85"/>
+    <mergeCell ref="AK85:AL85"/>
+    <mergeCell ref="AM85:AN85"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
